--- a/checkrates/week-18/Analisis_Checkrates_OP_7d.xlsx
+++ b/checkrates/week-18/Analisis_Checkrates_OP_7d.xlsx
@@ -541,7 +541,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 05/05/2026 01:35 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 03:47 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -694,7 +694,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 05/05/2026 01:35 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 03:47 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -821,19 +821,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J55"/>
+  <dimension ref="A1:K55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
     <col width="50" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
     <col width="41" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="11" customWidth="1" min="7" max="7"/>
-    <col width="23" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
     <col width="23" customWidth="1" min="9" max="9"/>
-    <col width="16" customWidth="1" min="10" max="10"/>
+    <col width="23" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -853,7 +854,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 05/05/2026 01:35 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 03:47 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -880,30 +881,35 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
+          <t>Channel</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
           <t>CR_Unicos</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="G5" s="3" t="inlineStr">
         <is>
           <t>Success</t>
         </is>
       </c>
-      <c r="G5" s="3" t="inlineStr">
+      <c r="H5" s="3" t="inlineStr">
         <is>
           <t>Bookings</t>
         </is>
       </c>
-      <c r="H5" s="3" t="inlineStr">
+      <c r="I5" s="3" t="inlineStr">
         <is>
           <t>Eficacia</t>
         </is>
       </c>
-      <c r="I5" s="3" t="inlineStr">
+      <c r="J5" s="3" t="inlineStr">
         <is>
           <t>ConvRate</t>
         </is>
       </c>
-      <c r="J5" s="3" t="inlineStr">
+      <c r="K5" s="3" t="inlineStr">
         <is>
           <t>BandaEficacia</t>
         </is>
@@ -928,22 +934,27 @@
           <t>Puebla</t>
         </is>
       </c>
-      <c r="E6" s="12" t="n">
-        <v>0</v>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
       </c>
       <c r="F6" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G6" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" s="12" t="n">
         <v>1</v>
-      </c>
-      <c r="H6" s="13" t="n">
-        <v>0</v>
       </c>
       <c r="I6" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="J6" s="4" t="inlineStr">
+      <c r="J6" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" s="4" t="inlineStr">
         <is>
           <t>Súper Crítica</t>
         </is>
@@ -968,22 +979,27 @@
           <t>Hearst Area</t>
         </is>
       </c>
-      <c r="E7" s="12" t="n">
-        <v>0</v>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
       </c>
       <c r="F7" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G7" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" s="12" t="n">
         <v>1</v>
-      </c>
-      <c r="H7" s="13" t="n">
-        <v>0</v>
       </c>
       <c r="I7" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="J7" s="4" t="inlineStr">
+      <c r="J7" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" s="4" t="inlineStr">
         <is>
           <t>Súper Crítica</t>
         </is>
@@ -1008,22 +1024,27 @@
           <t>Seattle Area</t>
         </is>
       </c>
-      <c r="E8" s="12" t="n">
-        <v>0</v>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
       </c>
       <c r="F8" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G8" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" s="12" t="n">
         <v>1</v>
-      </c>
-      <c r="H8" s="13" t="n">
-        <v>0</v>
       </c>
       <c r="I8" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="J8" s="4" t="inlineStr">
+      <c r="J8" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" s="4" t="inlineStr">
         <is>
           <t>Súper Crítica</t>
         </is>
@@ -1048,22 +1069,27 @@
           <t>Chiapas</t>
         </is>
       </c>
-      <c r="E9" s="12" t="n">
-        <v>0</v>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
       </c>
       <c r="F9" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G9" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" s="12" t="n">
         <v>1</v>
-      </c>
-      <c r="H9" s="13" t="n">
-        <v>0</v>
       </c>
       <c r="I9" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="J9" s="4" t="inlineStr">
+      <c r="J9" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" s="4" t="inlineStr">
         <is>
           <t>Súper Crítica</t>
         </is>
@@ -1088,22 +1114,27 @@
           <t>Riviera Nayarit</t>
         </is>
       </c>
-      <c r="E10" s="12" t="n">
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F10" s="12" t="n">
         <v>439</v>
       </c>
-      <c r="F10" s="12" t="n">
+      <c r="G10" s="12" t="n">
         <v>21</v>
       </c>
-      <c r="G10" s="12" t="n">
+      <c r="H10" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="H10" s="13" t="n">
+      <c r="I10" s="13" t="n">
         <v>0.04783599088838269</v>
       </c>
-      <c r="I10" s="13" t="n">
+      <c r="J10" s="13" t="n">
         <v>0.002277904328018223</v>
       </c>
-      <c r="J10" s="4" t="inlineStr">
+      <c r="K10" s="4" t="inlineStr">
         <is>
           <t>Súper Crítica</t>
         </is>
@@ -1128,22 +1159,27 @@
           <t>Medellin Area</t>
         </is>
       </c>
-      <c r="E11" s="12" t="n">
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F11" s="12" t="n">
         <v>123</v>
       </c>
-      <c r="F11" s="12" t="n">
+      <c r="G11" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="G11" s="12" t="n">
+      <c r="H11" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="H11" s="13" t="n">
+      <c r="I11" s="13" t="n">
         <v>0.05691056910569105</v>
       </c>
-      <c r="I11" s="13" t="n">
+      <c r="J11" s="13" t="n">
         <v>0.008130081300813009</v>
       </c>
-      <c r="J11" s="4" t="inlineStr">
+      <c r="K11" s="4" t="inlineStr">
         <is>
           <t>Súper Crítica</t>
         </is>
@@ -1168,22 +1204,27 @@
           <t>Detroit Area</t>
         </is>
       </c>
-      <c r="E12" s="12" t="n">
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F12" s="12" t="n">
         <v>12</v>
-      </c>
-      <c r="F12" s="12" t="n">
-        <v>1</v>
       </c>
       <c r="G12" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="H12" s="13" t="n">
-        <v>0.08333333333333333</v>
+      <c r="H12" s="12" t="n">
+        <v>1</v>
       </c>
       <c r="I12" s="13" t="n">
         <v>0.08333333333333333</v>
       </c>
-      <c r="J12" s="4" t="inlineStr">
+      <c r="J12" s="13" t="n">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="K12" s="4" t="inlineStr">
         <is>
           <t>Súper Crítica</t>
         </is>
@@ -1208,22 +1249,27 @@
           <t>Riviera Nayarit</t>
         </is>
       </c>
-      <c r="E13" s="12" t="n">
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F13" s="12" t="n">
         <v>26</v>
       </c>
-      <c r="F13" s="12" t="n">
+      <c r="G13" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="G13" s="12" t="n">
+      <c r="H13" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="H13" s="13" t="n">
+      <c r="I13" s="13" t="n">
         <v>0.1153846153846154</v>
       </c>
-      <c r="I13" s="13" t="n">
+      <c r="J13" s="13" t="n">
         <v>0.07692307692307693</v>
       </c>
-      <c r="J13" s="4" t="inlineStr">
+      <c r="K13" s="4" t="inlineStr">
         <is>
           <t>Súper Crítica</t>
         </is>
@@ -1248,22 +1294,27 @@
           <t>Mazatlán</t>
         </is>
       </c>
-      <c r="E14" s="12" t="n">
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F14" s="12" t="n">
         <v>98</v>
       </c>
-      <c r="F14" s="12" t="n">
+      <c r="G14" s="12" t="n">
         <v>18</v>
       </c>
-      <c r="G14" s="12" t="n">
+      <c r="H14" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="H14" s="13" t="n">
+      <c r="I14" s="13" t="n">
         <v>0.1836734693877551</v>
       </c>
-      <c r="I14" s="13" t="n">
+      <c r="J14" s="13" t="n">
         <v>0.01020408163265306</v>
       </c>
-      <c r="J14" s="4" t="inlineStr">
+      <c r="K14" s="4" t="inlineStr">
         <is>
           <t>Súper Crítica</t>
         </is>
@@ -1288,22 +1339,27 @@
           <t>Munich Area</t>
         </is>
       </c>
-      <c r="E15" s="12" t="n">
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F15" s="12" t="n">
         <v>5</v>
-      </c>
-      <c r="F15" s="12" t="n">
-        <v>1</v>
       </c>
       <c r="G15" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="H15" s="13" t="n">
-        <v>0.2</v>
+      <c r="H15" s="12" t="n">
+        <v>1</v>
       </c>
       <c r="I15" s="13" t="n">
         <v>0.2</v>
       </c>
-      <c r="J15" s="4" t="inlineStr">
+      <c r="J15" s="13" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="K15" s="4" t="inlineStr">
         <is>
           <t>Súper Crítica</t>
         </is>
@@ -1328,22 +1384,27 @@
           <t>Managua Area</t>
         </is>
       </c>
-      <c r="E16" s="12" t="n">
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F16" s="12" t="n">
         <v>5</v>
-      </c>
-      <c r="F16" s="12" t="n">
-        <v>1</v>
       </c>
       <c r="G16" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="H16" s="13" t="n">
-        <v>0.2</v>
+      <c r="H16" s="12" t="n">
+        <v>1</v>
       </c>
       <c r="I16" s="13" t="n">
         <v>0.2</v>
       </c>
-      <c r="J16" s="4" t="inlineStr">
+      <c r="J16" s="13" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="K16" s="4" t="inlineStr">
         <is>
           <t>Súper Crítica</t>
         </is>
@@ -1368,22 +1429,27 @@
           <t>Las Vegas (and vicinity), NV, US</t>
         </is>
       </c>
-      <c r="E17" s="12" t="n">
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F17" s="12" t="n">
         <v>345</v>
       </c>
-      <c r="F17" s="12" t="n">
+      <c r="G17" s="12" t="n">
         <v>72</v>
       </c>
-      <c r="G17" s="12" t="n">
+      <c r="H17" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="H17" s="13" t="n">
+      <c r="I17" s="13" t="n">
         <v>0.208695652173913</v>
       </c>
-      <c r="I17" s="13" t="n">
+      <c r="J17" s="13" t="n">
         <v>0.002898550724637681</v>
       </c>
-      <c r="J17" s="4" t="inlineStr">
+      <c r="K17" s="4" t="inlineStr">
         <is>
           <t>Súper Crítica</t>
         </is>
@@ -1408,22 +1474,27 @@
           <t>Riviera Nayarit</t>
         </is>
       </c>
-      <c r="E18" s="12" t="n">
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F18" s="12" t="n">
         <v>459</v>
       </c>
-      <c r="F18" s="12" t="n">
+      <c r="G18" s="12" t="n">
         <v>98</v>
       </c>
-      <c r="G18" s="12" t="n">
+      <c r="H18" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="H18" s="13" t="n">
+      <c r="I18" s="13" t="n">
         <v>0.2135076252723312</v>
       </c>
-      <c r="I18" s="13" t="n">
+      <c r="J18" s="13" t="n">
         <v>0.008714596949891068</v>
       </c>
-      <c r="J18" s="4" t="inlineStr">
+      <c r="K18" s="4" t="inlineStr">
         <is>
           <t>Súper Crítica</t>
         </is>
@@ -1448,22 +1519,27 @@
           <t>Central Black Forest Area</t>
         </is>
       </c>
-      <c r="E19" s="12" t="n">
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F19" s="12" t="n">
         <v>48</v>
       </c>
-      <c r="F19" s="12" t="n">
+      <c r="G19" s="12" t="n">
         <v>12</v>
       </c>
-      <c r="G19" s="12" t="n">
+      <c r="H19" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="H19" s="13" t="n">
+      <c r="I19" s="13" t="n">
         <v>0.25</v>
       </c>
-      <c r="I19" s="13" t="n">
+      <c r="J19" s="13" t="n">
         <v>0.02083333333333333</v>
       </c>
-      <c r="J19" s="4" t="inlineStr">
+      <c r="K19" s="4" t="inlineStr">
         <is>
           <t>Súper Crítica</t>
         </is>
@@ -1488,22 +1564,27 @@
           <t>San Antonio</t>
         </is>
       </c>
-      <c r="E20" s="12" t="n">
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F20" s="12" t="n">
         <v>287</v>
       </c>
-      <c r="F20" s="12" t="n">
+      <c r="G20" s="12" t="n">
         <v>82</v>
       </c>
-      <c r="G20" s="12" t="n">
+      <c r="H20" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="H20" s="13" t="n">
+      <c r="I20" s="13" t="n">
         <v>0.2857142857142857</v>
       </c>
-      <c r="I20" s="13" t="n">
+      <c r="J20" s="13" t="n">
         <v>0.01045296167247387</v>
       </c>
-      <c r="J20" s="4" t="inlineStr">
+      <c r="K20" s="4" t="inlineStr">
         <is>
           <t>Súper Crítica</t>
         </is>
@@ -1528,22 +1609,27 @@
           <t>Guadalajara</t>
         </is>
       </c>
-      <c r="E21" s="12" t="n">
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F21" s="12" t="n">
         <v>58</v>
       </c>
-      <c r="F21" s="12" t="n">
+      <c r="G21" s="12" t="n">
         <v>17</v>
       </c>
-      <c r="G21" s="12" t="n">
+      <c r="H21" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="H21" s="13" t="n">
+      <c r="I21" s="13" t="n">
         <v>0.293103448275862</v>
       </c>
-      <c r="I21" s="13" t="n">
+      <c r="J21" s="13" t="n">
         <v>0.01724137931034483</v>
       </c>
-      <c r="J21" s="4" t="inlineStr">
+      <c r="K21" s="4" t="inlineStr">
         <is>
           <t>Súper Crítica</t>
         </is>
@@ -1568,22 +1654,27 @@
           <t>Cancún</t>
         </is>
       </c>
-      <c r="E22" s="12" t="n">
+      <c r="E22" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F22" s="12" t="n">
         <v>49</v>
       </c>
-      <c r="F22" s="12" t="n">
+      <c r="G22" s="12" t="n">
         <v>15</v>
       </c>
-      <c r="G22" s="12" t="n">
+      <c r="H22" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="H22" s="13" t="n">
+      <c r="I22" s="13" t="n">
         <v>0.3061224489795918</v>
       </c>
-      <c r="I22" s="13" t="n">
+      <c r="J22" s="13" t="n">
         <v>0.02040816326530612</v>
       </c>
-      <c r="J22" s="4" t="inlineStr">
+      <c r="K22" s="4" t="inlineStr">
         <is>
           <t>Súper Crítica</t>
         </is>
@@ -1608,22 +1699,27 @@
           <t>Riviera Nayarit</t>
         </is>
       </c>
-      <c r="E23" s="12" t="n">
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F23" s="12" t="n">
         <v>1676</v>
       </c>
-      <c r="F23" s="12" t="n">
+      <c r="G23" s="12" t="n">
         <v>551</v>
       </c>
-      <c r="G23" s="12" t="n">
+      <c r="H23" s="12" t="n">
         <v>29</v>
       </c>
-      <c r="H23" s="13" t="n">
+      <c r="I23" s="13" t="n">
         <v>0.3287589498806683</v>
       </c>
-      <c r="I23" s="13" t="n">
+      <c r="J23" s="13" t="n">
         <v>0.01730310262529833</v>
       </c>
-      <c r="J23" s="4" t="inlineStr">
+      <c r="K23" s="4" t="inlineStr">
         <is>
           <t>Súper Crítica</t>
         </is>
@@ -1648,22 +1744,27 @@
           <t>Ixtapa / Zihuatanejo</t>
         </is>
       </c>
-      <c r="E24" s="12" t="n">
+      <c r="E24" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F24" s="12" t="n">
         <v>479</v>
       </c>
-      <c r="F24" s="12" t="n">
+      <c r="G24" s="12" t="n">
         <v>159</v>
       </c>
-      <c r="G24" s="12" t="n">
+      <c r="H24" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="H24" s="13" t="n">
+      <c r="I24" s="13" t="n">
         <v>0.3319415448851775</v>
       </c>
-      <c r="I24" s="13" t="n">
+      <c r="J24" s="13" t="n">
         <v>0.01252609603340292</v>
       </c>
-      <c r="J24" s="4" t="inlineStr">
+      <c r="K24" s="4" t="inlineStr">
         <is>
           <t>Súper Crítica</t>
         </is>
@@ -1688,22 +1789,27 @@
           <t>Ogden Area</t>
         </is>
       </c>
-      <c r="E25" s="12" t="n">
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F25" s="12" t="n">
         <v>3</v>
-      </c>
-      <c r="F25" s="12" t="n">
-        <v>1</v>
       </c>
       <c r="G25" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="H25" s="13" t="n">
-        <v>0.3333333333333333</v>
+      <c r="H25" s="12" t="n">
+        <v>1</v>
       </c>
       <c r="I25" s="13" t="n">
         <v>0.3333333333333333</v>
       </c>
-      <c r="J25" s="4" t="inlineStr">
+      <c r="J25" s="13" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="K25" s="4" t="inlineStr">
         <is>
           <t>Súper Crítica</t>
         </is>
@@ -1728,22 +1834,27 @@
           <t>Fort Atkinson Area</t>
         </is>
       </c>
-      <c r="E26" s="12" t="n">
+      <c r="E26" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F26" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="F26" s="12" t="n">
+      <c r="G26" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="G26" s="12" t="n">
+      <c r="H26" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="H26" s="13" t="n">
+      <c r="I26" s="13" t="n">
         <v>0.3333333333333333</v>
       </c>
-      <c r="I26" s="13" t="n">
+      <c r="J26" s="13" t="n">
         <v>0.1666666666666667</v>
       </c>
-      <c r="J26" s="4" t="inlineStr">
+      <c r="K26" s="4" t="inlineStr">
         <is>
           <t>Súper Crítica</t>
         </is>
@@ -1768,22 +1879,27 @@
           <t>Austin</t>
         </is>
       </c>
-      <c r="E27" s="12" t="n">
+      <c r="E27" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F27" s="12" t="n">
         <v>11</v>
       </c>
-      <c r="F27" s="12" t="n">
+      <c r="G27" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="G27" s="12" t="n">
+      <c r="H27" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="H27" s="13" t="n">
+      <c r="I27" s="13" t="n">
         <v>0.3636363636363636</v>
       </c>
-      <c r="I27" s="13" t="n">
+      <c r="J27" s="13" t="n">
         <v>0.09090909090909091</v>
       </c>
-      <c r="J27" s="4" t="inlineStr">
+      <c r="K27" s="4" t="inlineStr">
         <is>
           <t>Súper Crítica</t>
         </is>
@@ -1808,22 +1924,27 @@
           <t>Orange County Area</t>
         </is>
       </c>
-      <c r="E28" s="12" t="n">
+      <c r="E28" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F28" s="12" t="n">
         <v>47</v>
       </c>
-      <c r="F28" s="12" t="n">
+      <c r="G28" s="12" t="n">
         <v>18</v>
       </c>
-      <c r="G28" s="12" t="n">
+      <c r="H28" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="H28" s="13" t="n">
+      <c r="I28" s="13" t="n">
         <v>0.3829787234042553</v>
       </c>
-      <c r="I28" s="13" t="n">
+      <c r="J28" s="13" t="n">
         <v>0.0851063829787234</v>
       </c>
-      <c r="J28" s="4" t="inlineStr">
+      <c r="K28" s="4" t="inlineStr">
         <is>
           <t>Súper Crítica</t>
         </is>
@@ -1848,22 +1969,27 @@
           <t>Columbus (and vicinity), OH, US</t>
         </is>
       </c>
-      <c r="E29" s="12" t="n">
+      <c r="E29" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F29" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="F29" s="12" t="n">
+      <c r="G29" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="G29" s="12" t="n">
+      <c r="H29" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="H29" s="13" t="n">
+      <c r="I29" s="13" t="n">
         <v>0.4</v>
       </c>
-      <c r="I29" s="13" t="n">
+      <c r="J29" s="13" t="n">
         <v>0.2</v>
       </c>
-      <c r="J29" s="4" t="inlineStr">
+      <c r="K29" s="4" t="inlineStr">
         <is>
           <t>Súper Crítica</t>
         </is>
@@ -1888,22 +2014,27 @@
           <t>Medford Area</t>
         </is>
       </c>
-      <c r="E30" s="12" t="n">
+      <c r="E30" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F30" s="12" t="n">
         <v>12</v>
       </c>
-      <c r="F30" s="12" t="n">
+      <c r="G30" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="G30" s="12" t="n">
+      <c r="H30" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="H30" s="13" t="n">
+      <c r="I30" s="13" t="n">
         <v>0.4166666666666667</v>
       </c>
-      <c r="I30" s="13" t="n">
+      <c r="J30" s="13" t="n">
         <v>0.08333333333333333</v>
       </c>
-      <c r="J30" s="4" t="inlineStr">
+      <c r="K30" s="4" t="inlineStr">
         <is>
           <t>Súper Crítica</t>
         </is>
@@ -1928,22 +2059,27 @@
           <t>Chihuahua</t>
         </is>
       </c>
-      <c r="E31" s="12" t="n">
+      <c r="E31" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F31" s="12" t="n">
         <v>12</v>
       </c>
-      <c r="F31" s="12" t="n">
+      <c r="G31" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="G31" s="12" t="n">
+      <c r="H31" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="H31" s="13" t="n">
+      <c r="I31" s="13" t="n">
         <v>0.4166666666666667</v>
       </c>
-      <c r="I31" s="13" t="n">
+      <c r="J31" s="13" t="n">
         <v>0.1666666666666667</v>
       </c>
-      <c r="J31" s="4" t="inlineStr">
+      <c r="K31" s="4" t="inlineStr">
         <is>
           <t>Súper Crítica</t>
         </is>
@@ -1968,22 +2104,27 @@
           <t>Melbourne Area</t>
         </is>
       </c>
-      <c r="E32" s="12" t="n">
+      <c r="E32" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F32" s="12" t="n">
         <v>422</v>
       </c>
-      <c r="F32" s="12" t="n">
+      <c r="G32" s="12" t="n">
         <v>177</v>
       </c>
-      <c r="G32" s="12" t="n">
+      <c r="H32" s="12" t="n">
         <v>15</v>
       </c>
-      <c r="H32" s="13" t="n">
+      <c r="I32" s="13" t="n">
         <v>0.4194312796208531</v>
       </c>
-      <c r="I32" s="13" t="n">
+      <c r="J32" s="13" t="n">
         <v>0.03554502369668246</v>
       </c>
-      <c r="J32" s="4" t="inlineStr">
+      <c r="K32" s="4" t="inlineStr">
         <is>
           <t>Súper Crítica</t>
         </is>
@@ -2008,22 +2149,27 @@
           <t>Mexico City - Central Mexico</t>
         </is>
       </c>
-      <c r="E33" s="12" t="n">
+      <c r="E33" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F33" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="F33" s="12" t="n">
+      <c r="G33" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="G33" s="12" t="n">
+      <c r="H33" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="H33" s="13" t="n">
+      <c r="I33" s="13" t="n">
         <v>0.4285714285714285</v>
       </c>
-      <c r="I33" s="13" t="n">
+      <c r="J33" s="13" t="n">
         <v>0.1428571428571428</v>
       </c>
-      <c r="J33" s="4" t="inlineStr">
+      <c r="K33" s="4" t="inlineStr">
         <is>
           <t>Súper Crítica</t>
         </is>
@@ -2048,22 +2194,27 @@
           <t>Franconia Area</t>
         </is>
       </c>
-      <c r="E34" s="12" t="n">
+      <c r="E34" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F34" s="12" t="n">
         <v>43</v>
       </c>
-      <c r="F34" s="12" t="n">
+      <c r="G34" s="12" t="n">
         <v>19</v>
       </c>
-      <c r="G34" s="12" t="n">
+      <c r="H34" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="H34" s="13" t="n">
+      <c r="I34" s="13" t="n">
         <v>0.4418604651162791</v>
       </c>
-      <c r="I34" s="13" t="n">
+      <c r="J34" s="13" t="n">
         <v>0.02325581395348837</v>
       </c>
-      <c r="J34" s="4" t="inlineStr">
+      <c r="K34" s="4" t="inlineStr">
         <is>
           <t>Súper Crítica</t>
         </is>
@@ -2088,22 +2239,27 @@
           <t>Albany Area</t>
         </is>
       </c>
-      <c r="E35" s="12" t="n">
+      <c r="E35" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F35" s="12" t="n">
         <v>33</v>
       </c>
-      <c r="F35" s="12" t="n">
+      <c r="G35" s="12" t="n">
         <v>15</v>
       </c>
-      <c r="G35" s="12" t="n">
+      <c r="H35" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="H35" s="13" t="n">
+      <c r="I35" s="13" t="n">
         <v>0.4545454545454545</v>
       </c>
-      <c r="I35" s="13" t="n">
+      <c r="J35" s="13" t="n">
         <v>0.0303030303030303</v>
       </c>
-      <c r="J35" s="4" t="inlineStr">
+      <c r="K35" s="4" t="inlineStr">
         <is>
           <t>Súper Crítica</t>
         </is>
@@ -2128,22 +2284,27 @@
           <t>Orlando</t>
         </is>
       </c>
-      <c r="E36" s="12" t="n">
+      <c r="E36" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F36" s="12" t="n">
         <v>22</v>
       </c>
-      <c r="F36" s="12" t="n">
+      <c r="G36" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="G36" s="12" t="n">
+      <c r="H36" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="H36" s="13" t="n">
+      <c r="I36" s="13" t="n">
         <v>0.4545454545454545</v>
       </c>
-      <c r="I36" s="13" t="n">
+      <c r="J36" s="13" t="n">
         <v>0.04545454545454546</v>
       </c>
-      <c r="J36" s="4" t="inlineStr">
+      <c r="K36" s="4" t="inlineStr">
         <is>
           <t>Súper Crítica</t>
         </is>
@@ -2168,22 +2329,27 @@
           <t>Abu Dhabi</t>
         </is>
       </c>
-      <c r="E37" s="12" t="n">
+      <c r="E37" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F37" s="12" t="n">
         <v>28</v>
       </c>
-      <c r="F37" s="12" t="n">
+      <c r="G37" s="12" t="n">
         <v>13</v>
       </c>
-      <c r="G37" s="12" t="n">
+      <c r="H37" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="H37" s="13" t="n">
+      <c r="I37" s="13" t="n">
         <v>0.4642857142857143</v>
       </c>
-      <c r="I37" s="13" t="n">
+      <c r="J37" s="13" t="n">
         <v>0.03571428571428571</v>
       </c>
-      <c r="J37" s="4" t="inlineStr">
+      <c r="K37" s="4" t="inlineStr">
         <is>
           <t>Súper Crítica</t>
         </is>
@@ -2208,22 +2374,27 @@
           <t>Murray Area</t>
         </is>
       </c>
-      <c r="E38" s="12" t="n">
+      <c r="E38" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F38" s="12" t="n">
         <v>33</v>
       </c>
-      <c r="F38" s="12" t="n">
+      <c r="G38" s="12" t="n">
         <v>16</v>
       </c>
-      <c r="G38" s="12" t="n">
+      <c r="H38" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="H38" s="13" t="n">
+      <c r="I38" s="13" t="n">
         <v>0.4848484848484849</v>
       </c>
-      <c r="I38" s="13" t="n">
+      <c r="J38" s="13" t="n">
         <v>0.0303030303030303</v>
       </c>
-      <c r="J38" s="4" t="inlineStr">
+      <c r="K38" s="4" t="inlineStr">
         <is>
           <t>Súper Crítica</t>
         </is>
@@ -2248,22 +2419,27 @@
           <t>Tucson Area</t>
         </is>
       </c>
-      <c r="E39" s="12" t="n">
+      <c r="E39" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F39" s="12" t="n">
         <v>63</v>
       </c>
-      <c r="F39" s="12" t="n">
+      <c r="G39" s="12" t="n">
         <v>31</v>
       </c>
-      <c r="G39" s="12" t="n">
+      <c r="H39" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="H39" s="13" t="n">
+      <c r="I39" s="13" t="n">
         <v>0.492063492063492</v>
       </c>
-      <c r="I39" s="13" t="n">
+      <c r="J39" s="13" t="n">
         <v>0.04761904761904762</v>
       </c>
-      <c r="J39" s="4" t="inlineStr">
+      <c r="K39" s="4" t="inlineStr">
         <is>
           <t>Súper Crítica</t>
         </is>
@@ -2288,22 +2464,27 @@
           <t>Newcastle Area</t>
         </is>
       </c>
-      <c r="E40" s="12" t="n">
+      <c r="E40" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F40" s="12" t="n">
         <v>138</v>
       </c>
-      <c r="F40" s="12" t="n">
+      <c r="G40" s="12" t="n">
         <v>68</v>
       </c>
-      <c r="G40" s="12" t="n">
+      <c r="H40" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="H40" s="13" t="n">
+      <c r="I40" s="13" t="n">
         <v>0.4927536231884058</v>
       </c>
-      <c r="I40" s="13" t="n">
+      <c r="J40" s="13" t="n">
         <v>0.02173913043478261</v>
       </c>
-      <c r="J40" s="4" t="inlineStr">
+      <c r="K40" s="4" t="inlineStr">
         <is>
           <t>Súper Crítica</t>
         </is>
@@ -2328,22 +2509,27 @@
           <t>Cumbria Area</t>
         </is>
       </c>
-      <c r="E41" s="12" t="n">
+      <c r="E41" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F41" s="12" t="n">
         <v>20</v>
       </c>
-      <c r="F41" s="12" t="n">
+      <c r="G41" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="G41" s="12" t="n">
+      <c r="H41" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="H41" s="13" t="n">
+      <c r="I41" s="13" t="n">
         <v>0.5</v>
       </c>
-      <c r="I41" s="13" t="n">
+      <c r="J41" s="13" t="n">
         <v>0.05</v>
       </c>
-      <c r="J41" s="4" t="inlineStr">
+      <c r="K41" s="4" t="inlineStr">
         <is>
           <t>Súper Crítica</t>
         </is>
@@ -2368,22 +2554,27 @@
           <t>Lubbock Area</t>
         </is>
       </c>
-      <c r="E42" s="12" t="n">
+      <c r="E42" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F42" s="12" t="n">
         <v>2</v>
-      </c>
-      <c r="F42" s="12" t="n">
-        <v>1</v>
       </c>
       <c r="G42" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="H42" s="13" t="n">
-        <v>0.5</v>
+      <c r="H42" s="12" t="n">
+        <v>1</v>
       </c>
       <c r="I42" s="13" t="n">
         <v>0.5</v>
       </c>
-      <c r="J42" s="4" t="inlineStr">
+      <c r="J42" s="13" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K42" s="4" t="inlineStr">
         <is>
           <t>Súper Crítica</t>
         </is>
@@ -2408,22 +2599,27 @@
           <t>Cedar Rapids - Iowa City Area</t>
         </is>
       </c>
-      <c r="E43" s="12" t="n">
+      <c r="E43" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F43" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="F43" s="12" t="n">
+      <c r="G43" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="G43" s="12" t="n">
+      <c r="H43" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="H43" s="13" t="n">
+      <c r="I43" s="13" t="n">
         <v>0.5</v>
       </c>
-      <c r="I43" s="13" t="n">
+      <c r="J43" s="13" t="n">
         <v>0.125</v>
       </c>
-      <c r="J43" s="4" t="inlineStr">
+      <c r="K43" s="4" t="inlineStr">
         <is>
           <t>Súper Crítica</t>
         </is>
@@ -2448,22 +2644,27 @@
           <t>Denver (and vicinity), CO, US</t>
         </is>
       </c>
-      <c r="E44" s="12" t="n">
+      <c r="E44" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F44" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="F44" s="12" t="n">
+      <c r="G44" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="G44" s="12" t="n">
+      <c r="H44" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="H44" s="13" t="n">
+      <c r="I44" s="13" t="n">
         <v>0.5</v>
       </c>
-      <c r="I44" s="13" t="n">
+      <c r="J44" s="13" t="n">
         <v>0.125</v>
       </c>
-      <c r="J44" s="4" t="inlineStr">
+      <c r="K44" s="4" t="inlineStr">
         <is>
           <t>Súper Crítica</t>
         </is>
@@ -2488,22 +2689,27 @@
           <t>Nashville (and vicinity), TN, US</t>
         </is>
       </c>
-      <c r="E45" s="12" t="n">
+      <c r="E45" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F45" s="12" t="n">
         <v>2</v>
-      </c>
-      <c r="F45" s="12" t="n">
-        <v>1</v>
       </c>
       <c r="G45" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="H45" s="13" t="n">
-        <v>0.5</v>
+      <c r="H45" s="12" t="n">
+        <v>1</v>
       </c>
       <c r="I45" s="13" t="n">
         <v>0.5</v>
       </c>
-      <c r="J45" s="4" t="inlineStr">
+      <c r="J45" s="13" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K45" s="4" t="inlineStr">
         <is>
           <t>Súper Crítica</t>
         </is>
@@ -2528,22 +2734,27 @@
           <t>Orlando</t>
         </is>
       </c>
-      <c r="E46" s="12" t="n">
+      <c r="E46" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F46" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="F46" s="12" t="n">
+      <c r="G46" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="G46" s="12" t="n">
+      <c r="H46" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="H46" s="13" t="n">
+      <c r="I46" s="13" t="n">
         <v>0.5</v>
       </c>
-      <c r="I46" s="13" t="n">
+      <c r="J46" s="13" t="n">
         <v>0.125</v>
       </c>
-      <c r="J46" s="4" t="inlineStr">
+      <c r="K46" s="4" t="inlineStr">
         <is>
           <t>Súper Crítica</t>
         </is>
@@ -2568,22 +2779,27 @@
           <t>Chennai Area</t>
         </is>
       </c>
-      <c r="E47" s="12" t="n">
+      <c r="E47" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F47" s="12" t="n">
         <v>12</v>
       </c>
-      <c r="F47" s="12" t="n">
+      <c r="G47" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="G47" s="12" t="n">
+      <c r="H47" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="H47" s="13" t="n">
+      <c r="I47" s="13" t="n">
         <v>0.5</v>
       </c>
-      <c r="I47" s="13" t="n">
+      <c r="J47" s="13" t="n">
         <v>0.08333333333333333</v>
       </c>
-      <c r="J47" s="4" t="inlineStr">
+      <c r="K47" s="4" t="inlineStr">
         <is>
           <t>Súper Crítica</t>
         </is>
@@ -2608,22 +2824,27 @@
           <t>Mexico City - Central Mexico</t>
         </is>
       </c>
-      <c r="E48" s="12" t="n">
+      <c r="E48" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F48" s="12" t="n">
         <v>35</v>
       </c>
-      <c r="F48" s="12" t="n">
+      <c r="G48" s="12" t="n">
         <v>18</v>
       </c>
-      <c r="G48" s="12" t="n">
+      <c r="H48" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="H48" s="13" t="n">
+      <c r="I48" s="13" t="n">
         <v>0.5142857142857142</v>
       </c>
-      <c r="I48" s="13" t="n">
+      <c r="J48" s="13" t="n">
         <v>0.1142857142857143</v>
       </c>
-      <c r="J48" s="4" t="inlineStr">
+      <c r="K48" s="4" t="inlineStr">
         <is>
           <t>Súper Crítica</t>
         </is>
@@ -2648,22 +2869,27 @@
           <t>Melbourne Area</t>
         </is>
       </c>
-      <c r="E49" s="12" t="n">
+      <c r="E49" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F49" s="12" t="n">
         <v>190</v>
       </c>
-      <c r="F49" s="12" t="n">
+      <c r="G49" s="12" t="n">
         <v>98</v>
       </c>
-      <c r="G49" s="12" t="n">
+      <c r="H49" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="H49" s="13" t="n">
+      <c r="I49" s="13" t="n">
         <v>0.5157894736842106</v>
       </c>
-      <c r="I49" s="13" t="n">
+      <c r="J49" s="13" t="n">
         <v>0.005263157894736842</v>
       </c>
-      <c r="J49" s="4" t="inlineStr">
+      <c r="K49" s="4" t="inlineStr">
         <is>
           <t>Súper Crítica</t>
         </is>
@@ -2688,22 +2914,27 @@
           <t>Chicago</t>
         </is>
       </c>
-      <c r="E50" s="12" t="n">
+      <c r="E50" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F50" s="12" t="n">
         <v>23</v>
       </c>
-      <c r="F50" s="12" t="n">
+      <c r="G50" s="12" t="n">
         <v>12</v>
       </c>
-      <c r="G50" s="12" t="n">
+      <c r="H50" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="H50" s="13" t="n">
+      <c r="I50" s="13" t="n">
         <v>0.5217391304347826</v>
       </c>
-      <c r="I50" s="13" t="n">
+      <c r="J50" s="13" t="n">
         <v>0.04347826086956522</v>
       </c>
-      <c r="J50" s="4" t="inlineStr">
+      <c r="K50" s="4" t="inlineStr">
         <is>
           <t>Súper Crítica</t>
         </is>
@@ -2728,22 +2959,27 @@
           <t>Manchester Area</t>
         </is>
       </c>
-      <c r="E51" s="12" t="n">
+      <c r="E51" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F51" s="12" t="n">
         <v>21</v>
       </c>
-      <c r="F51" s="12" t="n">
+      <c r="G51" s="12" t="n">
         <v>11</v>
       </c>
-      <c r="G51" s="12" t="n">
+      <c r="H51" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="H51" s="13" t="n">
+      <c r="I51" s="13" t="n">
         <v>0.5238095238095238</v>
       </c>
-      <c r="I51" s="13" t="n">
+      <c r="J51" s="13" t="n">
         <v>0.04761904761904762</v>
       </c>
-      <c r="J51" s="4" t="inlineStr">
+      <c r="K51" s="4" t="inlineStr">
         <is>
           <t>Súper Crítica</t>
         </is>
@@ -2768,22 +3004,27 @@
           <t>San Diego Area</t>
         </is>
       </c>
-      <c r="E52" s="12" t="n">
+      <c r="E52" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F52" s="12" t="n">
         <v>162</v>
       </c>
-      <c r="F52" s="12" t="n">
+      <c r="G52" s="12" t="n">
         <v>85</v>
       </c>
-      <c r="G52" s="12" t="n">
+      <c r="H52" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="H52" s="13" t="n">
+      <c r="I52" s="13" t="n">
         <v>0.5246913580246914</v>
       </c>
-      <c r="I52" s="13" t="n">
+      <c r="J52" s="13" t="n">
         <v>0.01851851851851852</v>
       </c>
-      <c r="J52" s="4" t="inlineStr">
+      <c r="K52" s="4" t="inlineStr">
         <is>
           <t>Súper Crítica</t>
         </is>
@@ -2808,22 +3049,27 @@
           <t>Fort Lauderdale (and vicinity), FL, US</t>
         </is>
       </c>
-      <c r="E53" s="12" t="n">
+      <c r="E53" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F53" s="12" t="n">
         <v>91</v>
       </c>
-      <c r="F53" s="12" t="n">
+      <c r="G53" s="12" t="n">
         <v>48</v>
       </c>
-      <c r="G53" s="12" t="n">
+      <c r="H53" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="H53" s="13" t="n">
+      <c r="I53" s="13" t="n">
         <v>0.5274725274725275</v>
       </c>
-      <c r="I53" s="13" t="n">
+      <c r="J53" s="13" t="n">
         <v>0.01098901098901099</v>
       </c>
-      <c r="J53" s="4" t="inlineStr">
+      <c r="K53" s="4" t="inlineStr">
         <is>
           <t>Súper Crítica</t>
         </is>
@@ -2848,22 +3094,27 @@
           <t>Cancún</t>
         </is>
       </c>
-      <c r="E54" s="12" t="n">
+      <c r="E54" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F54" s="12" t="n">
         <v>427</v>
       </c>
-      <c r="F54" s="12" t="n">
+      <c r="G54" s="12" t="n">
         <v>233</v>
       </c>
-      <c r="G54" s="12" t="n">
+      <c r="H54" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="H54" s="13" t="n">
+      <c r="I54" s="13" t="n">
         <v>0.5456674473067916</v>
       </c>
-      <c r="I54" s="13" t="n">
+      <c r="J54" s="13" t="n">
         <v>0.01873536299765808</v>
       </c>
-      <c r="J54" s="4" t="inlineStr">
+      <c r="K54" s="4" t="inlineStr">
         <is>
           <t>Súper Crítica</t>
         </is>
@@ -2888,22 +3139,27 @@
           <t>Williamsburg Area</t>
         </is>
       </c>
-      <c r="E55" s="12" t="n">
+      <c r="E55" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F55" s="12" t="n">
         <v>73</v>
       </c>
-      <c r="F55" s="12" t="n">
+      <c r="G55" s="12" t="n">
         <v>40</v>
       </c>
-      <c r="G55" s="12" t="n">
+      <c r="H55" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="H55" s="13" t="n">
+      <c r="I55" s="13" t="n">
         <v>0.547945205479452</v>
       </c>
-      <c r="I55" s="13" t="n">
+      <c r="J55" s="13" t="n">
         <v>0.0273972602739726</v>
       </c>
-      <c r="J55" s="4" t="inlineStr">
+      <c r="K55" s="4" t="inlineStr">
         <is>
           <t>Súper Crítica</t>
         </is>
@@ -2920,18 +3176,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I55"/>
+  <dimension ref="A1:J55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
     <col width="50" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
     <col width="35" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="11" customWidth="1" min="6" max="6"/>
-    <col width="21" customWidth="1" min="7" max="7"/>
-    <col width="25" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="21" customWidth="1" min="8" max="8"/>
+    <col width="25" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2951,7 +3208,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 05/05/2026 01:35 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 03:47 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -2978,25 +3235,30 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
+          <t>Channel</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
           <t>CR_Unicos</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="G5" s="3" t="inlineStr">
         <is>
           <t>Bookings</t>
         </is>
       </c>
-      <c r="G5" s="3" t="inlineStr">
+      <c r="H5" s="3" t="inlineStr">
         <is>
           <t>Eficacia</t>
         </is>
       </c>
-      <c r="H5" s="3" t="inlineStr">
+      <c r="I5" s="3" t="inlineStr">
         <is>
           <t>ConvRate</t>
         </is>
       </c>
-      <c r="I5" s="3" t="inlineStr">
+      <c r="J5" s="3" t="inlineStr">
         <is>
           <t>BandaConvRate</t>
         </is>
@@ -3021,19 +3283,24 @@
           <t>New York</t>
         </is>
       </c>
-      <c r="E6" s="12" t="n">
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F6" s="12" t="n">
         <v>8879</v>
       </c>
-      <c r="F6" s="12" t="n">
+      <c r="G6" s="12" t="n">
         <v>42</v>
       </c>
-      <c r="G6" s="13" t="n">
+      <c r="H6" s="13" t="n">
         <v>0.9713931749070841</v>
       </c>
-      <c r="H6" s="13" t="n">
+      <c r="I6" s="13" t="n">
         <v>0.004730262416938844</v>
       </c>
-      <c r="I6" s="7" t="inlineStr">
+      <c r="J6" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -3058,19 +3325,24 @@
           <t>Istanbul Area</t>
         </is>
       </c>
-      <c r="E7" s="12" t="n">
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F7" s="12" t="n">
         <v>6781</v>
       </c>
-      <c r="F7" s="12" t="n">
+      <c r="G7" s="12" t="n">
         <v>14</v>
       </c>
-      <c r="G7" s="13" t="n">
+      <c r="H7" s="13" t="n">
         <v>0.9983778203804748</v>
       </c>
-      <c r="H7" s="13" t="n">
+      <c r="I7" s="13" t="n">
         <v>0.002064592243032001</v>
       </c>
-      <c r="I7" s="7" t="inlineStr">
+      <c r="J7" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -3095,19 +3367,24 @@
           <t>New York</t>
         </is>
       </c>
-      <c r="E8" s="12" t="n">
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F8" s="12" t="n">
         <v>6333</v>
       </c>
-      <c r="F8" s="12" t="n">
+      <c r="G8" s="12" t="n">
         <v>25</v>
       </c>
-      <c r="G8" s="13" t="n">
+      <c r="H8" s="13" t="n">
         <v>0.9883151744828675</v>
       </c>
-      <c r="H8" s="13" t="n">
+      <c r="I8" s="13" t="n">
         <v>0.003947576188220433</v>
       </c>
-      <c r="I8" s="7" t="inlineStr">
+      <c r="J8" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -3132,19 +3409,24 @@
           <t>Las Vegas (and vicinity), NV, US</t>
         </is>
       </c>
-      <c r="E9" s="12" t="n">
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F9" s="12" t="n">
         <v>5744</v>
       </c>
-      <c r="F9" s="12" t="n">
+      <c r="G9" s="12" t="n">
         <v>60</v>
       </c>
-      <c r="G9" s="13" t="n">
+      <c r="H9" s="13" t="n">
         <v>0.9895543175487466</v>
       </c>
-      <c r="H9" s="13" t="n">
+      <c r="I9" s="13" t="n">
         <v>0.01044568245125348</v>
       </c>
-      <c r="I9" s="8" t="inlineStr">
+      <c r="J9" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -3169,19 +3451,24 @@
           <t>Las Vegas (and vicinity), NV, US</t>
         </is>
       </c>
-      <c r="E10" s="12" t="n">
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F10" s="12" t="n">
         <v>4117</v>
       </c>
-      <c r="F10" s="12" t="n">
+      <c r="G10" s="12" t="n">
         <v>29</v>
       </c>
-      <c r="G10" s="13" t="n">
+      <c r="H10" s="13" t="n">
         <v>0.7391304347826086</v>
       </c>
-      <c r="H10" s="13" t="n">
+      <c r="I10" s="13" t="n">
         <v>0.007043964051493806</v>
       </c>
-      <c r="I10" s="7" t="inlineStr">
+      <c r="J10" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -3206,19 +3493,24 @@
           <t>Las Vegas (and vicinity), NV, US</t>
         </is>
       </c>
-      <c r="E11" s="12" t="n">
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F11" s="12" t="n">
         <v>4029</v>
       </c>
-      <c r="F11" s="12" t="n">
+      <c r="G11" s="12" t="n">
         <v>19</v>
       </c>
-      <c r="G11" s="13" t="n">
+      <c r="H11" s="13" t="n">
         <v>0.9893273765202284</v>
       </c>
-      <c r="H11" s="13" t="n">
+      <c r="I11" s="13" t="n">
         <v>0.004715810374782825</v>
       </c>
-      <c r="I11" s="7" t="inlineStr">
+      <c r="J11" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -3243,19 +3535,24 @@
           <t>New Orleans</t>
         </is>
       </c>
-      <c r="E12" s="12" t="n">
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F12" s="12" t="n">
         <v>3776</v>
       </c>
-      <c r="F12" s="12" t="n">
+      <c r="G12" s="12" t="n">
         <v>12</v>
       </c>
-      <c r="G12" s="13" t="n">
+      <c r="H12" s="13" t="n">
         <v>0.9909957627118644</v>
       </c>
-      <c r="H12" s="13" t="n">
+      <c r="I12" s="13" t="n">
         <v>0.003177966101694915</v>
       </c>
-      <c r="I12" s="7" t="inlineStr">
+      <c r="J12" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -3280,19 +3577,24 @@
           <t>New York</t>
         </is>
       </c>
-      <c r="E13" s="12" t="n">
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F13" s="12" t="n">
         <v>3733</v>
       </c>
-      <c r="F13" s="12" t="n">
+      <c r="G13" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="G13" s="13" t="n">
+      <c r="H13" s="13" t="n">
         <v>0.998928475756764</v>
       </c>
-      <c r="H13" s="13" t="n">
+      <c r="I13" s="13" t="n">
         <v>0.002143048486472007</v>
       </c>
-      <c r="I13" s="7" t="inlineStr">
+      <c r="J13" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -3317,19 +3619,24 @@
           <t>Vancouver</t>
         </is>
       </c>
-      <c r="E14" s="12" t="n">
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F14" s="12" t="n">
         <v>3639</v>
       </c>
-      <c r="F14" s="12" t="n">
+      <c r="G14" s="12" t="n">
         <v>35</v>
       </c>
-      <c r="G14" s="13" t="n">
+      <c r="H14" s="13" t="n">
         <v>0.9884583676834295</v>
       </c>
-      <c r="H14" s="13" t="n">
+      <c r="I14" s="13" t="n">
         <v>0.009618026930475405</v>
       </c>
-      <c r="I14" s="8" t="inlineStr">
+      <c r="J14" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -3354,19 +3661,24 @@
           <t>Honolulu Area</t>
         </is>
       </c>
-      <c r="E15" s="12" t="n">
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F15" s="12" t="n">
         <v>3420</v>
       </c>
-      <c r="F15" s="12" t="n">
+      <c r="G15" s="12" t="n">
         <v>19</v>
       </c>
-      <c r="G15" s="13" t="n">
+      <c r="H15" s="13" t="n">
         <v>0.9944444444444445</v>
       </c>
-      <c r="H15" s="13" t="n">
+      <c r="I15" s="13" t="n">
         <v>0.005555555555555556</v>
       </c>
-      <c r="I15" s="7" t="inlineStr">
+      <c r="J15" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -3391,19 +3703,24 @@
           <t>Las Vegas (and vicinity), NV, US</t>
         </is>
       </c>
-      <c r="E16" s="12" t="n">
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F16" s="12" t="n">
         <v>3295</v>
       </c>
-      <c r="F16" s="12" t="n">
+      <c r="G16" s="12" t="n">
         <v>33</v>
       </c>
-      <c r="G16" s="13" t="n">
+      <c r="H16" s="13" t="n">
         <v>0.980576631259484</v>
       </c>
-      <c r="H16" s="13" t="n">
+      <c r="I16" s="13" t="n">
         <v>0.01001517450682853</v>
       </c>
-      <c r="I16" s="8" t="inlineStr">
+      <c r="J16" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -3428,19 +3745,24 @@
           <t>Toronto Area</t>
         </is>
       </c>
-      <c r="E17" s="12" t="n">
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F17" s="12" t="n">
         <v>3116</v>
       </c>
-      <c r="F17" s="12" t="n">
+      <c r="G17" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="G17" s="13" t="n">
+      <c r="H17" s="13" t="n">
         <v>0.9801026957637997</v>
       </c>
-      <c r="H17" s="13" t="n">
+      <c r="I17" s="13" t="n">
         <v>0.0009627727856225931</v>
       </c>
-      <c r="I17" s="7" t="inlineStr">
+      <c r="J17" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -3465,19 +3787,24 @@
           <t>Abu Dhabi</t>
         </is>
       </c>
-      <c r="E18" s="12" t="n">
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F18" s="12" t="n">
         <v>3099</v>
       </c>
-      <c r="F18" s="12" t="n">
+      <c r="G18" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G18" s="13" t="n">
+      <c r="H18" s="13" t="n">
         <v>0.9970958373668926</v>
       </c>
-      <c r="H18" s="13" t="n">
+      <c r="I18" s="13" t="n">
         <v>0.0003226847370119393</v>
       </c>
-      <c r="I18" s="7" t="inlineStr">
+      <c r="J18" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -3502,19 +3829,24 @@
           <t>Chicago</t>
         </is>
       </c>
-      <c r="E19" s="12" t="n">
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F19" s="12" t="n">
         <v>3062</v>
       </c>
-      <c r="F19" s="12" t="n">
+      <c r="G19" s="12" t="n">
         <v>19</v>
       </c>
-      <c r="G19" s="13" t="n">
+      <c r="H19" s="13" t="n">
         <v>0.9647289353363815</v>
       </c>
-      <c r="H19" s="13" t="n">
+      <c r="I19" s="13" t="n">
         <v>0.0062050947093403</v>
       </c>
-      <c r="I19" s="7" t="inlineStr">
+      <c r="J19" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -3539,19 +3871,24 @@
           <t>Seattle Area</t>
         </is>
       </c>
-      <c r="E20" s="12" t="n">
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F20" s="12" t="n">
         <v>2889</v>
       </c>
-      <c r="F20" s="12" t="n">
+      <c r="G20" s="12" t="n">
         <v>31</v>
       </c>
-      <c r="G20" s="13" t="n">
+      <c r="H20" s="13" t="n">
         <v>0.9930771893388716</v>
       </c>
-      <c r="H20" s="13" t="n">
+      <c r="I20" s="13" t="n">
         <v>0.01073035652474905</v>
       </c>
-      <c r="I20" s="8" t="inlineStr">
+      <c r="J20" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -3576,19 +3913,24 @@
           <t>Riviera Maya</t>
         </is>
       </c>
-      <c r="E21" s="12" t="n">
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F21" s="12" t="n">
         <v>2849</v>
       </c>
-      <c r="F21" s="12" t="n">
+      <c r="G21" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="G21" s="13" t="n">
+      <c r="H21" s="13" t="n">
         <v>0.9982449982449982</v>
       </c>
-      <c r="H21" s="13" t="n">
+      <c r="I21" s="13" t="n">
         <v>0.002457002457002457</v>
       </c>
-      <c r="I21" s="7" t="inlineStr">
+      <c r="J21" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -3613,19 +3955,24 @@
           <t>Niagara Falls, Canada</t>
         </is>
       </c>
-      <c r="E22" s="12" t="n">
+      <c r="E22" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F22" s="12" t="n">
         <v>2778</v>
       </c>
-      <c r="F22" s="12" t="n">
+      <c r="G22" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="G22" s="13" t="n">
+      <c r="H22" s="13" t="n">
         <v>0.9946004319654428</v>
       </c>
-      <c r="H22" s="13" t="n">
+      <c r="I22" s="13" t="n">
         <v>0.001799856011519079</v>
       </c>
-      <c r="I22" s="7" t="inlineStr">
+      <c r="J22" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -3650,19 +3997,24 @@
           <t>Anaheim Area</t>
         </is>
       </c>
-      <c r="E23" s="12" t="n">
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F23" s="12" t="n">
         <v>2728</v>
       </c>
-      <c r="F23" s="12" t="n">
+      <c r="G23" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="G23" s="13" t="n">
+      <c r="H23" s="13" t="n">
         <v>0.9948680351906158</v>
       </c>
-      <c r="H23" s="13" t="n">
+      <c r="I23" s="13" t="n">
         <v>0.003665689149560118</v>
       </c>
-      <c r="I23" s="7" t="inlineStr">
+      <c r="J23" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -3687,19 +4039,24 @@
           <t>Chicago</t>
         </is>
       </c>
-      <c r="E24" s="12" t="n">
+      <c r="E24" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F24" s="12" t="n">
         <v>2702</v>
       </c>
-      <c r="F24" s="12" t="n">
+      <c r="G24" s="12" t="n">
         <v>16</v>
       </c>
-      <c r="G24" s="13" t="n">
+      <c r="H24" s="13" t="n">
         <v>0.9803849000740192</v>
       </c>
-      <c r="H24" s="13" t="n">
+      <c r="I24" s="13" t="n">
         <v>0.005921539600296077</v>
       </c>
-      <c r="I24" s="7" t="inlineStr">
+      <c r="J24" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -3724,19 +4081,24 @@
           <t>Puerto Rico</t>
         </is>
       </c>
-      <c r="E25" s="12" t="n">
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F25" s="12" t="n">
         <v>2701</v>
       </c>
-      <c r="F25" s="12" t="n">
+      <c r="G25" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="G25" s="13" t="n">
+      <c r="H25" s="13" t="n">
         <v>0.9914846353202518</v>
       </c>
-      <c r="H25" s="13" t="n">
+      <c r="I25" s="13" t="n">
         <v>0.003702332469455757</v>
       </c>
-      <c r="I25" s="7" t="inlineStr">
+      <c r="J25" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -3761,19 +4123,24 @@
           <t>Paris</t>
         </is>
       </c>
-      <c r="E26" s="12" t="n">
+      <c r="E26" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F26" s="12" t="n">
         <v>2625</v>
       </c>
-      <c r="F26" s="12" t="n">
+      <c r="G26" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="G26" s="13" t="n">
+      <c r="H26" s="13" t="n">
         <v>0.9885714285714285</v>
       </c>
-      <c r="H26" s="13" t="n">
+      <c r="I26" s="13" t="n">
         <v>0.0007619047619047619</v>
       </c>
-      <c r="I26" s="7" t="inlineStr">
+      <c r="J26" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -3798,19 +4165,24 @@
           <t>Las Vegas (and vicinity), NV, US</t>
         </is>
       </c>
-      <c r="E27" s="12" t="n">
+      <c r="E27" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F27" s="12" t="n">
         <v>2565</v>
       </c>
-      <c r="F27" s="12" t="n">
+      <c r="G27" s="12" t="n">
         <v>25</v>
       </c>
-      <c r="G27" s="13" t="n">
+      <c r="H27" s="13" t="n">
         <v>0.989083820662768</v>
       </c>
-      <c r="H27" s="13" t="n">
+      <c r="I27" s="13" t="n">
         <v>0.009746588693957114</v>
       </c>
-      <c r="I27" s="8" t="inlineStr">
+      <c r="J27" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -3835,19 +4207,24 @@
           <t>Londres</t>
         </is>
       </c>
-      <c r="E28" s="12" t="n">
+      <c r="E28" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F28" s="12" t="n">
         <v>2531</v>
       </c>
-      <c r="F28" s="12" t="n">
+      <c r="G28" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="G28" s="13" t="n">
+      <c r="H28" s="13" t="n">
         <v>0.8249703674436981</v>
       </c>
-      <c r="H28" s="13" t="n">
+      <c r="I28" s="13" t="n">
         <v>0.0007902015013828526</v>
       </c>
-      <c r="I28" s="7" t="inlineStr">
+      <c r="J28" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -3872,19 +4249,24 @@
           <t>Vancouver</t>
         </is>
       </c>
-      <c r="E29" s="12" t="n">
+      <c r="E29" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F29" s="12" t="n">
         <v>2510</v>
       </c>
-      <c r="F29" s="12" t="n">
+      <c r="G29" s="12" t="n">
         <v>24</v>
       </c>
-      <c r="G29" s="13" t="n">
+      <c r="H29" s="13" t="n">
         <v>0.9948207171314741</v>
       </c>
-      <c r="H29" s="13" t="n">
+      <c r="I29" s="13" t="n">
         <v>0.009561752988047808</v>
       </c>
-      <c r="I29" s="8" t="inlineStr">
+      <c r="J29" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -3909,19 +4291,24 @@
           <t>New York</t>
         </is>
       </c>
-      <c r="E30" s="12" t="n">
+      <c r="E30" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F30" s="12" t="n">
         <v>2394</v>
       </c>
-      <c r="F30" s="12" t="n">
+      <c r="G30" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="G30" s="13" t="n">
+      <c r="H30" s="13" t="n">
         <v>0.9690893901420217</v>
       </c>
-      <c r="H30" s="13" t="n">
+      <c r="I30" s="13" t="n">
         <v>0.002923976608187134</v>
       </c>
-      <c r="I30" s="7" t="inlineStr">
+      <c r="J30" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -3946,19 +4333,24 @@
           <t>Halifax Area</t>
         </is>
       </c>
-      <c r="E31" s="12" t="n">
+      <c r="E31" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F31" s="12" t="n">
         <v>2264</v>
       </c>
-      <c r="F31" s="12" t="n">
+      <c r="G31" s="12" t="n">
         <v>19</v>
       </c>
-      <c r="G31" s="13" t="n">
+      <c r="H31" s="13" t="n">
         <v>0.9469964664310954</v>
       </c>
-      <c r="H31" s="13" t="n">
+      <c r="I31" s="13" t="n">
         <v>0.008392226148409895</v>
       </c>
-      <c r="I31" s="8" t="inlineStr">
+      <c r="J31" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -3983,19 +4375,24 @@
           <t>New York</t>
         </is>
       </c>
-      <c r="E32" s="12" t="n">
+      <c r="E32" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F32" s="12" t="n">
         <v>2211</v>
       </c>
-      <c r="F32" s="12" t="n">
+      <c r="G32" s="12" t="n">
         <v>21</v>
       </c>
-      <c r="G32" s="13" t="n">
+      <c r="H32" s="13" t="n">
         <v>0.9877883310719131</v>
       </c>
-      <c r="H32" s="13" t="n">
+      <c r="I32" s="13" t="n">
         <v>0.009497964721845319</v>
       </c>
-      <c r="I32" s="8" t="inlineStr">
+      <c r="J32" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -4020,19 +4417,24 @@
           <t>Las Vegas (and vicinity), NV, US</t>
         </is>
       </c>
-      <c r="E33" s="12" t="n">
+      <c r="E33" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F33" s="12" t="n">
         <v>2209</v>
       </c>
-      <c r="F33" s="12" t="n">
+      <c r="G33" s="12" t="n">
         <v>24</v>
       </c>
-      <c r="G33" s="13" t="n">
+      <c r="H33" s="13" t="n">
         <v>0.9859665006790402</v>
       </c>
-      <c r="H33" s="13" t="n">
+      <c r="I33" s="13" t="n">
         <v>0.01086464463558171</v>
       </c>
-      <c r="I33" s="8" t="inlineStr">
+      <c r="J33" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -4057,19 +4459,24 @@
           <t>New York</t>
         </is>
       </c>
-      <c r="E34" s="12" t="n">
+      <c r="E34" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F34" s="12" t="n">
         <v>2098</v>
       </c>
-      <c r="F34" s="12" t="n">
+      <c r="G34" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="G34" s="13" t="n">
+      <c r="H34" s="13" t="n">
         <v>0.8975214489990467</v>
       </c>
-      <c r="H34" s="13" t="n">
+      <c r="I34" s="13" t="n">
         <v>0.001906577693040991</v>
       </c>
-      <c r="I34" s="7" t="inlineStr">
+      <c r="J34" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -4094,19 +4501,24 @@
           <t>New York</t>
         </is>
       </c>
-      <c r="E35" s="12" t="n">
+      <c r="E35" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F35" s="12" t="n">
         <v>2048</v>
       </c>
-      <c r="F35" s="12" t="n">
+      <c r="G35" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="G35" s="13" t="n">
+      <c r="H35" s="13" t="n">
         <v>0.99365234375</v>
       </c>
-      <c r="H35" s="13" t="n">
+      <c r="I35" s="13" t="n">
         <v>0.001953125</v>
       </c>
-      <c r="I35" s="7" t="inlineStr">
+      <c r="J35" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -4131,19 +4543,24 @@
           <t>Puerto Vallarta Area</t>
         </is>
       </c>
-      <c r="E36" s="12" t="n">
+      <c r="E36" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F36" s="12" t="n">
         <v>2041</v>
       </c>
-      <c r="F36" s="12" t="n">
+      <c r="G36" s="12" t="n">
         <v>16</v>
       </c>
-      <c r="G36" s="13" t="n">
+      <c r="H36" s="13" t="n">
         <v>0.9980401763841255</v>
       </c>
-      <c r="H36" s="13" t="n">
+      <c r="I36" s="13" t="n">
         <v>0.007839294463498285</v>
       </c>
-      <c r="I36" s="7" t="inlineStr">
+      <c r="J36" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -4168,19 +4585,24 @@
           <t>New Orleans</t>
         </is>
       </c>
-      <c r="E37" s="12" t="n">
+      <c r="E37" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F37" s="12" t="n">
         <v>2002</v>
       </c>
-      <c r="F37" s="12" t="n">
+      <c r="G37" s="12" t="n">
         <v>17</v>
       </c>
-      <c r="G37" s="13" t="n">
+      <c r="H37" s="13" t="n">
         <v>0.9745254745254746</v>
       </c>
-      <c r="H37" s="13" t="n">
+      <c r="I37" s="13" t="n">
         <v>0.008491508491508492</v>
       </c>
-      <c r="I37" s="8" t="inlineStr">
+      <c r="J37" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -4205,19 +4627,24 @@
           <t>New York</t>
         </is>
       </c>
-      <c r="E38" s="12" t="n">
+      <c r="E38" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F38" s="12" t="n">
         <v>1995</v>
       </c>
-      <c r="F38" s="12" t="n">
+      <c r="G38" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="G38" s="13" t="n">
+      <c r="H38" s="13" t="n">
         <v>0.9739348370927319</v>
       </c>
-      <c r="H38" s="13" t="n">
+      <c r="I38" s="13" t="n">
         <v>0.003508771929824561</v>
       </c>
-      <c r="I38" s="7" t="inlineStr">
+      <c r="J38" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -4242,19 +4669,24 @@
           <t>Las Vegas (and vicinity), NV, US</t>
         </is>
       </c>
-      <c r="E39" s="12" t="n">
+      <c r="E39" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F39" s="12" t="n">
         <v>1967</v>
       </c>
-      <c r="F39" s="12" t="n">
+      <c r="G39" s="12" t="n">
         <v>17</v>
       </c>
-      <c r="G39" s="13" t="n">
+      <c r="H39" s="13" t="n">
         <v>0.9898322318251144</v>
       </c>
-      <c r="H39" s="13" t="n">
+      <c r="I39" s="13" t="n">
         <v>0.00864260294865277</v>
       </c>
-      <c r="I39" s="8" t="inlineStr">
+      <c r="J39" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -4279,19 +4711,24 @@
           <t>New York</t>
         </is>
       </c>
-      <c r="E40" s="12" t="n">
+      <c r="E40" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F40" s="12" t="n">
         <v>1966</v>
       </c>
-      <c r="F40" s="12" t="n">
+      <c r="G40" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="G40" s="13" t="n">
+      <c r="H40" s="13" t="n">
         <v>0.9771108850457783</v>
       </c>
-      <c r="H40" s="13" t="n">
+      <c r="I40" s="13" t="n">
         <v>0.001017293997965412</v>
       </c>
-      <c r="I40" s="7" t="inlineStr">
+      <c r="J40" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -4316,19 +4753,24 @@
           <t>Toronto Area</t>
         </is>
       </c>
-      <c r="E41" s="12" t="n">
+      <c r="E41" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F41" s="12" t="n">
         <v>1875</v>
       </c>
-      <c r="F41" s="12" t="n">
+      <c r="G41" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="G41" s="13" t="n">
+      <c r="H41" s="13" t="n">
         <v>0.9861333333333333</v>
       </c>
-      <c r="H41" s="13" t="n">
+      <c r="I41" s="13" t="n">
         <v>0.002133333333333333</v>
       </c>
-      <c r="I41" s="7" t="inlineStr">
+      <c r="J41" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -4353,19 +4795,24 @@
           <t>Londres</t>
         </is>
       </c>
-      <c r="E42" s="12" t="n">
+      <c r="E42" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F42" s="12" t="n">
         <v>1873</v>
       </c>
-      <c r="F42" s="12" t="n">
+      <c r="G42" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="G42" s="13" t="n">
+      <c r="H42" s="13" t="n">
         <v>0.9679658302189001</v>
       </c>
-      <c r="H42" s="13" t="n">
+      <c r="I42" s="13" t="n">
         <v>0.002669514148424987</v>
       </c>
-      <c r="I42" s="7" t="inlineStr">
+      <c r="J42" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -4390,19 +4837,24 @@
           <t>Toronto Area</t>
         </is>
       </c>
-      <c r="E43" s="12" t="n">
+      <c r="E43" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F43" s="12" t="n">
         <v>1853</v>
       </c>
-      <c r="F43" s="12" t="n">
+      <c r="G43" s="12" t="n">
         <v>24</v>
       </c>
-      <c r="G43" s="13" t="n">
+      <c r="H43" s="13" t="n">
         <v>0.9767943874797625</v>
       </c>
-      <c r="H43" s="13" t="n">
+      <c r="I43" s="13" t="n">
         <v>0.01295196977873718</v>
       </c>
-      <c r="I43" s="8" t="inlineStr">
+      <c r="J43" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -4427,19 +4879,24 @@
           <t>French Riviera Area</t>
         </is>
       </c>
-      <c r="E44" s="12" t="n">
+      <c r="E44" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F44" s="12" t="n">
         <v>1743</v>
       </c>
-      <c r="F44" s="12" t="n">
+      <c r="G44" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="G44" s="13" t="n">
+      <c r="H44" s="13" t="n">
         <v>0.9845094664371773</v>
       </c>
-      <c r="H44" s="13" t="n">
+      <c r="I44" s="13" t="n">
         <v>0.001147446930579461</v>
       </c>
-      <c r="I44" s="7" t="inlineStr">
+      <c r="J44" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -4464,19 +4921,24 @@
           <t>Madrid</t>
         </is>
       </c>
-      <c r="E45" s="12" t="n">
+      <c r="E45" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F45" s="12" t="n">
         <v>1700</v>
       </c>
-      <c r="F45" s="12" t="n">
+      <c r="G45" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="G45" s="13" t="n">
+      <c r="H45" s="13" t="n">
         <v>0.971764705882353</v>
       </c>
-      <c r="H45" s="13" t="n">
+      <c r="I45" s="13" t="n">
         <v>0.005882352941176471</v>
       </c>
-      <c r="I45" s="7" t="inlineStr">
+      <c r="J45" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -4501,19 +4963,24 @@
           <t>Miami Area</t>
         </is>
       </c>
-      <c r="E46" s="12" t="n">
+      <c r="E46" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F46" s="12" t="n">
         <v>1688</v>
       </c>
-      <c r="F46" s="12" t="n">
+      <c r="G46" s="12" t="n">
         <v>19</v>
       </c>
-      <c r="G46" s="13" t="n">
+      <c r="H46" s="13" t="n">
         <v>0.9792654028436019</v>
       </c>
-      <c r="H46" s="13" t="n">
+      <c r="I46" s="13" t="n">
         <v>0.01125592417061611</v>
       </c>
-      <c r="I46" s="8" t="inlineStr">
+      <c r="J46" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -4538,19 +5005,24 @@
           <t>Greenville Area</t>
         </is>
       </c>
-      <c r="E47" s="12" t="n">
+      <c r="E47" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F47" s="12" t="n">
         <v>1687</v>
       </c>
-      <c r="F47" s="12" t="n">
+      <c r="G47" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="G47" s="13" t="n">
+      <c r="H47" s="13" t="n">
         <v>0.99407231772377</v>
       </c>
-      <c r="H47" s="13" t="n">
+      <c r="I47" s="13" t="n">
         <v>0.001778304682868998</v>
       </c>
-      <c r="I47" s="7" t="inlineStr">
+      <c r="J47" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -4575,19 +5047,24 @@
           <t>Miami Area</t>
         </is>
       </c>
-      <c r="E48" s="12" t="n">
+      <c r="E48" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F48" s="12" t="n">
         <v>1663</v>
       </c>
-      <c r="F48" s="12" t="n">
+      <c r="G48" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="G48" s="13" t="n">
+      <c r="H48" s="13" t="n">
         <v>0.9446782922429344</v>
       </c>
-      <c r="H48" s="13" t="n">
+      <c r="I48" s="13" t="n">
         <v>0.003006614552014432</v>
       </c>
-      <c r="I48" s="7" t="inlineStr">
+      <c r="J48" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -4612,19 +5089,24 @@
           <t>Seattle Area</t>
         </is>
       </c>
-      <c r="E49" s="12" t="n">
+      <c r="E49" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F49" s="12" t="n">
         <v>1645</v>
       </c>
-      <c r="F49" s="12" t="n">
+      <c r="G49" s="12" t="n">
         <v>22</v>
       </c>
-      <c r="G49" s="13" t="n">
+      <c r="H49" s="13" t="n">
         <v>0.9951367781155015</v>
       </c>
-      <c r="H49" s="13" t="n">
+      <c r="I49" s="13" t="n">
         <v>0.01337386018237082</v>
       </c>
-      <c r="I49" s="8" t="inlineStr">
+      <c r="J49" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -4649,19 +5131,24 @@
           <t>Punta Cana</t>
         </is>
       </c>
-      <c r="E50" s="12" t="n">
+      <c r="E50" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F50" s="12" t="n">
         <v>1629</v>
       </c>
-      <c r="F50" s="12" t="n">
+      <c r="G50" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="G50" s="13" t="n">
+      <c r="H50" s="13" t="n">
         <v>0.9987722529158993</v>
       </c>
-      <c r="H50" s="13" t="n">
+      <c r="I50" s="13" t="n">
         <v>0.005524861878453038</v>
       </c>
-      <c r="I50" s="7" t="inlineStr">
+      <c r="J50" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -4686,19 +5173,24 @@
           <t>Riviera Nayarit</t>
         </is>
       </c>
-      <c r="E51" s="12" t="n">
+      <c r="E51" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F51" s="12" t="n">
         <v>1601</v>
       </c>
-      <c r="F51" s="12" t="n">
+      <c r="G51" s="12" t="n">
         <v>18</v>
       </c>
-      <c r="G51" s="13" t="n">
+      <c r="H51" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="H51" s="13" t="n">
+      <c r="I51" s="13" t="n">
         <v>0.01124297314178638</v>
       </c>
-      <c r="I51" s="8" t="inlineStr">
+      <c r="J51" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -4723,19 +5215,24 @@
           <t>El Cairo Area</t>
         </is>
       </c>
-      <c r="E52" s="12" t="n">
+      <c r="E52" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F52" s="12" t="n">
         <v>1556</v>
       </c>
-      <c r="F52" s="12" t="n">
+      <c r="G52" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="G52" s="13" t="n">
+      <c r="H52" s="13" t="n">
         <v>0.9839331619537275</v>
       </c>
-      <c r="H52" s="13" t="n">
+      <c r="I52" s="13" t="n">
         <v>0.001285347043701799</v>
       </c>
-      <c r="I52" s="7" t="inlineStr">
+      <c r="J52" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -4760,19 +5257,24 @@
           <t>Amsterdam</t>
         </is>
       </c>
-      <c r="E53" s="12" t="n">
+      <c r="E53" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F53" s="12" t="n">
         <v>1552</v>
       </c>
-      <c r="F53" s="12" t="n">
+      <c r="G53" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G53" s="13" t="n">
+      <c r="H53" s="13" t="n">
         <v>0.9877577319587629</v>
       </c>
-      <c r="H53" s="13" t="n">
+      <c r="I53" s="13" t="n">
         <v>0.0006443298969072165</v>
       </c>
-      <c r="I53" s="7" t="inlineStr">
+      <c r="J53" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -4797,19 +5299,24 @@
           <t>Londres</t>
         </is>
       </c>
-      <c r="E54" s="12" t="n">
+      <c r="E54" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F54" s="12" t="n">
         <v>1533</v>
       </c>
-      <c r="F54" s="12" t="n">
+      <c r="G54" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="G54" s="13" t="n">
+      <c r="H54" s="13" t="n">
         <v>0.9980430528375733</v>
       </c>
-      <c r="H54" s="13" t="n">
+      <c r="I54" s="13" t="n">
         <v>0.001304631441617743</v>
       </c>
-      <c r="I54" s="7" t="inlineStr">
+      <c r="J54" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -4834,19 +5341,24 @@
           <t>New York</t>
         </is>
       </c>
-      <c r="E55" s="12" t="n">
+      <c r="E55" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F55" s="12" t="n">
         <v>1532</v>
       </c>
-      <c r="F55" s="12" t="n">
+      <c r="G55" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="G55" s="13" t="n">
+      <c r="H55" s="13" t="n">
         <v>0.9895561357702349</v>
       </c>
-      <c r="H55" s="13" t="n">
+      <c r="I55" s="13" t="n">
         <v>0.00391644908616188</v>
       </c>
-      <c r="I55" s="7" t="inlineStr">
+      <c r="J55" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -4863,18 +5375,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I55"/>
+  <dimension ref="A1:J55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
     <col width="50" customWidth="1" min="2" max="2"/>
     <col width="30" customWidth="1" min="3" max="3"/>
     <col width="37" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="11" customWidth="1" min="7" max="7"/>
-    <col width="22" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4894,7 +5407,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 05/05/2026 01:35 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 03:47 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -4921,25 +5434,30 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
+          <t>Channel</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
           <t>CR_Unicos</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="G5" s="3" t="inlineStr">
         <is>
           <t>Success</t>
         </is>
       </c>
-      <c r="G5" s="3" t="inlineStr">
+      <c r="H5" s="3" t="inlineStr">
         <is>
           <t>Bookings</t>
         </is>
       </c>
-      <c r="H5" s="3" t="inlineStr">
+      <c r="I5" s="3" t="inlineStr">
         <is>
           <t>Eficacia</t>
         </is>
       </c>
-      <c r="I5" s="3" t="inlineStr">
+      <c r="J5" s="3" t="inlineStr">
         <is>
           <t>BandaEficacia</t>
         </is>
@@ -4964,19 +5482,24 @@
           <t>Abu Dhabi</t>
         </is>
       </c>
-      <c r="E6" s="12" t="n">
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F6" s="12" t="n">
         <v>4411</v>
       </c>
-      <c r="F6" s="12" t="n">
+      <c r="G6" s="12" t="n">
         <v>4408</v>
       </c>
-      <c r="G6" s="12" t="n">
+      <c r="H6" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H6" s="13" t="n">
+      <c r="I6" s="13" t="n">
         <v>0.9993198821128996</v>
       </c>
-      <c r="I6" s="10" t="inlineStr">
+      <c r="J6" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -5001,19 +5524,24 @@
           <t>El Cairo Area</t>
         </is>
       </c>
-      <c r="E7" s="12" t="n">
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F7" s="12" t="n">
         <v>3304</v>
       </c>
-      <c r="F7" s="12" t="n">
+      <c r="G7" s="12" t="n">
         <v>3189</v>
       </c>
-      <c r="G7" s="12" t="n">
+      <c r="H7" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H7" s="13" t="n">
+      <c r="I7" s="13" t="n">
         <v>0.9651937046004843</v>
       </c>
-      <c r="I7" s="9" t="inlineStr">
+      <c r="J7" s="9" t="inlineStr">
         <is>
           <t>Aceptable</t>
         </is>
@@ -5038,19 +5566,24 @@
           <t>El Cairo Area</t>
         </is>
       </c>
-      <c r="E8" s="12" t="n">
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F8" s="12" t="n">
         <v>2923</v>
       </c>
-      <c r="F8" s="12" t="n">
+      <c r="G8" s="12" t="n">
         <v>2891</v>
       </c>
-      <c r="G8" s="12" t="n">
+      <c r="H8" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H8" s="13" t="n">
+      <c r="I8" s="13" t="n">
         <v>0.9890523434827232</v>
       </c>
-      <c r="I8" s="10" t="inlineStr">
+      <c r="J8" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -5075,19 +5608,24 @@
           <t>Las Vegas (and vicinity), NV, US</t>
         </is>
       </c>
-      <c r="E9" s="12" t="n">
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F9" s="12" t="n">
         <v>2861</v>
       </c>
-      <c r="F9" s="12" t="n">
+      <c r="G9" s="12" t="n">
         <v>284</v>
       </c>
-      <c r="G9" s="12" t="n">
+      <c r="H9" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H9" s="13" t="n">
+      <c r="I9" s="13" t="n">
         <v>0.09926599091226844</v>
       </c>
-      <c r="I9" s="4" t="inlineStr">
+      <c r="J9" s="4" t="inlineStr">
         <is>
           <t>Súper Crítica</t>
         </is>
@@ -5112,19 +5650,24 @@
           <t>Las Vegas (and vicinity), NV, US</t>
         </is>
       </c>
-      <c r="E10" s="12" t="n">
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F10" s="12" t="n">
         <v>2637</v>
       </c>
-      <c r="F10" s="12" t="n">
+      <c r="G10" s="12" t="n">
         <v>480</v>
       </c>
-      <c r="G10" s="12" t="n">
+      <c r="H10" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H10" s="13" t="n">
+      <c r="I10" s="13" t="n">
         <v>0.1820250284414107</v>
       </c>
-      <c r="I10" s="4" t="inlineStr">
+      <c r="J10" s="4" t="inlineStr">
         <is>
           <t>Súper Crítica</t>
         </is>
@@ -5149,19 +5692,24 @@
           <t>Dubai Area</t>
         </is>
       </c>
-      <c r="E11" s="12" t="n">
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F11" s="12" t="n">
         <v>2424</v>
       </c>
-      <c r="F11" s="12" t="n">
+      <c r="G11" s="12" t="n">
         <v>2100</v>
       </c>
-      <c r="G11" s="12" t="n">
+      <c r="H11" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H11" s="13" t="n">
+      <c r="I11" s="13" t="n">
         <v>0.8663366336633663</v>
       </c>
-      <c r="I11" s="8" t="inlineStr">
+      <c r="J11" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -5186,19 +5734,24 @@
           <t>Istanbul Area</t>
         </is>
       </c>
-      <c r="E12" s="12" t="n">
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F12" s="12" t="n">
         <v>2022</v>
       </c>
-      <c r="F12" s="12" t="n">
+      <c r="G12" s="12" t="n">
         <v>2003</v>
       </c>
-      <c r="G12" s="12" t="n">
+      <c r="H12" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H12" s="13" t="n">
+      <c r="I12" s="13" t="n">
         <v>0.9906033630069239</v>
       </c>
-      <c r="I12" s="10" t="inlineStr">
+      <c r="J12" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -5223,19 +5776,24 @@
           <t>El Cairo Area</t>
         </is>
       </c>
-      <c r="E13" s="12" t="n">
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F13" s="12" t="n">
         <v>1937</v>
       </c>
-      <c r="F13" s="12" t="n">
+      <c r="G13" s="12" t="n">
         <v>1930</v>
       </c>
-      <c r="G13" s="12" t="n">
+      <c r="H13" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H13" s="13" t="n">
+      <c r="I13" s="13" t="n">
         <v>0.996386164171399</v>
       </c>
-      <c r="I13" s="10" t="inlineStr">
+      <c r="J13" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -5260,19 +5818,24 @@
           <t>Amsterdam</t>
         </is>
       </c>
-      <c r="E14" s="12" t="n">
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F14" s="12" t="n">
         <v>1709</v>
       </c>
-      <c r="F14" s="12" t="n">
+      <c r="G14" s="12" t="n">
         <v>1661</v>
       </c>
-      <c r="G14" s="12" t="n">
+      <c r="H14" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H14" s="13" t="n">
+      <c r="I14" s="13" t="n">
         <v>0.9719133996489175</v>
       </c>
-      <c r="I14" s="10" t="inlineStr">
+      <c r="J14" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -5297,19 +5860,24 @@
           <t>Paris</t>
         </is>
       </c>
-      <c r="E15" s="12" t="n">
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F15" s="12" t="n">
         <v>1566</v>
       </c>
-      <c r="F15" s="12" t="n">
+      <c r="G15" s="12" t="n">
         <v>1546</v>
       </c>
-      <c r="G15" s="12" t="n">
+      <c r="H15" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H15" s="13" t="n">
+      <c r="I15" s="13" t="n">
         <v>0.9872286079182631</v>
       </c>
-      <c r="I15" s="10" t="inlineStr">
+      <c r="J15" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -5334,19 +5902,24 @@
           <t>New York</t>
         </is>
       </c>
-      <c r="E16" s="12" t="n">
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F16" s="12" t="n">
         <v>1414</v>
       </c>
-      <c r="F16" s="12" t="n">
+      <c r="G16" s="12" t="n">
         <v>1355</v>
       </c>
-      <c r="G16" s="12" t="n">
+      <c r="H16" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H16" s="13" t="n">
+      <c r="I16" s="13" t="n">
         <v>0.9582743988684582</v>
       </c>
-      <c r="I16" s="9" t="inlineStr">
+      <c r="J16" s="9" t="inlineStr">
         <is>
           <t>Aceptable</t>
         </is>
@@ -5371,19 +5944,24 @@
           <t>Sharm el Sheikh Area</t>
         </is>
       </c>
-      <c r="E17" s="12" t="n">
-        <v>1359</v>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
       </c>
       <c r="F17" s="12" t="n">
         <v>1359</v>
       </c>
       <c r="G17" s="12" t="n">
+        <v>1359</v>
+      </c>
+      <c r="H17" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H17" s="13" t="n">
+      <c r="I17" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="I17" s="10" t="inlineStr">
+      <c r="J17" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -5408,19 +5986,24 @@
           <t>SinClasificar</t>
         </is>
       </c>
-      <c r="E18" s="12" t="n">
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F18" s="12" t="n">
         <v>1356</v>
       </c>
-      <c r="F18" s="12" t="n">
+      <c r="G18" s="12" t="n">
         <v>1052</v>
       </c>
-      <c r="G18" s="12" t="n">
+      <c r="H18" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H18" s="13" t="n">
+      <c r="I18" s="13" t="n">
         <v>0.775811209439528</v>
       </c>
-      <c r="I18" s="7" t="inlineStr">
+      <c r="J18" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -5445,19 +6028,24 @@
           <t>Adjara Area</t>
         </is>
       </c>
-      <c r="E19" s="12" t="n">
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F19" s="12" t="n">
         <v>1350</v>
       </c>
-      <c r="F19" s="12" t="n">
+      <c r="G19" s="12" t="n">
         <v>1301</v>
       </c>
-      <c r="G19" s="12" t="n">
+      <c r="H19" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H19" s="13" t="n">
+      <c r="I19" s="13" t="n">
         <v>0.9637037037037037</v>
       </c>
-      <c r="I19" s="9" t="inlineStr">
+      <c r="J19" s="9" t="inlineStr">
         <is>
           <t>Aceptable</t>
         </is>
@@ -5482,19 +6070,24 @@
           <t>New York</t>
         </is>
       </c>
-      <c r="E20" s="12" t="n">
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F20" s="12" t="n">
         <v>1337</v>
       </c>
-      <c r="F20" s="12" t="n">
+      <c r="G20" s="12" t="n">
         <v>1315</v>
       </c>
-      <c r="G20" s="12" t="n">
+      <c r="H20" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H20" s="13" t="n">
+      <c r="I20" s="13" t="n">
         <v>0.9835452505609573</v>
       </c>
-      <c r="I20" s="10" t="inlineStr">
+      <c r="J20" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -5519,19 +6112,24 @@
           <t>Paris</t>
         </is>
       </c>
-      <c r="E21" s="12" t="n">
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F21" s="12" t="n">
         <v>1264</v>
       </c>
-      <c r="F21" s="12" t="n">
+      <c r="G21" s="12" t="n">
         <v>1254</v>
       </c>
-      <c r="G21" s="12" t="n">
+      <c r="H21" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H21" s="13" t="n">
+      <c r="I21" s="13" t="n">
         <v>0.9920886075949367</v>
       </c>
-      <c r="I21" s="10" t="inlineStr">
+      <c r="J21" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -5556,19 +6154,24 @@
           <t>New York</t>
         </is>
       </c>
-      <c r="E22" s="12" t="n">
-        <v>1218</v>
+      <c r="E22" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
       </c>
       <c r="F22" s="12" t="n">
         <v>1218</v>
       </c>
       <c r="G22" s="12" t="n">
+        <v>1218</v>
+      </c>
+      <c r="H22" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H22" s="13" t="n">
+      <c r="I22" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="I22" s="10" t="inlineStr">
+      <c r="J22" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -5593,19 +6196,24 @@
           <t>Istanbul Area</t>
         </is>
       </c>
-      <c r="E23" s="12" t="n">
-        <v>1193</v>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
       </c>
       <c r="F23" s="12" t="n">
         <v>1193</v>
       </c>
       <c r="G23" s="12" t="n">
+        <v>1193</v>
+      </c>
+      <c r="H23" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H23" s="13" t="n">
+      <c r="I23" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="I23" s="10" t="inlineStr">
+      <c r="J23" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -5630,19 +6238,24 @@
           <t>Istanbul Area</t>
         </is>
       </c>
-      <c r="E24" s="12" t="n">
+      <c r="E24" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F24" s="12" t="n">
         <v>1182</v>
       </c>
-      <c r="F24" s="12" t="n">
+      <c r="G24" s="12" t="n">
         <v>1176</v>
       </c>
-      <c r="G24" s="12" t="n">
+      <c r="H24" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H24" s="13" t="n">
+      <c r="I24" s="13" t="n">
         <v>0.9949238578680203</v>
       </c>
-      <c r="I24" s="10" t="inlineStr">
+      <c r="J24" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -5667,19 +6280,24 @@
           <t>Ras Al Khaimah Area</t>
         </is>
       </c>
-      <c r="E25" s="12" t="n">
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F25" s="12" t="n">
         <v>1178</v>
       </c>
-      <c r="F25" s="12" t="n">
+      <c r="G25" s="12" t="n">
         <v>1085</v>
       </c>
-      <c r="G25" s="12" t="n">
+      <c r="H25" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H25" s="13" t="n">
+      <c r="I25" s="13" t="n">
         <v>0.9210526315789473</v>
       </c>
-      <c r="I25" s="8" t="inlineStr">
+      <c r="J25" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -5704,19 +6322,24 @@
           <t>Miami Area</t>
         </is>
       </c>
-      <c r="E26" s="12" t="n">
+      <c r="E26" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F26" s="12" t="n">
         <v>1141</v>
       </c>
-      <c r="F26" s="12" t="n">
+      <c r="G26" s="12" t="n">
         <v>1099</v>
       </c>
-      <c r="G26" s="12" t="n">
+      <c r="H26" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H26" s="13" t="n">
+      <c r="I26" s="13" t="n">
         <v>0.9631901840490797</v>
       </c>
-      <c r="I26" s="9" t="inlineStr">
+      <c r="J26" s="9" t="inlineStr">
         <is>
           <t>Aceptable</t>
         </is>
@@ -5741,19 +6364,24 @@
           <t>Cancún</t>
         </is>
       </c>
-      <c r="E27" s="12" t="n">
+      <c r="E27" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F27" s="12" t="n">
         <v>1111</v>
-      </c>
-      <c r="F27" s="12" t="n">
-        <v>0</v>
       </c>
       <c r="G27" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H27" s="13" t="n">
+      <c r="H27" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="I27" s="4" t="inlineStr">
+      <c r="I27" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" s="4" t="inlineStr">
         <is>
           <t>Súper Crítica</t>
         </is>
@@ -5778,19 +6406,24 @@
           <t>Jeddah Area</t>
         </is>
       </c>
-      <c r="E28" s="12" t="n">
+      <c r="E28" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F28" s="12" t="n">
         <v>1086</v>
       </c>
-      <c r="F28" s="12" t="n">
+      <c r="G28" s="12" t="n">
         <v>1063</v>
       </c>
-      <c r="G28" s="12" t="n">
+      <c r="H28" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H28" s="13" t="n">
+      <c r="I28" s="13" t="n">
         <v>0.9788213627992634</v>
       </c>
-      <c r="I28" s="10" t="inlineStr">
+      <c r="J28" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -5815,19 +6448,24 @@
           <t>El Cairo Area</t>
         </is>
       </c>
-      <c r="E29" s="12" t="n">
+      <c r="E29" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F29" s="12" t="n">
         <v>1064</v>
       </c>
-      <c r="F29" s="12" t="n">
+      <c r="G29" s="12" t="n">
         <v>1062</v>
       </c>
-      <c r="G29" s="12" t="n">
+      <c r="H29" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H29" s="13" t="n">
+      <c r="I29" s="13" t="n">
         <v>0.9981203007518797</v>
       </c>
-      <c r="I29" s="10" t="inlineStr">
+      <c r="J29" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -5852,19 +6490,24 @@
           <t>New York</t>
         </is>
       </c>
-      <c r="E30" s="12" t="n">
+      <c r="E30" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F30" s="12" t="n">
         <v>1058</v>
       </c>
-      <c r="F30" s="12" t="n">
+      <c r="G30" s="12" t="n">
         <v>1043</v>
       </c>
-      <c r="G30" s="12" t="n">
+      <c r="H30" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H30" s="13" t="n">
+      <c r="I30" s="13" t="n">
         <v>0.9858223062381852</v>
       </c>
-      <c r="I30" s="10" t="inlineStr">
+      <c r="J30" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -5889,19 +6532,24 @@
           <t>Berlin Area</t>
         </is>
       </c>
-      <c r="E31" s="12" t="n">
+      <c r="E31" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F31" s="12" t="n">
         <v>1007</v>
       </c>
-      <c r="F31" s="12" t="n">
+      <c r="G31" s="12" t="n">
         <v>918</v>
       </c>
-      <c r="G31" s="12" t="n">
+      <c r="H31" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H31" s="13" t="n">
+      <c r="I31" s="13" t="n">
         <v>0.9116186693147964</v>
       </c>
-      <c r="I31" s="8" t="inlineStr">
+      <c r="J31" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -5926,19 +6574,24 @@
           <t>Tbilisi Area</t>
         </is>
       </c>
-      <c r="E32" s="12" t="n">
-        <v>995</v>
+      <c r="E32" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
       </c>
       <c r="F32" s="12" t="n">
         <v>995</v>
       </c>
       <c r="G32" s="12" t="n">
+        <v>995</v>
+      </c>
+      <c r="H32" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H32" s="13" t="n">
+      <c r="I32" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="I32" s="10" t="inlineStr">
+      <c r="J32" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -5963,19 +6616,24 @@
           <t>Ras Al Khaimah Area</t>
         </is>
       </c>
-      <c r="E33" s="12" t="n">
+      <c r="E33" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F33" s="12" t="n">
         <v>992</v>
       </c>
-      <c r="F33" s="12" t="n">
+      <c r="G33" s="12" t="n">
         <v>978</v>
       </c>
-      <c r="G33" s="12" t="n">
+      <c r="H33" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H33" s="13" t="n">
+      <c r="I33" s="13" t="n">
         <v>0.9858870967741935</v>
       </c>
-      <c r="I33" s="10" t="inlineStr">
+      <c r="J33" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -6000,19 +6658,24 @@
           <t>Dubai Area</t>
         </is>
       </c>
-      <c r="E34" s="12" t="n">
+      <c r="E34" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F34" s="12" t="n">
         <v>985</v>
       </c>
-      <c r="F34" s="12" t="n">
+      <c r="G34" s="12" t="n">
         <v>846</v>
       </c>
-      <c r="G34" s="12" t="n">
+      <c r="H34" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H34" s="13" t="n">
+      <c r="I34" s="13" t="n">
         <v>0.8588832487309644</v>
       </c>
-      <c r="I34" s="8" t="inlineStr">
+      <c r="J34" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -6037,19 +6700,24 @@
           <t>Londres</t>
         </is>
       </c>
-      <c r="E35" s="12" t="n">
+      <c r="E35" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F35" s="12" t="n">
         <v>959</v>
       </c>
-      <c r="F35" s="12" t="n">
+      <c r="G35" s="12" t="n">
         <v>956</v>
       </c>
-      <c r="G35" s="12" t="n">
+      <c r="H35" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H35" s="13" t="n">
+      <c r="I35" s="13" t="n">
         <v>0.9968717413972888</v>
       </c>
-      <c r="I35" s="10" t="inlineStr">
+      <c r="J35" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -6074,19 +6742,24 @@
           <t>Atlanta Area</t>
         </is>
       </c>
-      <c r="E36" s="12" t="n">
+      <c r="E36" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F36" s="12" t="n">
         <v>952</v>
       </c>
-      <c r="F36" s="12" t="n">
+      <c r="G36" s="12" t="n">
         <v>921</v>
       </c>
-      <c r="G36" s="12" t="n">
+      <c r="H36" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H36" s="13" t="n">
+      <c r="I36" s="13" t="n">
         <v>0.967436974789916</v>
       </c>
-      <c r="I36" s="9" t="inlineStr">
+      <c r="J36" s="9" t="inlineStr">
         <is>
           <t>Aceptable</t>
         </is>
@@ -6111,19 +6784,24 @@
           <t>Dubai Area</t>
         </is>
       </c>
-      <c r="E37" s="12" t="n">
+      <c r="E37" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F37" s="12" t="n">
         <v>929</v>
       </c>
-      <c r="F37" s="12" t="n">
+      <c r="G37" s="12" t="n">
         <v>842</v>
       </c>
-      <c r="G37" s="12" t="n">
+      <c r="H37" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H37" s="13" t="n">
+      <c r="I37" s="13" t="n">
         <v>0.9063509149623251</v>
       </c>
-      <c r="I37" s="8" t="inlineStr">
+      <c r="J37" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -6148,19 +6826,24 @@
           <t>Los Angeles (and vicinity), CA, US</t>
         </is>
       </c>
-      <c r="E38" s="12" t="n">
+      <c r="E38" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F38" s="12" t="n">
         <v>921</v>
       </c>
-      <c r="F38" s="12" t="n">
+      <c r="G38" s="12" t="n">
         <v>905</v>
       </c>
-      <c r="G38" s="12" t="n">
+      <c r="H38" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H38" s="13" t="n">
+      <c r="I38" s="13" t="n">
         <v>0.9826275787187839</v>
       </c>
-      <c r="I38" s="10" t="inlineStr">
+      <c r="J38" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -6185,19 +6868,24 @@
           <t>Orlando</t>
         </is>
       </c>
-      <c r="E39" s="12" t="n">
+      <c r="E39" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F39" s="12" t="n">
         <v>899</v>
       </c>
-      <c r="F39" s="12" t="n">
+      <c r="G39" s="12" t="n">
         <v>897</v>
       </c>
-      <c r="G39" s="12" t="n">
+      <c r="H39" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H39" s="13" t="n">
+      <c r="I39" s="13" t="n">
         <v>0.9977753058954394</v>
       </c>
-      <c r="I39" s="10" t="inlineStr">
+      <c r="J39" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -6222,19 +6910,24 @@
           <t>New York</t>
         </is>
       </c>
-      <c r="E40" s="12" t="n">
-        <v>869</v>
+      <c r="E40" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
       </c>
       <c r="F40" s="12" t="n">
         <v>869</v>
       </c>
       <c r="G40" s="12" t="n">
+        <v>869</v>
+      </c>
+      <c r="H40" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H40" s="13" t="n">
+      <c r="I40" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="I40" s="10" t="inlineStr">
+      <c r="J40" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -6259,19 +6952,24 @@
           <t>Amsterdam</t>
         </is>
       </c>
-      <c r="E41" s="12" t="n">
+      <c r="E41" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F41" s="12" t="n">
         <v>845</v>
       </c>
-      <c r="F41" s="12" t="n">
+      <c r="G41" s="12" t="n">
         <v>830</v>
       </c>
-      <c r="G41" s="12" t="n">
+      <c r="H41" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H41" s="13" t="n">
+      <c r="I41" s="13" t="n">
         <v>0.9822485207100592</v>
       </c>
-      <c r="I41" s="10" t="inlineStr">
+      <c r="J41" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -6296,19 +6994,24 @@
           <t>New York</t>
         </is>
       </c>
-      <c r="E42" s="12" t="n">
+      <c r="E42" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F42" s="12" t="n">
         <v>841</v>
       </c>
-      <c r="F42" s="12" t="n">
+      <c r="G42" s="12" t="n">
         <v>711</v>
       </c>
-      <c r="G42" s="12" t="n">
+      <c r="H42" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H42" s="13" t="n">
+      <c r="I42" s="13" t="n">
         <v>0.845422116527943</v>
       </c>
-      <c r="I42" s="7" t="inlineStr">
+      <c r="J42" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -6333,19 +7036,24 @@
           <t>Vienna Area</t>
         </is>
       </c>
-      <c r="E43" s="12" t="n">
+      <c r="E43" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F43" s="12" t="n">
         <v>829</v>
       </c>
-      <c r="F43" s="12" t="n">
+      <c r="G43" s="12" t="n">
         <v>827</v>
       </c>
-      <c r="G43" s="12" t="n">
+      <c r="H43" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H43" s="13" t="n">
+      <c r="I43" s="13" t="n">
         <v>0.9975874547647768</v>
       </c>
-      <c r="I43" s="10" t="inlineStr">
+      <c r="J43" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -6370,19 +7078,24 @@
           <t>Los Angeles (and vicinity), CA, US</t>
         </is>
       </c>
-      <c r="E44" s="12" t="n">
+      <c r="E44" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F44" s="12" t="n">
         <v>809</v>
       </c>
-      <c r="F44" s="12" t="n">
+      <c r="G44" s="12" t="n">
         <v>448</v>
       </c>
-      <c r="G44" s="12" t="n">
+      <c r="H44" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H44" s="13" t="n">
+      <c r="I44" s="13" t="n">
         <v>0.553770086526576</v>
       </c>
-      <c r="I44" s="4" t="inlineStr">
+      <c r="J44" s="4" t="inlineStr">
         <is>
           <t>Súper Crítica</t>
         </is>
@@ -6407,19 +7120,24 @@
           <t>Veneto Area</t>
         </is>
       </c>
-      <c r="E45" s="12" t="n">
+      <c r="E45" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F45" s="12" t="n">
         <v>803</v>
       </c>
-      <c r="F45" s="12" t="n">
+      <c r="G45" s="12" t="n">
         <v>499</v>
       </c>
-      <c r="G45" s="12" t="n">
+      <c r="H45" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H45" s="13" t="n">
+      <c r="I45" s="13" t="n">
         <v>0.6214196762141968</v>
       </c>
-      <c r="I45" s="7" t="inlineStr">
+      <c r="J45" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -6444,19 +7162,24 @@
           <t>Cancún</t>
         </is>
       </c>
-      <c r="E46" s="12" t="n">
-        <v>725</v>
+      <c r="E46" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
       </c>
       <c r="F46" s="12" t="n">
         <v>725</v>
       </c>
       <c r="G46" s="12" t="n">
+        <v>725</v>
+      </c>
+      <c r="H46" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H46" s="13" t="n">
+      <c r="I46" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="I46" s="10" t="inlineStr">
+      <c r="J46" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -6481,19 +7204,24 @@
           <t>New York</t>
         </is>
       </c>
-      <c r="E47" s="12" t="n">
-        <v>713</v>
+      <c r="E47" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
       </c>
       <c r="F47" s="12" t="n">
         <v>713</v>
       </c>
       <c r="G47" s="12" t="n">
+        <v>713</v>
+      </c>
+      <c r="H47" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H47" s="13" t="n">
+      <c r="I47" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="I47" s="10" t="inlineStr">
+      <c r="J47" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -6518,19 +7246,24 @@
           <t>El Cairo Area</t>
         </is>
       </c>
-      <c r="E48" s="12" t="n">
+      <c r="E48" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F48" s="12" t="n">
         <v>706</v>
       </c>
-      <c r="F48" s="12" t="n">
+      <c r="G48" s="12" t="n">
         <v>685</v>
       </c>
-      <c r="G48" s="12" t="n">
+      <c r="H48" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H48" s="13" t="n">
+      <c r="I48" s="13" t="n">
         <v>0.9702549575070821</v>
       </c>
-      <c r="I48" s="10" t="inlineStr">
+      <c r="J48" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -6555,19 +7288,24 @@
           <t>Dubai Area</t>
         </is>
       </c>
-      <c r="E49" s="12" t="n">
-        <v>691</v>
+      <c r="E49" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
       </c>
       <c r="F49" s="12" t="n">
         <v>691</v>
       </c>
       <c r="G49" s="12" t="n">
+        <v>691</v>
+      </c>
+      <c r="H49" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H49" s="13" t="n">
+      <c r="I49" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="I49" s="10" t="inlineStr">
+      <c r="J49" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -6592,19 +7330,24 @@
           <t>Bali Area</t>
         </is>
       </c>
-      <c r="E50" s="12" t="n">
+      <c r="E50" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F50" s="12" t="n">
         <v>679</v>
       </c>
-      <c r="F50" s="12" t="n">
+      <c r="G50" s="12" t="n">
         <v>678</v>
       </c>
-      <c r="G50" s="12" t="n">
+      <c r="H50" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H50" s="13" t="n">
+      <c r="I50" s="13" t="n">
         <v>0.9985272459499264</v>
       </c>
-      <c r="I50" s="10" t="inlineStr">
+      <c r="J50" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -6629,19 +7372,24 @@
           <t>Key Largo Area</t>
         </is>
       </c>
-      <c r="E51" s="12" t="n">
+      <c r="E51" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F51" s="12" t="n">
         <v>677</v>
       </c>
-      <c r="F51" s="12" t="n">
+      <c r="G51" s="12" t="n">
         <v>522</v>
       </c>
-      <c r="G51" s="12" t="n">
+      <c r="H51" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H51" s="13" t="n">
+      <c r="I51" s="13" t="n">
         <v>0.7710487444608567</v>
       </c>
-      <c r="I51" s="7" t="inlineStr">
+      <c r="J51" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -6666,19 +7414,24 @@
           <t>New York</t>
         </is>
       </c>
-      <c r="E52" s="12" t="n">
+      <c r="E52" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F52" s="12" t="n">
         <v>674</v>
       </c>
-      <c r="F52" s="12" t="n">
+      <c r="G52" s="12" t="n">
         <v>552</v>
       </c>
-      <c r="G52" s="12" t="n">
+      <c r="H52" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H52" s="13" t="n">
+      <c r="I52" s="13" t="n">
         <v>0.8189910979228486</v>
       </c>
-      <c r="I52" s="7" t="inlineStr">
+      <c r="J52" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -6703,19 +7456,24 @@
           <t>Paphos Area</t>
         </is>
       </c>
-      <c r="E53" s="12" t="n">
+      <c r="E53" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F53" s="12" t="n">
         <v>673</v>
       </c>
-      <c r="F53" s="12" t="n">
+      <c r="G53" s="12" t="n">
         <v>667</v>
       </c>
-      <c r="G53" s="12" t="n">
+      <c r="H53" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H53" s="13" t="n">
+      <c r="I53" s="13" t="n">
         <v>0.9910846953937593</v>
       </c>
-      <c r="I53" s="10" t="inlineStr">
+      <c r="J53" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -6740,19 +7498,24 @@
           <t>Cancún</t>
         </is>
       </c>
-      <c r="E54" s="12" t="n">
+      <c r="E54" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F54" s="12" t="n">
         <v>648</v>
       </c>
-      <c r="F54" s="12" t="n">
+      <c r="G54" s="12" t="n">
         <v>600</v>
       </c>
-      <c r="G54" s="12" t="n">
+      <c r="H54" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H54" s="13" t="n">
+      <c r="I54" s="13" t="n">
         <v>0.9259259259259259</v>
       </c>
-      <c r="I54" s="8" t="inlineStr">
+      <c r="J54" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -6777,19 +7540,24 @@
           <t>Daytona Beach Area</t>
         </is>
       </c>
-      <c r="E55" s="12" t="n">
+      <c r="E55" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F55" s="12" t="n">
         <v>644</v>
       </c>
-      <c r="F55" s="12" t="n">
+      <c r="G55" s="12" t="n">
         <v>641</v>
       </c>
-      <c r="G55" s="12" t="n">
+      <c r="H55" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H55" s="13" t="n">
+      <c r="I55" s="13" t="n">
         <v>0.9953416149068323</v>
       </c>
-      <c r="I55" s="10" t="inlineStr">
+      <c r="J55" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -6837,7 +7605,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 05/05/2026 01:35 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 03:47 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -8680,7 +9448,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 05/05/2026 01:35 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 03:47 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -10523,7 +11291,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 05/05/2026 01:35 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 03:47 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -10935,18 +11703,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I55"/>
+  <dimension ref="A1:J55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
     <col width="50" customWidth="1" min="2" max="2"/>
     <col width="17" customWidth="1" min="3" max="3"/>
     <col width="41" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="11" customWidth="1" min="6" max="6"/>
-    <col width="21" customWidth="1" min="7" max="7"/>
-    <col width="25" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="21" customWidth="1" min="8" max="8"/>
+    <col width="25" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -10966,7 +11735,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 05/05/2026 01:35 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 03:47 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -10993,25 +11762,30 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
+          <t>Channel</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
           <t>CR_Unicos</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="G5" s="3" t="inlineStr">
         <is>
           <t>Bookings</t>
         </is>
       </c>
-      <c r="G5" s="3" t="inlineStr">
+      <c r="H5" s="3" t="inlineStr">
         <is>
           <t>Eficacia</t>
         </is>
       </c>
-      <c r="H5" s="3" t="inlineStr">
+      <c r="I5" s="3" t="inlineStr">
         <is>
           <t>ConvRate</t>
         </is>
       </c>
-      <c r="I5" s="3" t="inlineStr">
+      <c r="J5" s="3" t="inlineStr">
         <is>
           <t>BandaConvRate</t>
         </is>
@@ -11036,19 +11810,24 @@
           <t>Seattle Area</t>
         </is>
       </c>
-      <c r="E6" s="12" t="n">
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F6" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="F6" s="12" t="n">
+      <c r="G6" s="12" t="n">
         <v>1</v>
-      </c>
-      <c r="G6" s="13" t="n">
-        <v>0</v>
       </c>
       <c r="H6" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="I6" s="7" t="inlineStr">
+      <c r="I6" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -11073,19 +11852,24 @@
           <t>Hearst Area</t>
         </is>
       </c>
-      <c r="E7" s="12" t="n">
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F7" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="F7" s="12" t="n">
+      <c r="G7" s="12" t="n">
         <v>1</v>
-      </c>
-      <c r="G7" s="13" t="n">
-        <v>0</v>
       </c>
       <c r="H7" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="I7" s="7" t="inlineStr">
+      <c r="I7" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -11110,19 +11894,24 @@
           <t>Chiapas</t>
         </is>
       </c>
-      <c r="E8" s="12" t="n">
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F8" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="F8" s="12" t="n">
+      <c r="G8" s="12" t="n">
         <v>1</v>
-      </c>
-      <c r="G8" s="13" t="n">
-        <v>0</v>
       </c>
       <c r="H8" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="I8" s="7" t="inlineStr">
+      <c r="I8" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -11147,19 +11936,24 @@
           <t>Puebla</t>
         </is>
       </c>
-      <c r="E9" s="12" t="n">
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F9" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="F9" s="12" t="n">
+      <c r="G9" s="12" t="n">
         <v>1</v>
-      </c>
-      <c r="G9" s="13" t="n">
-        <v>0</v>
       </c>
       <c r="H9" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="I9" s="7" t="inlineStr">
+      <c r="I9" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -11184,19 +11978,24 @@
           <t>Abu Dhabi</t>
         </is>
       </c>
-      <c r="E10" s="12" t="n">
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F10" s="12" t="n">
         <v>3099</v>
       </c>
-      <c r="F10" s="12" t="n">
+      <c r="G10" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G10" s="13" t="n">
+      <c r="H10" s="13" t="n">
         <v>0.9970958373668926</v>
       </c>
-      <c r="H10" s="13" t="n">
+      <c r="I10" s="13" t="n">
         <v>0.0003226847370119393</v>
       </c>
-      <c r="I10" s="7" t="inlineStr">
+      <c r="J10" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -11221,19 +12020,24 @@
           <t>Amsterdam</t>
         </is>
       </c>
-      <c r="E11" s="12" t="n">
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F11" s="12" t="n">
         <v>1552</v>
       </c>
-      <c r="F11" s="12" t="n">
+      <c r="G11" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G11" s="13" t="n">
+      <c r="H11" s="13" t="n">
         <v>0.9877577319587629</v>
       </c>
-      <c r="H11" s="13" t="n">
+      <c r="I11" s="13" t="n">
         <v>0.0006443298969072165</v>
       </c>
-      <c r="I11" s="7" t="inlineStr">
+      <c r="J11" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -11258,19 +12062,24 @@
           <t>Ras Al Khaimah Area</t>
         </is>
       </c>
-      <c r="E12" s="12" t="n">
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F12" s="12" t="n">
         <v>1503</v>
       </c>
-      <c r="F12" s="12" t="n">
+      <c r="G12" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G12" s="13" t="n">
+      <c r="H12" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="H12" s="13" t="n">
+      <c r="I12" s="13" t="n">
         <v>0.0006653359946773121</v>
       </c>
-      <c r="I12" s="7" t="inlineStr">
+      <c r="J12" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -11295,19 +12104,24 @@
           <t>Vancouver</t>
         </is>
       </c>
-      <c r="E13" s="12" t="n">
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F13" s="12" t="n">
         <v>1464</v>
       </c>
-      <c r="F13" s="12" t="n">
+      <c r="G13" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G13" s="13" t="n">
+      <c r="H13" s="13" t="n">
         <v>0.9330601092896175</v>
       </c>
-      <c r="H13" s="13" t="n">
+      <c r="I13" s="13" t="n">
         <v>0.0006830601092896175</v>
       </c>
-      <c r="I13" s="7" t="inlineStr">
+      <c r="J13" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -11332,19 +12146,24 @@
           <t>Orlando</t>
         </is>
       </c>
-      <c r="E14" s="12" t="n">
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F14" s="12" t="n">
         <v>1447</v>
       </c>
-      <c r="F14" s="12" t="n">
+      <c r="G14" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G14" s="13" t="n">
+      <c r="H14" s="13" t="n">
         <v>0.9689011748445059</v>
       </c>
-      <c r="H14" s="13" t="n">
+      <c r="I14" s="13" t="n">
         <v>0.000691085003455425</v>
       </c>
-      <c r="I14" s="7" t="inlineStr">
+      <c r="J14" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -11369,19 +12188,24 @@
           <t>Paris</t>
         </is>
       </c>
-      <c r="E15" s="12" t="n">
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F15" s="12" t="n">
         <v>2625</v>
       </c>
-      <c r="F15" s="12" t="n">
+      <c r="G15" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="G15" s="13" t="n">
+      <c r="H15" s="13" t="n">
         <v>0.9885714285714285</v>
       </c>
-      <c r="H15" s="13" t="n">
+      <c r="I15" s="13" t="n">
         <v>0.0007619047619047619</v>
       </c>
-      <c r="I15" s="7" t="inlineStr">
+      <c r="J15" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -11406,19 +12230,24 @@
           <t>Londres</t>
         </is>
       </c>
-      <c r="E16" s="12" t="n">
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F16" s="12" t="n">
         <v>2531</v>
       </c>
-      <c r="F16" s="12" t="n">
+      <c r="G16" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="G16" s="13" t="n">
+      <c r="H16" s="13" t="n">
         <v>0.8249703674436981</v>
       </c>
-      <c r="H16" s="13" t="n">
+      <c r="I16" s="13" t="n">
         <v>0.0007902015013828526</v>
       </c>
-      <c r="I16" s="7" t="inlineStr">
+      <c r="J16" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -11443,19 +12272,24 @@
           <t>Dubai Area</t>
         </is>
       </c>
-      <c r="E17" s="12" t="n">
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F17" s="12" t="n">
         <v>1173</v>
       </c>
-      <c r="F17" s="12" t="n">
+      <c r="G17" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G17" s="13" t="n">
+      <c r="H17" s="13" t="n">
         <v>0.7919863597612958</v>
       </c>
-      <c r="H17" s="13" t="n">
+      <c r="I17" s="13" t="n">
         <v>0.0008525149190110827</v>
       </c>
-      <c r="I17" s="7" t="inlineStr">
+      <c r="J17" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -11480,19 +12314,24 @@
           <t>Dubai Area</t>
         </is>
       </c>
-      <c r="E18" s="12" t="n">
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F18" s="12" t="n">
         <v>1133</v>
       </c>
-      <c r="F18" s="12" t="n">
+      <c r="G18" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G18" s="13" t="n">
+      <c r="H18" s="13" t="n">
         <v>0.9982347749338041</v>
       </c>
-      <c r="H18" s="13" t="n">
+      <c r="I18" s="13" t="n">
         <v>0.00088261253309797</v>
       </c>
-      <c r="I18" s="7" t="inlineStr">
+      <c r="J18" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -11517,19 +12356,24 @@
           <t>Toronto Area</t>
         </is>
       </c>
-      <c r="E19" s="12" t="n">
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F19" s="12" t="n">
         <v>3116</v>
       </c>
-      <c r="F19" s="12" t="n">
+      <c r="G19" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="G19" s="13" t="n">
+      <c r="H19" s="13" t="n">
         <v>0.9801026957637997</v>
       </c>
-      <c r="H19" s="13" t="n">
+      <c r="I19" s="13" t="n">
         <v>0.0009627727856225931</v>
       </c>
-      <c r="I19" s="7" t="inlineStr">
+      <c r="J19" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -11554,19 +12398,24 @@
           <t>Dubai Area</t>
         </is>
       </c>
-      <c r="E20" s="12" t="n">
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F20" s="12" t="n">
         <v>1009</v>
       </c>
-      <c r="F20" s="12" t="n">
+      <c r="G20" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G20" s="13" t="n">
+      <c r="H20" s="13" t="n">
         <v>0.9940535183349851</v>
       </c>
-      <c r="H20" s="13" t="n">
+      <c r="I20" s="13" t="n">
         <v>0.0009910802775024777</v>
       </c>
-      <c r="I20" s="7" t="inlineStr">
+      <c r="J20" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -11591,19 +12440,24 @@
           <t>Fort Lauderdale (and vicinity), FL, US</t>
         </is>
       </c>
-      <c r="E21" s="12" t="n">
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F21" s="12" t="n">
         <v>999</v>
       </c>
-      <c r="F21" s="12" t="n">
+      <c r="G21" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G21" s="13" t="n">
+      <c r="H21" s="13" t="n">
         <v>0.991991991991992</v>
       </c>
-      <c r="H21" s="13" t="n">
+      <c r="I21" s="13" t="n">
         <v>0.001001001001001001</v>
       </c>
-      <c r="I21" s="7" t="inlineStr">
+      <c r="J21" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -11628,19 +12482,24 @@
           <t>Sharjah Area</t>
         </is>
       </c>
-      <c r="E22" s="12" t="n">
+      <c r="E22" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F22" s="12" t="n">
         <v>992</v>
       </c>
-      <c r="F22" s="12" t="n">
+      <c r="G22" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G22" s="13" t="n">
+      <c r="H22" s="13" t="n">
         <v>0.9879032258064516</v>
       </c>
-      <c r="H22" s="13" t="n">
+      <c r="I22" s="13" t="n">
         <v>0.001008064516129032</v>
       </c>
-      <c r="I22" s="7" t="inlineStr">
+      <c r="J22" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -11665,19 +12524,24 @@
           <t>New York</t>
         </is>
       </c>
-      <c r="E23" s="12" t="n">
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F23" s="12" t="n">
         <v>1966</v>
       </c>
-      <c r="F23" s="12" t="n">
+      <c r="G23" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="G23" s="13" t="n">
+      <c r="H23" s="13" t="n">
         <v>0.9771108850457783</v>
       </c>
-      <c r="H23" s="13" t="n">
+      <c r="I23" s="13" t="n">
         <v>0.001017293997965412</v>
       </c>
-      <c r="I23" s="7" t="inlineStr">
+      <c r="J23" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -11702,19 +12566,24 @@
           <t>Múnich Area</t>
         </is>
       </c>
-      <c r="E24" s="12" t="n">
+      <c r="E24" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F24" s="12" t="n">
         <v>953</v>
       </c>
-      <c r="F24" s="12" t="n">
+      <c r="G24" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G24" s="13" t="n">
+      <c r="H24" s="13" t="n">
         <v>0.8426023084994754</v>
       </c>
-      <c r="H24" s="13" t="n">
+      <c r="I24" s="13" t="n">
         <v>0.001049317943336831</v>
       </c>
-      <c r="I24" s="7" t="inlineStr">
+      <c r="J24" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -11739,19 +12608,24 @@
           <t>El Cairo Area</t>
         </is>
       </c>
-      <c r="E25" s="12" t="n">
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F25" s="12" t="n">
         <v>953</v>
       </c>
-      <c r="F25" s="12" t="n">
+      <c r="G25" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G25" s="13" t="n">
+      <c r="H25" s="13" t="n">
         <v>0.7292759706190975</v>
       </c>
-      <c r="H25" s="13" t="n">
+      <c r="I25" s="13" t="n">
         <v>0.001049317943336831</v>
       </c>
-      <c r="I25" s="7" t="inlineStr">
+      <c r="J25" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -11776,19 +12650,24 @@
           <t>Paris</t>
         </is>
       </c>
-      <c r="E26" s="12" t="n">
+      <c r="E26" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F26" s="12" t="n">
         <v>943</v>
       </c>
-      <c r="F26" s="12" t="n">
+      <c r="G26" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G26" s="13" t="n">
+      <c r="H26" s="13" t="n">
         <v>0.8176033934252386</v>
       </c>
-      <c r="H26" s="13" t="n">
+      <c r="I26" s="13" t="n">
         <v>0.001060445387062566</v>
       </c>
-      <c r="I26" s="7" t="inlineStr">
+      <c r="J26" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -11813,19 +12692,24 @@
           <t>Washington, DC Area</t>
         </is>
       </c>
-      <c r="E27" s="12" t="n">
+      <c r="E27" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F27" s="12" t="n">
         <v>880</v>
       </c>
-      <c r="F27" s="12" t="n">
+      <c r="G27" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G27" s="13" t="n">
+      <c r="H27" s="13" t="n">
         <v>0.9761363636363637</v>
       </c>
-      <c r="H27" s="13" t="n">
+      <c r="I27" s="13" t="n">
         <v>0.001136363636363636</v>
       </c>
-      <c r="I27" s="7" t="inlineStr">
+      <c r="J27" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -11850,19 +12734,24 @@
           <t>French Riviera Area</t>
         </is>
       </c>
-      <c r="E28" s="12" t="n">
+      <c r="E28" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F28" s="12" t="n">
         <v>1743</v>
       </c>
-      <c r="F28" s="12" t="n">
+      <c r="G28" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="G28" s="13" t="n">
+      <c r="H28" s="13" t="n">
         <v>0.9845094664371773</v>
       </c>
-      <c r="H28" s="13" t="n">
+      <c r="I28" s="13" t="n">
         <v>0.001147446930579461</v>
       </c>
-      <c r="I28" s="7" t="inlineStr">
+      <c r="J28" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -11887,19 +12776,24 @@
           <t>Pittsburgh Area</t>
         </is>
       </c>
-      <c r="E29" s="12" t="n">
+      <c r="E29" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F29" s="12" t="n">
         <v>852</v>
       </c>
-      <c r="F29" s="12" t="n">
+      <c r="G29" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G29" s="13" t="n">
+      <c r="H29" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="H29" s="13" t="n">
+      <c r="I29" s="13" t="n">
         <v>0.001173708920187793</v>
       </c>
-      <c r="I29" s="7" t="inlineStr">
+      <c r="J29" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -11924,19 +12818,24 @@
           <t>Atenas</t>
         </is>
       </c>
-      <c r="E30" s="12" t="n">
+      <c r="E30" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F30" s="12" t="n">
         <v>818</v>
       </c>
-      <c r="F30" s="12" t="n">
+      <c r="G30" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G30" s="13" t="n">
+      <c r="H30" s="13" t="n">
         <v>0.9559902200488998</v>
       </c>
-      <c r="H30" s="13" t="n">
+      <c r="I30" s="13" t="n">
         <v>0.001222493887530562</v>
       </c>
-      <c r="I30" s="7" t="inlineStr">
+      <c r="J30" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -11961,19 +12860,24 @@
           <t>Chicago</t>
         </is>
       </c>
-      <c r="E31" s="12" t="n">
+      <c r="E31" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F31" s="12" t="n">
         <v>789</v>
       </c>
-      <c r="F31" s="12" t="n">
+      <c r="G31" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G31" s="13" t="n">
+      <c r="H31" s="13" t="n">
         <v>0.7503168567807351</v>
       </c>
-      <c r="H31" s="13" t="n">
+      <c r="I31" s="13" t="n">
         <v>0.001267427122940431</v>
       </c>
-      <c r="I31" s="7" t="inlineStr">
+      <c r="J31" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -11998,19 +12902,24 @@
           <t>El Cairo Area</t>
         </is>
       </c>
-      <c r="E32" s="12" t="n">
+      <c r="E32" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F32" s="12" t="n">
         <v>1556</v>
       </c>
-      <c r="F32" s="12" t="n">
+      <c r="G32" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="G32" s="13" t="n">
+      <c r="H32" s="13" t="n">
         <v>0.9839331619537275</v>
       </c>
-      <c r="H32" s="13" t="n">
+      <c r="I32" s="13" t="n">
         <v>0.001285347043701799</v>
       </c>
-      <c r="I32" s="7" t="inlineStr">
+      <c r="J32" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -12035,19 +12944,24 @@
           <t>Londres</t>
         </is>
       </c>
-      <c r="E33" s="12" t="n">
+      <c r="E33" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F33" s="12" t="n">
         <v>1533</v>
       </c>
-      <c r="F33" s="12" t="n">
+      <c r="G33" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="G33" s="13" t="n">
+      <c r="H33" s="13" t="n">
         <v>0.9980430528375733</v>
       </c>
-      <c r="H33" s="13" t="n">
+      <c r="I33" s="13" t="n">
         <v>0.001304631441617743</v>
       </c>
-      <c r="I33" s="7" t="inlineStr">
+      <c r="J33" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -12072,19 +12986,24 @@
           <t>Istanbul Area</t>
         </is>
       </c>
-      <c r="E34" s="12" t="n">
+      <c r="E34" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F34" s="12" t="n">
         <v>735</v>
       </c>
-      <c r="F34" s="12" t="n">
+      <c r="G34" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G34" s="13" t="n">
+      <c r="H34" s="13" t="n">
         <v>0.9918367346938776</v>
       </c>
-      <c r="H34" s="13" t="n">
+      <c r="I34" s="13" t="n">
         <v>0.001360544217687075</v>
       </c>
-      <c r="I34" s="7" t="inlineStr">
+      <c r="J34" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -12109,19 +13028,24 @@
           <t>Fort Lauderdale (and vicinity), FL, US</t>
         </is>
       </c>
-      <c r="E35" s="12" t="n">
+      <c r="E35" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F35" s="12" t="n">
         <v>713</v>
       </c>
-      <c r="F35" s="12" t="n">
+      <c r="G35" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G35" s="13" t="n">
+      <c r="H35" s="13" t="n">
         <v>0.9537166900420757</v>
       </c>
-      <c r="H35" s="13" t="n">
+      <c r="I35" s="13" t="n">
         <v>0.001402524544179523</v>
       </c>
-      <c r="I35" s="7" t="inlineStr">
+      <c r="J35" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -12146,19 +13070,24 @@
           <t>Tbilisi Area</t>
         </is>
       </c>
-      <c r="E36" s="12" t="n">
+      <c r="E36" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F36" s="12" t="n">
         <v>712</v>
       </c>
-      <c r="F36" s="12" t="n">
+      <c r="G36" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G36" s="13" t="n">
+      <c r="H36" s="13" t="n">
         <v>0.8202247191011236</v>
       </c>
-      <c r="H36" s="13" t="n">
+      <c r="I36" s="13" t="n">
         <v>0.001404494382022472</v>
       </c>
-      <c r="I36" s="7" t="inlineStr">
+      <c r="J36" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -12183,19 +13112,24 @@
           <t>Chicago</t>
         </is>
       </c>
-      <c r="E37" s="12" t="n">
+      <c r="E37" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F37" s="12" t="n">
         <v>712</v>
       </c>
-      <c r="F37" s="12" t="n">
+      <c r="G37" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G37" s="13" t="n">
+      <c r="H37" s="13" t="n">
         <v>0.9705056179775281</v>
       </c>
-      <c r="H37" s="13" t="n">
+      <c r="I37" s="13" t="n">
         <v>0.001404494382022472</v>
       </c>
-      <c r="I37" s="7" t="inlineStr">
+      <c r="J37" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -12220,19 +13154,24 @@
           <t>Cancún</t>
         </is>
       </c>
-      <c r="E38" s="12" t="n">
+      <c r="E38" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F38" s="12" t="n">
         <v>682</v>
       </c>
-      <c r="F38" s="12" t="n">
+      <c r="G38" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G38" s="13" t="n">
+      <c r="H38" s="13" t="n">
         <v>0.9970674486803519</v>
       </c>
-      <c r="H38" s="13" t="n">
+      <c r="I38" s="13" t="n">
         <v>0.001466275659824047</v>
       </c>
-      <c r="I38" s="7" t="inlineStr">
+      <c r="J38" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -12257,19 +13196,24 @@
           <t>Vienna Area</t>
         </is>
       </c>
-      <c r="E39" s="12" t="n">
+      <c r="E39" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F39" s="12" t="n">
         <v>675</v>
       </c>
-      <c r="F39" s="12" t="n">
+      <c r="G39" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G39" s="13" t="n">
+      <c r="H39" s="13" t="n">
         <v>0.9792592592592593</v>
       </c>
-      <c r="H39" s="13" t="n">
+      <c r="I39" s="13" t="n">
         <v>0.001481481481481481</v>
       </c>
-      <c r="I39" s="7" t="inlineStr">
+      <c r="J39" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -12294,19 +13238,24 @@
           <t>Phu Quoc Island Area</t>
         </is>
       </c>
-      <c r="E40" s="12" t="n">
+      <c r="E40" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F40" s="12" t="n">
         <v>673</v>
       </c>
-      <c r="F40" s="12" t="n">
+      <c r="G40" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G40" s="13" t="n">
+      <c r="H40" s="13" t="n">
         <v>0.7622585438335809</v>
       </c>
-      <c r="H40" s="13" t="n">
+      <c r="I40" s="13" t="n">
         <v>0.001485884101040119</v>
       </c>
-      <c r="I40" s="7" t="inlineStr">
+      <c r="J40" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -12331,19 +13280,24 @@
           <t>Boston</t>
         </is>
       </c>
-      <c r="E41" s="12" t="n">
+      <c r="E41" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F41" s="12" t="n">
         <v>669</v>
       </c>
-      <c r="F41" s="12" t="n">
+      <c r="G41" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G41" s="13" t="n">
+      <c r="H41" s="13" t="n">
         <v>0.9955156950672646</v>
       </c>
-      <c r="H41" s="13" t="n">
+      <c r="I41" s="13" t="n">
         <v>0.001494768310911809</v>
       </c>
-      <c r="I41" s="7" t="inlineStr">
+      <c r="J41" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -12368,19 +13322,24 @@
           <t>Paris</t>
         </is>
       </c>
-      <c r="E42" s="12" t="n">
+      <c r="E42" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F42" s="12" t="n">
         <v>1313</v>
       </c>
-      <c r="F42" s="12" t="n">
+      <c r="G42" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="G42" s="13" t="n">
+      <c r="H42" s="13" t="n">
         <v>0.9878141660319878</v>
       </c>
-      <c r="H42" s="13" t="n">
+      <c r="I42" s="13" t="n">
         <v>0.001523229246001523</v>
       </c>
-      <c r="I42" s="7" t="inlineStr">
+      <c r="J42" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -12405,19 +13364,24 @@
           <t>Miami Area</t>
         </is>
       </c>
-      <c r="E43" s="12" t="n">
+      <c r="E43" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F43" s="12" t="n">
         <v>649</v>
       </c>
-      <c r="F43" s="12" t="n">
+      <c r="G43" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G43" s="13" t="n">
+      <c r="H43" s="13" t="n">
         <v>0.9938366718027735</v>
       </c>
-      <c r="H43" s="13" t="n">
+      <c r="I43" s="13" t="n">
         <v>0.001540832049306626</v>
       </c>
-      <c r="I43" s="7" t="inlineStr">
+      <c r="J43" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -12442,19 +13406,24 @@
           <t>Fort Lauderdale (and vicinity), FL, US</t>
         </is>
       </c>
-      <c r="E44" s="12" t="n">
+      <c r="E44" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F44" s="12" t="n">
         <v>636</v>
       </c>
-      <c r="F44" s="12" t="n">
+      <c r="G44" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G44" s="13" t="n">
+      <c r="H44" s="13" t="n">
         <v>0.9921383647798742</v>
       </c>
-      <c r="H44" s="13" t="n">
+      <c r="I44" s="13" t="n">
         <v>0.001572327044025157</v>
       </c>
-      <c r="I44" s="7" t="inlineStr">
+      <c r="J44" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -12479,19 +13448,24 @@
           <t>Bahamas</t>
         </is>
       </c>
-      <c r="E45" s="12" t="n">
+      <c r="E45" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F45" s="12" t="n">
         <v>636</v>
       </c>
-      <c r="F45" s="12" t="n">
+      <c r="G45" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G45" s="13" t="n">
+      <c r="H45" s="13" t="n">
         <v>0.9292452830188679</v>
       </c>
-      <c r="H45" s="13" t="n">
+      <c r="I45" s="13" t="n">
         <v>0.001572327044025157</v>
       </c>
-      <c r="I45" s="7" t="inlineStr">
+      <c r="J45" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -12516,19 +13490,24 @@
           <t>New Orleans</t>
         </is>
       </c>
-      <c r="E46" s="12" t="n">
+      <c r="E46" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F46" s="12" t="n">
         <v>630</v>
       </c>
-      <c r="F46" s="12" t="n">
+      <c r="G46" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G46" s="13" t="n">
+      <c r="H46" s="13" t="n">
         <v>0.9666666666666667</v>
       </c>
-      <c r="H46" s="13" t="n">
+      <c r="I46" s="13" t="n">
         <v>0.001587301587301587</v>
       </c>
-      <c r="I46" s="7" t="inlineStr">
+      <c r="J46" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -12553,19 +13532,24 @@
           <t>Londres</t>
         </is>
       </c>
-      <c r="E47" s="12" t="n">
+      <c r="E47" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F47" s="12" t="n">
         <v>616</v>
       </c>
-      <c r="F47" s="12" t="n">
+      <c r="G47" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G47" s="13" t="n">
+      <c r="H47" s="13" t="n">
         <v>0.9967532467532467</v>
       </c>
-      <c r="H47" s="13" t="n">
+      <c r="I47" s="13" t="n">
         <v>0.001623376623376623</v>
       </c>
-      <c r="I47" s="7" t="inlineStr">
+      <c r="J47" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -12590,19 +13574,24 @@
           <t>Düsseldorf Area</t>
         </is>
       </c>
-      <c r="E48" s="12" t="n">
+      <c r="E48" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F48" s="12" t="n">
         <v>615</v>
       </c>
-      <c r="F48" s="12" t="n">
+      <c r="G48" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G48" s="13" t="n">
+      <c r="H48" s="13" t="n">
         <v>0.8634146341463415</v>
       </c>
-      <c r="H48" s="13" t="n">
+      <c r="I48" s="13" t="n">
         <v>0.001626016260162602</v>
       </c>
-      <c r="I48" s="7" t="inlineStr">
+      <c r="J48" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -12627,19 +13616,24 @@
           <t>Hurghada Area</t>
         </is>
       </c>
-      <c r="E49" s="12" t="n">
+      <c r="E49" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F49" s="12" t="n">
         <v>610</v>
       </c>
-      <c r="F49" s="12" t="n">
+      <c r="G49" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G49" s="13" t="n">
+      <c r="H49" s="13" t="n">
         <v>0.9967213114754099</v>
       </c>
-      <c r="H49" s="13" t="n">
+      <c r="I49" s="13" t="n">
         <v>0.001639344262295082</v>
       </c>
-      <c r="I49" s="7" t="inlineStr">
+      <c r="J49" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -12664,19 +13658,24 @@
           <t>Bucarest Area</t>
         </is>
       </c>
-      <c r="E50" s="12" t="n">
+      <c r="E50" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F50" s="12" t="n">
         <v>586</v>
       </c>
-      <c r="F50" s="12" t="n">
+      <c r="G50" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G50" s="13" t="n">
+      <c r="H50" s="13" t="n">
         <v>0.8020477815699659</v>
       </c>
-      <c r="H50" s="13" t="n">
+      <c r="I50" s="13" t="n">
         <v>0.001706484641638225</v>
       </c>
-      <c r="I50" s="7" t="inlineStr">
+      <c r="J50" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -12701,19 +13700,24 @@
           <t>Miami Area</t>
         </is>
       </c>
-      <c r="E51" s="12" t="n">
+      <c r="E51" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F51" s="12" t="n">
         <v>580</v>
       </c>
-      <c r="F51" s="12" t="n">
+      <c r="G51" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G51" s="13" t="n">
+      <c r="H51" s="13" t="n">
         <v>0.9517241379310345</v>
       </c>
-      <c r="H51" s="13" t="n">
+      <c r="I51" s="13" t="n">
         <v>0.001724137931034483</v>
       </c>
-      <c r="I51" s="7" t="inlineStr">
+      <c r="J51" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -12738,19 +13742,24 @@
           <t>Orlando</t>
         </is>
       </c>
-      <c r="E52" s="12" t="n">
+      <c r="E52" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F52" s="12" t="n">
         <v>568</v>
       </c>
-      <c r="F52" s="12" t="n">
+      <c r="G52" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G52" s="13" t="n">
+      <c r="H52" s="13" t="n">
         <v>0.9911971830985915</v>
       </c>
-      <c r="H52" s="13" t="n">
+      <c r="I52" s="13" t="n">
         <v>0.00176056338028169</v>
       </c>
-      <c r="I52" s="7" t="inlineStr">
+      <c r="J52" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -12775,19 +13784,24 @@
           <t>Puerto Rico</t>
         </is>
       </c>
-      <c r="E53" s="12" t="n">
+      <c r="E53" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F53" s="12" t="n">
         <v>565</v>
       </c>
-      <c r="F53" s="12" t="n">
+      <c r="G53" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G53" s="13" t="n">
+      <c r="H53" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="H53" s="13" t="n">
+      <c r="I53" s="13" t="n">
         <v>0.001769911504424779</v>
       </c>
-      <c r="I53" s="7" t="inlineStr">
+      <c r="J53" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -12812,19 +13826,24 @@
           <t>Greenville Area</t>
         </is>
       </c>
-      <c r="E54" s="12" t="n">
+      <c r="E54" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F54" s="12" t="n">
         <v>1687</v>
       </c>
-      <c r="F54" s="12" t="n">
+      <c r="G54" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="G54" s="13" t="n">
+      <c r="H54" s="13" t="n">
         <v>0.99407231772377</v>
       </c>
-      <c r="H54" s="13" t="n">
+      <c r="I54" s="13" t="n">
         <v>0.001778304682868998</v>
       </c>
-      <c r="I54" s="7" t="inlineStr">
+      <c r="J54" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -12849,19 +13868,24 @@
           <t>Niagara Falls, Canada</t>
         </is>
       </c>
-      <c r="E55" s="12" t="n">
+      <c r="E55" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F55" s="12" t="n">
         <v>2778</v>
       </c>
-      <c r="F55" s="12" t="n">
+      <c r="G55" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="G55" s="13" t="n">
+      <c r="H55" s="13" t="n">
         <v>0.9946004319654428</v>
       </c>
-      <c r="H55" s="13" t="n">
+      <c r="I55" s="13" t="n">
         <v>0.001799856011519079</v>
       </c>
-      <c r="I55" s="7" t="inlineStr">
+      <c r="J55" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>

--- a/checkrates/week-18/Analisis_Checkrates_OP_7d.xlsx
+++ b/checkrates/week-18/Analisis_Checkrates_OP_7d.xlsx
@@ -541,7 +541,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 09/05/2026 04:34 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 05:07 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -694,7 +694,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 09/05/2026 04:34 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 05:07 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -853,7 +853,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 09/05/2026 04:34 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 05:07 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -2951,7 +2951,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 09/05/2026 04:34 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 05:07 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -4894,7 +4894,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 09/05/2026 04:34 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 05:07 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -6837,7 +6837,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 09/05/2026 04:34 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 05:07 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -8649,16 +8649,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I15"/>
+  <dimension ref="A1:I55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="35" customWidth="1" min="2" max="2"/>
+    <col width="41" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
     <col width="11" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
-    <col width="23" customWidth="1" min="7" max="7"/>
+    <col width="25" customWidth="1" min="7" max="7"/>
     <col width="16" customWidth="1" min="8" max="8"/>
     <col width="16" customWidth="1" min="9" max="9"/>
   </cols>
@@ -8680,7 +8680,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 09/05/2026 04:34 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 05:07 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -9078,6 +9078,1406 @@
       <c r="I15" s="5" t="inlineStr">
         <is>
           <t>Crítica</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>Dallas</t>
+        </is>
+      </c>
+      <c r="C16" s="12" t="n">
+        <v>17781</v>
+      </c>
+      <c r="D16" s="12" t="n">
+        <v>17099</v>
+      </c>
+      <c r="E16" s="12" t="n">
+        <v>285</v>
+      </c>
+      <c r="F16" s="13" t="n">
+        <v>0.9616444519430853</v>
+      </c>
+      <c r="G16" s="13" t="n">
+        <v>0.01602834486249367</v>
+      </c>
+      <c r="H16" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+      <c r="I16" s="5" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>Seattle Area</t>
+        </is>
+      </c>
+      <c r="C17" s="12" t="n">
+        <v>17348</v>
+      </c>
+      <c r="D17" s="12" t="n">
+        <v>16949</v>
+      </c>
+      <c r="E17" s="12" t="n">
+        <v>196</v>
+      </c>
+      <c r="F17" s="13" t="n">
+        <v>0.9770002305741295</v>
+      </c>
+      <c r="G17" s="13" t="n">
+        <v>0.01129813234955038</v>
+      </c>
+      <c r="H17" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+      <c r="I17" s="5" t="inlineStr">
+        <is>
+          <t>Revisar</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>Dubai Area</t>
+        </is>
+      </c>
+      <c r="C18" s="12" t="n">
+        <v>17231</v>
+      </c>
+      <c r="D18" s="12" t="n">
+        <v>15932</v>
+      </c>
+      <c r="E18" s="12" t="n">
+        <v>12</v>
+      </c>
+      <c r="F18" s="13" t="n">
+        <v>0.9246126167953108</v>
+      </c>
+      <c r="G18" s="13" t="n">
+        <v>0.0006964192443851199</v>
+      </c>
+      <c r="H18" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
+        </is>
+      </c>
+      <c r="I18" s="5" t="inlineStr">
+        <is>
+          <t>Crítica</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="C19" s="12" t="n">
+        <v>15847</v>
+      </c>
+      <c r="D19" s="12" t="n">
+        <v>15429</v>
+      </c>
+      <c r="E19" s="12" t="n">
+        <v>13</v>
+      </c>
+      <c r="F19" s="13" t="n">
+        <v>0.973622767716287</v>
+      </c>
+      <c r="G19" s="13" t="n">
+        <v>0.0008203445447087777</v>
+      </c>
+      <c r="H19" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+      <c r="I19" s="5" t="inlineStr">
+        <is>
+          <t>Crítica</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>Boston</t>
+        </is>
+      </c>
+      <c r="C20" s="12" t="n">
+        <v>15303</v>
+      </c>
+      <c r="D20" s="12" t="n">
+        <v>14762</v>
+      </c>
+      <c r="E20" s="12" t="n">
+        <v>185</v>
+      </c>
+      <c r="F20" s="13" t="n">
+        <v>0.9646474547474352</v>
+      </c>
+      <c r="G20" s="13" t="n">
+        <v>0.01208913284976802</v>
+      </c>
+      <c r="H20" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+      <c r="I20" s="5" t="inlineStr">
+        <is>
+          <t>Revisar</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="n">
+        <v>16</v>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>El Cairo Area</t>
+        </is>
+      </c>
+      <c r="C21" s="12" t="n">
+        <v>14789</v>
+      </c>
+      <c r="D21" s="12" t="n">
+        <v>13836</v>
+      </c>
+      <c r="E21" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="F21" s="13" t="n">
+        <v>0.935560213672324</v>
+      </c>
+      <c r="G21" s="13" t="n">
+        <v>0.0006085604165257962</v>
+      </c>
+      <c r="H21" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+      <c r="I21" s="5" t="inlineStr">
+        <is>
+          <t>Crítica</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>Atlanta Area</t>
+        </is>
+      </c>
+      <c r="C22" s="12" t="n">
+        <v>14646</v>
+      </c>
+      <c r="D22" s="12" t="n">
+        <v>14003</v>
+      </c>
+      <c r="E22" s="12" t="n">
+        <v>191</v>
+      </c>
+      <c r="F22" s="13" t="n">
+        <v>0.9560972279120579</v>
+      </c>
+      <c r="G22" s="13" t="n">
+        <v>0.01304110337293459</v>
+      </c>
+      <c r="H22" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+      <c r="I22" s="5" t="inlineStr">
+        <is>
+          <t>Revisar</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>Los Angeles (and vicinity), CA, US</t>
+        </is>
+      </c>
+      <c r="C23" s="12" t="n">
+        <v>13459</v>
+      </c>
+      <c r="D23" s="12" t="n">
+        <v>12590</v>
+      </c>
+      <c r="E23" s="12" t="n">
+        <v>99</v>
+      </c>
+      <c r="F23" s="13" t="n">
+        <v>0.9354335388959061</v>
+      </c>
+      <c r="G23" s="13" t="n">
+        <v>0.007355672784010699</v>
+      </c>
+      <c r="H23" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+      <c r="I23" s="5" t="inlineStr">
+        <is>
+          <t>Crítica</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="n">
+        <v>19</v>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>New Orleans</t>
+        </is>
+      </c>
+      <c r="C24" s="12" t="n">
+        <v>13386</v>
+      </c>
+      <c r="D24" s="12" t="n">
+        <v>13010</v>
+      </c>
+      <c r="E24" s="12" t="n">
+        <v>106</v>
+      </c>
+      <c r="F24" s="13" t="n">
+        <v>0.9719109517406246</v>
+      </c>
+      <c r="G24" s="13" t="n">
+        <v>0.007918721051845212</v>
+      </c>
+      <c r="H24" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+      <c r="I24" s="5" t="inlineStr">
+        <is>
+          <t>Crítica</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>Houston (and vicinity), TX, US</t>
+        </is>
+      </c>
+      <c r="C25" s="12" t="n">
+        <v>12994</v>
+      </c>
+      <c r="D25" s="12" t="n">
+        <v>12334</v>
+      </c>
+      <c r="E25" s="12" t="n">
+        <v>211</v>
+      </c>
+      <c r="F25" s="13" t="n">
+        <v>0.9492073264583654</v>
+      </c>
+      <c r="G25" s="13" t="n">
+        <v>0.01623826381406803</v>
+      </c>
+      <c r="H25" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+      <c r="I25" s="5" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="n">
+        <v>21</v>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>Nashville (and vicinity), TN, US</t>
+        </is>
+      </c>
+      <c r="C26" s="12" t="n">
+        <v>12558</v>
+      </c>
+      <c r="D26" s="12" t="n">
+        <v>12155</v>
+      </c>
+      <c r="E26" s="12" t="n">
+        <v>187</v>
+      </c>
+      <c r="F26" s="13" t="n">
+        <v>0.9679089026915114</v>
+      </c>
+      <c r="G26" s="13" t="n">
+        <v>0.01489090619525402</v>
+      </c>
+      <c r="H26" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+      <c r="I26" s="5" t="inlineStr">
+        <is>
+          <t>Revisar</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="n">
+        <v>22</v>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="C27" s="12" t="n">
+        <v>11695</v>
+      </c>
+      <c r="D27" s="12" t="n">
+        <v>11414</v>
+      </c>
+      <c r="E27" s="12" t="n">
+        <v>96</v>
+      </c>
+      <c r="F27" s="13" t="n">
+        <v>0.9759726378794357</v>
+      </c>
+      <c r="G27" s="13" t="n">
+        <v>0.00820863616930312</v>
+      </c>
+      <c r="H27" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+      <c r="I27" s="5" t="inlineStr">
+        <is>
+          <t>Revisar</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="n">
+        <v>23</v>
+      </c>
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t>Greenville Area</t>
+        </is>
+      </c>
+      <c r="C28" s="12" t="n">
+        <v>10629</v>
+      </c>
+      <c r="D28" s="12" t="n">
+        <v>9947</v>
+      </c>
+      <c r="E28" s="12" t="n">
+        <v>111</v>
+      </c>
+      <c r="F28" s="13" t="n">
+        <v>0.9358359205945996</v>
+      </c>
+      <c r="G28" s="13" t="n">
+        <v>0.0104431272932543</v>
+      </c>
+      <c r="H28" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+      <c r="I28" s="5" t="inlineStr">
+        <is>
+          <t>Revisar</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>Phoenix (and vicinity), AZ, US</t>
+        </is>
+      </c>
+      <c r="C29" s="12" t="n">
+        <v>10312</v>
+      </c>
+      <c r="D29" s="12" t="n">
+        <v>9980</v>
+      </c>
+      <c r="E29" s="12" t="n">
+        <v>157</v>
+      </c>
+      <c r="F29" s="13" t="n">
+        <v>0.9678044996121024</v>
+      </c>
+      <c r="G29" s="13" t="n">
+        <v>0.01522498060512025</v>
+      </c>
+      <c r="H29" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+      <c r="I29" s="5" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>Denver (and vicinity), CO, US</t>
+        </is>
+      </c>
+      <c r="C30" s="12" t="n">
+        <v>10244</v>
+      </c>
+      <c r="D30" s="12" t="n">
+        <v>9805</v>
+      </c>
+      <c r="E30" s="12" t="n">
+        <v>144</v>
+      </c>
+      <c r="F30" s="13" t="n">
+        <v>0.9571456462319406</v>
+      </c>
+      <c r="G30" s="13" t="n">
+        <v>0.01405700898086685</v>
+      </c>
+      <c r="H30" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+      <c r="I30" s="5" t="inlineStr">
+        <is>
+          <t>Revisar</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="n">
+        <v>26</v>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>Riviera Nayarit</t>
+        </is>
+      </c>
+      <c r="C31" s="12" t="n">
+        <v>10034</v>
+      </c>
+      <c r="D31" s="12" t="n">
+        <v>7884</v>
+      </c>
+      <c r="E31" s="12" t="n">
+        <v>187</v>
+      </c>
+      <c r="F31" s="13" t="n">
+        <v>0.7857285230217261</v>
+      </c>
+      <c r="G31" s="13" t="n">
+        <v>0.01863663543950568</v>
+      </c>
+      <c r="H31" s="7" t="inlineStr">
+        <is>
+          <t>Crítica</t>
+        </is>
+      </c>
+      <c r="I31" s="5" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="n">
+        <v>27</v>
+      </c>
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>Fort Lauderdale (and vicinity), FL, US</t>
+        </is>
+      </c>
+      <c r="C32" s="12" t="n">
+        <v>10017</v>
+      </c>
+      <c r="D32" s="12" t="n">
+        <v>9647</v>
+      </c>
+      <c r="E32" s="12" t="n">
+        <v>105</v>
+      </c>
+      <c r="F32" s="13" t="n">
+        <v>0.9630627932514725</v>
+      </c>
+      <c r="G32" s="13" t="n">
+        <v>0.01048218029350105</v>
+      </c>
+      <c r="H32" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+      <c r="I32" s="5" t="inlineStr">
+        <is>
+          <t>Revisar</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="n">
+        <v>28</v>
+      </c>
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>Abu Dhabi</t>
+        </is>
+      </c>
+      <c r="C33" s="12" t="n">
+        <v>9939</v>
+      </c>
+      <c r="D33" s="12" t="n">
+        <v>9764</v>
+      </c>
+      <c r="E33" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="F33" s="13" t="n">
+        <v>0.9823925948284535</v>
+      </c>
+      <c r="G33" s="13" t="n">
+        <v>0.0003018412315122246</v>
+      </c>
+      <c r="H33" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+      <c r="I33" s="5" t="inlineStr">
+        <is>
+          <t>Crítica</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="n">
+        <v>29</v>
+      </c>
+      <c r="B34" s="5" t="inlineStr">
+        <is>
+          <t>Honolulu Area</t>
+        </is>
+      </c>
+      <c r="C34" s="12" t="n">
+        <v>9636</v>
+      </c>
+      <c r="D34" s="12" t="n">
+        <v>9456</v>
+      </c>
+      <c r="E34" s="12" t="n">
+        <v>88</v>
+      </c>
+      <c r="F34" s="13" t="n">
+        <v>0.9813200498132005</v>
+      </c>
+      <c r="G34" s="13" t="n">
+        <v>0.0091324200913242</v>
+      </c>
+      <c r="H34" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+      <c r="I34" s="5" t="inlineStr">
+        <is>
+          <t>Revisar</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="5" t="n">
+        <v>30</v>
+      </c>
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>Puerto Vallarta Area</t>
+        </is>
+      </c>
+      <c r="C35" s="12" t="n">
+        <v>9565</v>
+      </c>
+      <c r="D35" s="12" t="n">
+        <v>9172</v>
+      </c>
+      <c r="E35" s="12" t="n">
+        <v>240</v>
+      </c>
+      <c r="F35" s="13" t="n">
+        <v>0.9589127025614218</v>
+      </c>
+      <c r="G35" s="13" t="n">
+        <v>0.02509147935180345</v>
+      </c>
+      <c r="H35" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+      <c r="I35" s="5" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="5" t="n">
+        <v>31</v>
+      </c>
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>Punta Cana</t>
+        </is>
+      </c>
+      <c r="C36" s="12" t="n">
+        <v>9266</v>
+      </c>
+      <c r="D36" s="12" t="n">
+        <v>9144</v>
+      </c>
+      <c r="E36" s="12" t="n">
+        <v>103</v>
+      </c>
+      <c r="F36" s="13" t="n">
+        <v>0.9868335851500107</v>
+      </c>
+      <c r="G36" s="13" t="n">
+        <v>0.01111590761925318</v>
+      </c>
+      <c r="H36" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+      <c r="I36" s="5" t="inlineStr">
+        <is>
+          <t>Revisar</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="n">
+        <v>32</v>
+      </c>
+      <c r="B37" s="5" t="inlineStr">
+        <is>
+          <t>Amsterdam</t>
+        </is>
+      </c>
+      <c r="C37" s="12" t="n">
+        <v>8548</v>
+      </c>
+      <c r="D37" s="12" t="n">
+        <v>8188</v>
+      </c>
+      <c r="E37" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="F37" s="13" t="n">
+        <v>0.957884885353299</v>
+      </c>
+      <c r="G37" s="13" t="n">
+        <v>0.0008189050070191858</v>
+      </c>
+      <c r="H37" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+      <c r="I37" s="5" t="inlineStr">
+        <is>
+          <t>Crítica</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="5" t="n">
+        <v>33</v>
+      </c>
+      <c r="B38" s="5" t="inlineStr">
+        <is>
+          <t>Austin</t>
+        </is>
+      </c>
+      <c r="C38" s="12" t="n">
+        <v>8167</v>
+      </c>
+      <c r="D38" s="12" t="n">
+        <v>7846</v>
+      </c>
+      <c r="E38" s="12" t="n">
+        <v>94</v>
+      </c>
+      <c r="F38" s="13" t="n">
+        <v>0.9606954818170687</v>
+      </c>
+      <c r="G38" s="13" t="n">
+        <v>0.01150973429655932</v>
+      </c>
+      <c r="H38" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+      <c r="I38" s="5" t="inlineStr">
+        <is>
+          <t>Revisar</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="5" t="n">
+        <v>34</v>
+      </c>
+      <c r="B39" s="5" t="inlineStr">
+        <is>
+          <t>San Antonio</t>
+        </is>
+      </c>
+      <c r="C39" s="12" t="n">
+        <v>8074</v>
+      </c>
+      <c r="D39" s="12" t="n">
+        <v>7688</v>
+      </c>
+      <c r="E39" s="12" t="n">
+        <v>155</v>
+      </c>
+      <c r="F39" s="13" t="n">
+        <v>0.9521922219469904</v>
+      </c>
+      <c r="G39" s="13" t="n">
+        <v>0.01919742382957642</v>
+      </c>
+      <c r="H39" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+      <c r="I39" s="5" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="5" t="n">
+        <v>35</v>
+      </c>
+      <c r="B40" s="5" t="inlineStr">
+        <is>
+          <t>Mexico City - Central Mexico</t>
+        </is>
+      </c>
+      <c r="C40" s="12" t="n">
+        <v>7156</v>
+      </c>
+      <c r="D40" s="12" t="n">
+        <v>6845</v>
+      </c>
+      <c r="E40" s="12" t="n">
+        <v>238</v>
+      </c>
+      <c r="F40" s="13" t="n">
+        <v>0.9565399664617105</v>
+      </c>
+      <c r="G40" s="13" t="n">
+        <v>0.03325880380100615</v>
+      </c>
+      <c r="H40" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+      <c r="I40" s="5" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="5" t="n">
+        <v>36</v>
+      </c>
+      <c r="B41" s="5" t="inlineStr">
+        <is>
+          <t>Montreal</t>
+        </is>
+      </c>
+      <c r="C41" s="12" t="n">
+        <v>6888</v>
+      </c>
+      <c r="D41" s="12" t="n">
+        <v>6563</v>
+      </c>
+      <c r="E41" s="12" t="n">
+        <v>59</v>
+      </c>
+      <c r="F41" s="13" t="n">
+        <v>0.9528164924506388</v>
+      </c>
+      <c r="G41" s="13" t="n">
+        <v>0.00856562137049942</v>
+      </c>
+      <c r="H41" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+      <c r="I41" s="5" t="inlineStr">
+        <is>
+          <t>Revisar</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="5" t="n">
+        <v>37</v>
+      </c>
+      <c r="B42" s="5" t="inlineStr">
+        <is>
+          <t>Edinburgh Area</t>
+        </is>
+      </c>
+      <c r="C42" s="12" t="n">
+        <v>6803</v>
+      </c>
+      <c r="D42" s="12" t="n">
+        <v>6309</v>
+      </c>
+      <c r="E42" s="12" t="n">
+        <v>71</v>
+      </c>
+      <c r="F42" s="13" t="n">
+        <v>0.9273849772159342</v>
+      </c>
+      <c r="G42" s="13" t="n">
+        <v>0.01043657210054388</v>
+      </c>
+      <c r="H42" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
+        </is>
+      </c>
+      <c r="I42" s="5" t="inlineStr">
+        <is>
+          <t>Revisar</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="5" t="n">
+        <v>38</v>
+      </c>
+      <c r="B43" s="5" t="inlineStr">
+        <is>
+          <t>Washington, DC Area</t>
+        </is>
+      </c>
+      <c r="C43" s="12" t="n">
+        <v>6758</v>
+      </c>
+      <c r="D43" s="12" t="n">
+        <v>6649</v>
+      </c>
+      <c r="E43" s="12" t="n">
+        <v>110</v>
+      </c>
+      <c r="F43" s="13" t="n">
+        <v>0.9838709677419355</v>
+      </c>
+      <c r="G43" s="13" t="n">
+        <v>0.01627700503107428</v>
+      </c>
+      <c r="H43" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+      <c r="I43" s="5" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="5" t="n">
+        <v>39</v>
+      </c>
+      <c r="B44" s="5" t="inlineStr">
+        <is>
+          <t>Puerto Rico</t>
+        </is>
+      </c>
+      <c r="C44" s="12" t="n">
+        <v>6391</v>
+      </c>
+      <c r="D44" s="12" t="n">
+        <v>6152</v>
+      </c>
+      <c r="E44" s="12" t="n">
+        <v>43</v>
+      </c>
+      <c r="F44" s="13" t="n">
+        <v>0.9626036613988421</v>
+      </c>
+      <c r="G44" s="13" t="n">
+        <v>0.006728211547488656</v>
+      </c>
+      <c r="H44" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+      <c r="I44" s="5" t="inlineStr">
+        <is>
+          <t>Crítica</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="5" t="n">
+        <v>40</v>
+      </c>
+      <c r="B45" s="5" t="inlineStr">
+        <is>
+          <t>Múnich Area</t>
+        </is>
+      </c>
+      <c r="C45" s="12" t="n">
+        <v>6308</v>
+      </c>
+      <c r="D45" s="12" t="n">
+        <v>5606</v>
+      </c>
+      <c r="E45" s="12" t="n">
+        <v>79</v>
+      </c>
+      <c r="F45" s="13" t="n">
+        <v>0.888712745719721</v>
+      </c>
+      <c r="G45" s="13" t="n">
+        <v>0.01252377932783767</v>
+      </c>
+      <c r="H45" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
+        </is>
+      </c>
+      <c r="I45" s="5" t="inlineStr">
+        <is>
+          <t>Revisar</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="5" t="n">
+        <v>41</v>
+      </c>
+      <c r="B46" s="5" t="inlineStr">
+        <is>
+          <t>Berlin Area</t>
+        </is>
+      </c>
+      <c r="C46" s="12" t="n">
+        <v>6301</v>
+      </c>
+      <c r="D46" s="12" t="n">
+        <v>5931</v>
+      </c>
+      <c r="E46" s="12" t="n">
+        <v>39</v>
+      </c>
+      <c r="F46" s="13" t="n">
+        <v>0.9412791620377717</v>
+      </c>
+      <c r="G46" s="13" t="n">
+        <v>0.006189493731153785</v>
+      </c>
+      <c r="H46" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+      <c r="I46" s="5" t="inlineStr">
+        <is>
+          <t>Crítica</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="5" t="n">
+        <v>42</v>
+      </c>
+      <c r="B47" s="5" t="inlineStr">
+        <is>
+          <t>Vienna Area</t>
+        </is>
+      </c>
+      <c r="C47" s="12" t="n">
+        <v>6241</v>
+      </c>
+      <c r="D47" s="12" t="n">
+        <v>6005</v>
+      </c>
+      <c r="E47" s="12" t="n">
+        <v>30</v>
+      </c>
+      <c r="F47" s="13" t="n">
+        <v>0.9621855471879507</v>
+      </c>
+      <c r="G47" s="13" t="n">
+        <v>0.004806921967633392</v>
+      </c>
+      <c r="H47" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+      <c r="I47" s="5" t="inlineStr">
+        <is>
+          <t>Crítica</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="5" t="n">
+        <v>43</v>
+      </c>
+      <c r="B48" s="5" t="inlineStr">
+        <is>
+          <t>Madrid</t>
+        </is>
+      </c>
+      <c r="C48" s="12" t="n">
+        <v>6168</v>
+      </c>
+      <c r="D48" s="12" t="n">
+        <v>5834</v>
+      </c>
+      <c r="E48" s="12" t="n">
+        <v>58</v>
+      </c>
+      <c r="F48" s="13" t="n">
+        <v>0.9458495460440985</v>
+      </c>
+      <c r="G48" s="13" t="n">
+        <v>0.009403372243839169</v>
+      </c>
+      <c r="H48" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+      <c r="I48" s="5" t="inlineStr">
+        <is>
+          <t>Revisar</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="5" t="n">
+        <v>44</v>
+      </c>
+      <c r="B49" s="5" t="inlineStr">
+        <is>
+          <t>Tampa Area</t>
+        </is>
+      </c>
+      <c r="C49" s="12" t="n">
+        <v>6096</v>
+      </c>
+      <c r="D49" s="12" t="n">
+        <v>5940</v>
+      </c>
+      <c r="E49" s="12" t="n">
+        <v>80</v>
+      </c>
+      <c r="F49" s="13" t="n">
+        <v>0.9744094488188977</v>
+      </c>
+      <c r="G49" s="13" t="n">
+        <v>0.01312335958005249</v>
+      </c>
+      <c r="H49" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+      <c r="I49" s="5" t="inlineStr">
+        <is>
+          <t>Revisar</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="5" t="n">
+        <v>45</v>
+      </c>
+      <c r="B50" s="5" t="inlineStr">
+        <is>
+          <t>Anaheim Area</t>
+        </is>
+      </c>
+      <c r="C50" s="12" t="n">
+        <v>6068</v>
+      </c>
+      <c r="D50" s="12" t="n">
+        <v>5823</v>
+      </c>
+      <c r="E50" s="12" t="n">
+        <v>41</v>
+      </c>
+      <c r="F50" s="13" t="n">
+        <v>0.9596242584047462</v>
+      </c>
+      <c r="G50" s="13" t="n">
+        <v>0.006756756756756757</v>
+      </c>
+      <c r="H50" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+      <c r="I50" s="5" t="inlineStr">
+        <is>
+          <t>Crítica</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="5" t="n">
+        <v>46</v>
+      </c>
+      <c r="B51" s="5" t="inlineStr">
+        <is>
+          <t>Cartagena Area</t>
+        </is>
+      </c>
+      <c r="C51" s="12" t="n">
+        <v>5996</v>
+      </c>
+      <c r="D51" s="12" t="n">
+        <v>5648</v>
+      </c>
+      <c r="E51" s="12" t="n">
+        <v>93</v>
+      </c>
+      <c r="F51" s="13" t="n">
+        <v>0.9419613075383589</v>
+      </c>
+      <c r="G51" s="13" t="n">
+        <v>0.01551034022681788</v>
+      </c>
+      <c r="H51" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+      <c r="I51" s="5" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="5" t="n">
+        <v>47</v>
+      </c>
+      <c r="B52" s="5" t="inlineStr">
+        <is>
+          <t>Philadelphia (and vicinity), PA, US</t>
+        </is>
+      </c>
+      <c r="C52" s="12" t="n">
+        <v>5930</v>
+      </c>
+      <c r="D52" s="12" t="n">
+        <v>5740</v>
+      </c>
+      <c r="E52" s="12" t="n">
+        <v>95</v>
+      </c>
+      <c r="F52" s="13" t="n">
+        <v>0.9679595278246206</v>
+      </c>
+      <c r="G52" s="13" t="n">
+        <v>0.01602023608768971</v>
+      </c>
+      <c r="H52" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+      <c r="I52" s="5" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="5" t="n">
+        <v>48</v>
+      </c>
+      <c r="B53" s="5" t="inlineStr">
+        <is>
+          <t>London Area</t>
+        </is>
+      </c>
+      <c r="C53" s="12" t="n">
+        <v>5557</v>
+      </c>
+      <c r="D53" s="12" t="n">
+        <v>5280</v>
+      </c>
+      <c r="E53" s="12" t="n">
+        <v>56</v>
+      </c>
+      <c r="F53" s="13" t="n">
+        <v>0.9501529602303401</v>
+      </c>
+      <c r="G53" s="13" t="n">
+        <v>0.01007737988123088</v>
+      </c>
+      <c r="H53" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+      <c r="I53" s="5" t="inlineStr">
+        <is>
+          <t>Revisar</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="5" t="n">
+        <v>49</v>
+      </c>
+      <c r="B54" s="5" t="inlineStr">
+        <is>
+          <t>San Diego</t>
+        </is>
+      </c>
+      <c r="C54" s="12" t="n">
+        <v>5437</v>
+      </c>
+      <c r="D54" s="12" t="n">
+        <v>4993</v>
+      </c>
+      <c r="E54" s="12" t="n">
+        <v>56</v>
+      </c>
+      <c r="F54" s="13" t="n">
+        <v>0.9183373183741034</v>
+      </c>
+      <c r="G54" s="13" t="n">
+        <v>0.01029979768254552</v>
+      </c>
+      <c r="H54" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
+        </is>
+      </c>
+      <c r="I54" s="5" t="inlineStr">
+        <is>
+          <t>Revisar</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="5" t="n">
+        <v>50</v>
+      </c>
+      <c r="B55" s="5" t="inlineStr">
+        <is>
+          <t>Minneapolis - St. Paul Area</t>
+        </is>
+      </c>
+      <c r="C55" s="12" t="n">
+        <v>5421</v>
+      </c>
+      <c r="D55" s="12" t="n">
+        <v>5265</v>
+      </c>
+      <c r="E55" s="12" t="n">
+        <v>112</v>
+      </c>
+      <c r="F55" s="13" t="n">
+        <v>0.9712230215827338</v>
+      </c>
+      <c r="G55" s="13" t="n">
+        <v>0.02066039476111418</v>
+      </c>
+      <c r="H55" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+      <c r="I55" s="5" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -9123,7 +10523,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 09/05/2026 04:34 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 05:07 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -9566,7 +10966,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 09/05/2026 04:34 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 05:07 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>

--- a/checkrates/week-18/Analisis_Checkrates_OP_7d.xlsx
+++ b/checkrates/week-18/Analisis_Checkrates_OP_7d.xlsx
@@ -541,7 +541,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 09/05/2026 05:07 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 05:12 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -694,7 +694,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 09/05/2026 05:07 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 05:12 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -853,7 +853,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 09/05/2026 05:07 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 05:12 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -2951,7 +2951,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 09/05/2026 05:07 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 05:12 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -4894,7 +4894,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 09/05/2026 05:07 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 05:12 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -6837,7 +6837,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 09/05/2026 05:07 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 05:12 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -8680,7 +8680,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 09/05/2026 05:07 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 05:12 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -10523,7 +10523,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 09/05/2026 05:07 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 05:12 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -10966,7 +10966,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 09/05/2026 05:07 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 05:12 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>

--- a/checkrates/week-18/Analisis_Checkrates_OP_7d.xlsx
+++ b/checkrates/week-18/Analisis_Checkrates_OP_7d.xlsx
@@ -541,7 +541,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 09/05/2026 05:12 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 14:32 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -694,7 +694,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 09/05/2026 05:12 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 14:32 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -821,19 +821,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J55"/>
+  <dimension ref="A1:K55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
     <col width="50" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="41" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
-    <col width="11" customWidth="1" min="7" max="7"/>
-    <col width="23" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="41" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
     <col width="23" customWidth="1" min="9" max="9"/>
-    <col width="16" customWidth="1" min="10" max="10"/>
+    <col width="23" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -853,7 +854,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 09/05/2026 05:12 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 14:32 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -875,35 +876,40 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
+          <t>Channel</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
           <t>Destino</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="F5" s="3" t="inlineStr">
         <is>
           <t>CR_Unicos</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="G5" s="3" t="inlineStr">
         <is>
           <t>Successful</t>
         </is>
       </c>
-      <c r="G5" s="3" t="inlineStr">
+      <c r="H5" s="3" t="inlineStr">
         <is>
           <t>Bookings</t>
         </is>
       </c>
-      <c r="H5" s="3" t="inlineStr">
+      <c r="I5" s="3" t="inlineStr">
         <is>
           <t>Eficacia</t>
         </is>
       </c>
-      <c r="I5" s="3" t="inlineStr">
+      <c r="J5" s="3" t="inlineStr">
         <is>
           <t>ConvRate</t>
         </is>
       </c>
-      <c r="J5" s="3" t="inlineStr">
+      <c r="K5" s="3" t="inlineStr">
         <is>
           <t>BandaEficacia</t>
         </is>
@@ -925,25 +931,30 @@
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
           <t>Riviera Nayarit</t>
         </is>
       </c>
-      <c r="E6" s="12" t="n">
+      <c r="F6" s="12" t="n">
         <v>439</v>
       </c>
-      <c r="F6" s="12" t="n">
+      <c r="G6" s="12" t="n">
         <v>21</v>
       </c>
-      <c r="G6" s="12" t="n">
+      <c r="H6" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="H6" s="13" t="n">
+      <c r="I6" s="13" t="n">
         <v>0.04783599088838269</v>
       </c>
-      <c r="I6" s="13" t="n">
+      <c r="J6" s="13" t="n">
         <v>0.002277904328018223</v>
       </c>
-      <c r="J6" s="4" t="inlineStr">
+      <c r="K6" s="4" t="inlineStr">
         <is>
           <t>Súper Crítica</t>
         </is>
@@ -965,25 +976,30 @@
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
           <t>Medellin Area</t>
         </is>
       </c>
-      <c r="E7" s="12" t="n">
+      <c r="F7" s="12" t="n">
         <v>123</v>
       </c>
-      <c r="F7" s="12" t="n">
+      <c r="G7" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="G7" s="12" t="n">
+      <c r="H7" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="H7" s="13" t="n">
+      <c r="I7" s="13" t="n">
         <v>0.05691056910569105</v>
       </c>
-      <c r="I7" s="13" t="n">
+      <c r="J7" s="13" t="n">
         <v>0.008130081300813009</v>
       </c>
-      <c r="J7" s="4" t="inlineStr">
+      <c r="K7" s="4" t="inlineStr">
         <is>
           <t>Súper Crítica</t>
         </is>
@@ -1005,25 +1021,30 @@
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
           <t>Mazatlán</t>
         </is>
       </c>
-      <c r="E8" s="12" t="n">
+      <c r="F8" s="12" t="n">
         <v>98</v>
       </c>
-      <c r="F8" s="12" t="n">
+      <c r="G8" s="12" t="n">
         <v>18</v>
       </c>
-      <c r="G8" s="12" t="n">
+      <c r="H8" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="H8" s="13" t="n">
+      <c r="I8" s="13" t="n">
         <v>0.1836734693877551</v>
       </c>
-      <c r="I8" s="13" t="n">
+      <c r="J8" s="13" t="n">
         <v>0.01020408163265306</v>
       </c>
-      <c r="J8" s="4" t="inlineStr">
+      <c r="K8" s="4" t="inlineStr">
         <is>
           <t>Súper Crítica</t>
         </is>
@@ -1045,25 +1066,30 @@
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
+          <t>HBSI</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
           <t>Las Vegas (and vicinity), NV, US</t>
         </is>
       </c>
-      <c r="E9" s="12" t="n">
+      <c r="F9" s="12" t="n">
         <v>345</v>
       </c>
-      <c r="F9" s="12" t="n">
+      <c r="G9" s="12" t="n">
         <v>72</v>
       </c>
-      <c r="G9" s="12" t="n">
+      <c r="H9" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="H9" s="13" t="n">
+      <c r="I9" s="13" t="n">
         <v>0.208695652173913</v>
       </c>
-      <c r="I9" s="13" t="n">
+      <c r="J9" s="13" t="n">
         <v>0.002898550724637681</v>
       </c>
-      <c r="J9" s="4" t="inlineStr">
+      <c r="K9" s="4" t="inlineStr">
         <is>
           <t>Súper Crítica</t>
         </is>
@@ -1085,25 +1111,30 @@
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
           <t>Riviera Nayarit</t>
         </is>
       </c>
-      <c r="E10" s="12" t="n">
+      <c r="F10" s="12" t="n">
         <v>459</v>
       </c>
-      <c r="F10" s="12" t="n">
+      <c r="G10" s="12" t="n">
         <v>98</v>
       </c>
-      <c r="G10" s="12" t="n">
+      <c r="H10" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="H10" s="13" t="n">
+      <c r="I10" s="13" t="n">
         <v>0.2135076252723312</v>
       </c>
-      <c r="I10" s="13" t="n">
+      <c r="J10" s="13" t="n">
         <v>0.008714596949891068</v>
       </c>
-      <c r="J10" s="4" t="inlineStr">
+      <c r="K10" s="4" t="inlineStr">
         <is>
           <t>Súper Crítica</t>
         </is>
@@ -1125,25 +1156,30 @@
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
           <t>San Antonio</t>
         </is>
       </c>
-      <c r="E11" s="12" t="n">
+      <c r="F11" s="12" t="n">
         <v>287</v>
       </c>
-      <c r="F11" s="12" t="n">
+      <c r="G11" s="12" t="n">
         <v>82</v>
       </c>
-      <c r="G11" s="12" t="n">
+      <c r="H11" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="H11" s="13" t="n">
+      <c r="I11" s="13" t="n">
         <v>0.2857142857142857</v>
       </c>
-      <c r="I11" s="13" t="n">
+      <c r="J11" s="13" t="n">
         <v>0.01045296167247387</v>
       </c>
-      <c r="J11" s="4" t="inlineStr">
+      <c r="K11" s="4" t="inlineStr">
         <is>
           <t>Súper Crítica</t>
         </is>
@@ -1165,25 +1201,30 @@
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
           <t>Riviera Nayarit</t>
         </is>
       </c>
-      <c r="E12" s="12" t="n">
+      <c r="F12" s="12" t="n">
         <v>1676</v>
       </c>
-      <c r="F12" s="12" t="n">
+      <c r="G12" s="12" t="n">
         <v>551</v>
       </c>
-      <c r="G12" s="12" t="n">
+      <c r="H12" s="12" t="n">
         <v>29</v>
       </c>
-      <c r="H12" s="13" t="n">
+      <c r="I12" s="13" t="n">
         <v>0.3287589498806683</v>
       </c>
-      <c r="I12" s="13" t="n">
+      <c r="J12" s="13" t="n">
         <v>0.01730310262529833</v>
       </c>
-      <c r="J12" s="4" t="inlineStr">
+      <c r="K12" s="4" t="inlineStr">
         <is>
           <t>Súper Crítica</t>
         </is>
@@ -1205,25 +1246,30 @@
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
           <t>Ixtapa / Zihuatanejo</t>
         </is>
       </c>
-      <c r="E13" s="12" t="n">
+      <c r="F13" s="12" t="n">
         <v>479</v>
       </c>
-      <c r="F13" s="12" t="n">
+      <c r="G13" s="12" t="n">
         <v>159</v>
       </c>
-      <c r="G13" s="12" t="n">
+      <c r="H13" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="H13" s="13" t="n">
+      <c r="I13" s="13" t="n">
         <v>0.3319415448851775</v>
       </c>
-      <c r="I13" s="13" t="n">
+      <c r="J13" s="13" t="n">
         <v>0.01252609603340292</v>
       </c>
-      <c r="J13" s="4" t="inlineStr">
+      <c r="K13" s="4" t="inlineStr">
         <is>
           <t>Súper Crítica</t>
         </is>
@@ -1245,25 +1291,30 @@
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
           <t>Melbourne Area</t>
         </is>
       </c>
-      <c r="E14" s="12" t="n">
+      <c r="F14" s="12" t="n">
         <v>422</v>
       </c>
-      <c r="F14" s="12" t="n">
+      <c r="G14" s="12" t="n">
         <v>177</v>
       </c>
-      <c r="G14" s="12" t="n">
+      <c r="H14" s="12" t="n">
         <v>15</v>
       </c>
-      <c r="H14" s="13" t="n">
+      <c r="I14" s="13" t="n">
         <v>0.4194312796208531</v>
       </c>
-      <c r="I14" s="13" t="n">
+      <c r="J14" s="13" t="n">
         <v>0.03554502369668246</v>
       </c>
-      <c r="J14" s="4" t="inlineStr">
+      <c r="K14" s="4" t="inlineStr">
         <is>
           <t>Súper Crítica</t>
         </is>
@@ -1285,25 +1336,30 @@
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
           <t>Tucson Area</t>
         </is>
       </c>
-      <c r="E15" s="12" t="n">
+      <c r="F15" s="12" t="n">
         <v>63</v>
       </c>
-      <c r="F15" s="12" t="n">
+      <c r="G15" s="12" t="n">
         <v>31</v>
       </c>
-      <c r="G15" s="12" t="n">
+      <c r="H15" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="H15" s="13" t="n">
+      <c r="I15" s="13" t="n">
         <v>0.492063492063492</v>
       </c>
-      <c r="I15" s="13" t="n">
+      <c r="J15" s="13" t="n">
         <v>0.04761904761904762</v>
       </c>
-      <c r="J15" s="4" t="inlineStr">
+      <c r="K15" s="4" t="inlineStr">
         <is>
           <t>Súper Crítica</t>
         </is>
@@ -1325,25 +1381,30 @@
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
           <t>Newcastle Area</t>
         </is>
       </c>
-      <c r="E16" s="12" t="n">
+      <c r="F16" s="12" t="n">
         <v>138</v>
       </c>
-      <c r="F16" s="12" t="n">
+      <c r="G16" s="12" t="n">
         <v>68</v>
       </c>
-      <c r="G16" s="12" t="n">
+      <c r="H16" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="H16" s="13" t="n">
+      <c r="I16" s="13" t="n">
         <v>0.4927536231884058</v>
       </c>
-      <c r="I16" s="13" t="n">
+      <c r="J16" s="13" t="n">
         <v>0.02173913043478261</v>
       </c>
-      <c r="J16" s="4" t="inlineStr">
+      <c r="K16" s="4" t="inlineStr">
         <is>
           <t>Súper Crítica</t>
         </is>
@@ -1365,25 +1426,30 @@
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
           <t>Melbourne Area</t>
         </is>
       </c>
-      <c r="E17" s="12" t="n">
+      <c r="F17" s="12" t="n">
         <v>190</v>
       </c>
-      <c r="F17" s="12" t="n">
+      <c r="G17" s="12" t="n">
         <v>98</v>
       </c>
-      <c r="G17" s="12" t="n">
+      <c r="H17" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="H17" s="13" t="n">
+      <c r="I17" s="13" t="n">
         <v>0.5157894736842106</v>
       </c>
-      <c r="I17" s="13" t="n">
+      <c r="J17" s="13" t="n">
         <v>0.005263157894736842</v>
       </c>
-      <c r="J17" s="4" t="inlineStr">
+      <c r="K17" s="4" t="inlineStr">
         <is>
           <t>Súper Crítica</t>
         </is>
@@ -1405,25 +1471,30 @@
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
           <t>San Diego Area</t>
         </is>
       </c>
-      <c r="E18" s="12" t="n">
+      <c r="F18" s="12" t="n">
         <v>162</v>
       </c>
-      <c r="F18" s="12" t="n">
+      <c r="G18" s="12" t="n">
         <v>85</v>
       </c>
-      <c r="G18" s="12" t="n">
+      <c r="H18" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="H18" s="13" t="n">
+      <c r="I18" s="13" t="n">
         <v>0.5246913580246914</v>
       </c>
-      <c r="I18" s="13" t="n">
+      <c r="J18" s="13" t="n">
         <v>0.01851851851851852</v>
       </c>
-      <c r="J18" s="4" t="inlineStr">
+      <c r="K18" s="4" t="inlineStr">
         <is>
           <t>Súper Crítica</t>
         </is>
@@ -1445,25 +1516,30 @@
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
+          <t>Expedia</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
           <t>Fort Lauderdale (and vicinity), FL, US</t>
         </is>
       </c>
-      <c r="E19" s="12" t="n">
+      <c r="F19" s="12" t="n">
         <v>91</v>
       </c>
-      <c r="F19" s="12" t="n">
+      <c r="G19" s="12" t="n">
         <v>48</v>
       </c>
-      <c r="G19" s="12" t="n">
+      <c r="H19" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="H19" s="13" t="n">
+      <c r="I19" s="13" t="n">
         <v>0.5274725274725275</v>
       </c>
-      <c r="I19" s="13" t="n">
+      <c r="J19" s="13" t="n">
         <v>0.01098901098901099</v>
       </c>
-      <c r="J19" s="4" t="inlineStr">
+      <c r="K19" s="4" t="inlineStr">
         <is>
           <t>Súper Crítica</t>
         </is>
@@ -1485,25 +1561,30 @@
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
           <t>Cancún</t>
         </is>
       </c>
-      <c r="E20" s="12" t="n">
+      <c r="F20" s="12" t="n">
         <v>427</v>
       </c>
-      <c r="F20" s="12" t="n">
+      <c r="G20" s="12" t="n">
         <v>233</v>
       </c>
-      <c r="G20" s="12" t="n">
+      <c r="H20" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="H20" s="13" t="n">
+      <c r="I20" s="13" t="n">
         <v>0.5456674473067916</v>
       </c>
-      <c r="I20" s="13" t="n">
+      <c r="J20" s="13" t="n">
         <v>0.01873536299765808</v>
       </c>
-      <c r="J20" s="4" t="inlineStr">
+      <c r="K20" s="4" t="inlineStr">
         <is>
           <t>Súper Crítica</t>
         </is>
@@ -1525,25 +1606,30 @@
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
           <t>Williamsburg Area</t>
         </is>
       </c>
-      <c r="E21" s="12" t="n">
+      <c r="F21" s="12" t="n">
         <v>73</v>
       </c>
-      <c r="F21" s="12" t="n">
+      <c r="G21" s="12" t="n">
         <v>40</v>
       </c>
-      <c r="G21" s="12" t="n">
+      <c r="H21" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="H21" s="13" t="n">
+      <c r="I21" s="13" t="n">
         <v>0.547945205479452</v>
       </c>
-      <c r="I21" s="13" t="n">
+      <c r="J21" s="13" t="n">
         <v>0.0273972602739726</v>
       </c>
-      <c r="J21" s="4" t="inlineStr">
+      <c r="K21" s="4" t="inlineStr">
         <is>
           <t>Súper Crítica</t>
         </is>
@@ -1565,25 +1651,30 @@
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="inlineStr">
+        <is>
           <t>Osaka Area</t>
         </is>
       </c>
-      <c r="E22" s="12" t="n">
+      <c r="F22" s="12" t="n">
         <v>159</v>
       </c>
-      <c r="F22" s="12" t="n">
+      <c r="G22" s="12" t="n">
         <v>88</v>
       </c>
-      <c r="G22" s="12" t="n">
+      <c r="H22" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="H22" s="13" t="n">
+      <c r="I22" s="13" t="n">
         <v>0.5534591194968553</v>
       </c>
-      <c r="I22" s="13" t="n">
+      <c r="J22" s="13" t="n">
         <v>0.01886792452830189</v>
       </c>
-      <c r="J22" s="4" t="inlineStr">
+      <c r="K22" s="4" t="inlineStr">
         <is>
           <t>Súper Crítica</t>
         </is>
@@ -1605,25 +1696,30 @@
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
           <t>Vincennes Area</t>
         </is>
       </c>
-      <c r="E23" s="12" t="n">
+      <c r="F23" s="12" t="n">
         <v>244</v>
       </c>
-      <c r="F23" s="12" t="n">
+      <c r="G23" s="12" t="n">
         <v>136</v>
       </c>
-      <c r="G23" s="12" t="n">
+      <c r="H23" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="H23" s="13" t="n">
+      <c r="I23" s="13" t="n">
         <v>0.5573770491803278</v>
       </c>
-      <c r="I23" s="13" t="n">
+      <c r="J23" s="13" t="n">
         <v>0.00819672131147541</v>
       </c>
-      <c r="J23" s="4" t="inlineStr">
+      <c r="K23" s="4" t="inlineStr">
         <is>
           <t>Súper Crítica</t>
         </is>
@@ -1645,25 +1741,30 @@
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E24" s="5" t="inlineStr">
+        <is>
           <t>Upper Palatinate Area</t>
         </is>
       </c>
-      <c r="E24" s="12" t="n">
+      <c r="F24" s="12" t="n">
         <v>133</v>
       </c>
-      <c r="F24" s="12" t="n">
+      <c r="G24" s="12" t="n">
         <v>76</v>
       </c>
-      <c r="G24" s="12" t="n">
+      <c r="H24" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="H24" s="13" t="n">
+      <c r="I24" s="13" t="n">
         <v>0.5714285714285714</v>
       </c>
-      <c r="I24" s="13" t="n">
+      <c r="J24" s="13" t="n">
         <v>0.02255639097744361</v>
       </c>
-      <c r="J24" s="4" t="inlineStr">
+      <c r="K24" s="4" t="inlineStr">
         <is>
           <t>Súper Crítica</t>
         </is>
@@ -1685,25 +1786,30 @@
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
           <t>Sunshine Coast Area</t>
         </is>
       </c>
-      <c r="E25" s="12" t="n">
+      <c r="F25" s="12" t="n">
         <v>151</v>
       </c>
-      <c r="F25" s="12" t="n">
+      <c r="G25" s="12" t="n">
         <v>88</v>
       </c>
-      <c r="G25" s="12" t="n">
+      <c r="H25" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="H25" s="13" t="n">
+      <c r="I25" s="13" t="n">
         <v>0.5827814569536424</v>
       </c>
-      <c r="I25" s="13" t="n">
+      <c r="J25" s="13" t="n">
         <v>0.01324503311258278</v>
       </c>
-      <c r="J25" s="4" t="inlineStr">
+      <c r="K25" s="4" t="inlineStr">
         <is>
           <t>Súper Crítica</t>
         </is>
@@ -1725,25 +1831,30 @@
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E26" s="5" t="inlineStr">
+        <is>
           <t>Tokyo</t>
         </is>
       </c>
-      <c r="E26" s="12" t="n">
+      <c r="F26" s="12" t="n">
         <v>659</v>
       </c>
-      <c r="F26" s="12" t="n">
+      <c r="G26" s="12" t="n">
         <v>385</v>
       </c>
-      <c r="G26" s="12" t="n">
+      <c r="H26" s="12" t="n">
         <v>14</v>
       </c>
-      <c r="H26" s="13" t="n">
+      <c r="I26" s="13" t="n">
         <v>0.5842185128983308</v>
       </c>
-      <c r="I26" s="13" t="n">
+      <c r="J26" s="13" t="n">
         <v>0.0212443095599393</v>
       </c>
-      <c r="J26" s="4" t="inlineStr">
+      <c r="K26" s="4" t="inlineStr">
         <is>
           <t>Súper Crítica</t>
         </is>
@@ -1765,25 +1876,30 @@
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E27" s="5" t="inlineStr">
+        <is>
           <t>Atlanta Area</t>
         </is>
       </c>
-      <c r="E27" s="12" t="n">
+      <c r="F27" s="12" t="n">
         <v>200</v>
       </c>
-      <c r="F27" s="12" t="n">
+      <c r="G27" s="12" t="n">
         <v>117</v>
       </c>
-      <c r="G27" s="12" t="n">
+      <c r="H27" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="H27" s="13" t="n">
+      <c r="I27" s="13" t="n">
         <v>0.585</v>
       </c>
-      <c r="I27" s="13" t="n">
+      <c r="J27" s="13" t="n">
         <v>0.005</v>
       </c>
-      <c r="J27" s="4" t="inlineStr">
+      <c r="K27" s="4" t="inlineStr">
         <is>
           <t>Súper Crítica</t>
         </is>
@@ -1805,25 +1921,30 @@
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E28" s="5" t="inlineStr">
+        <is>
           <t>Topeka Area</t>
         </is>
       </c>
-      <c r="E28" s="12" t="n">
+      <c r="F28" s="12" t="n">
         <v>192</v>
       </c>
-      <c r="F28" s="12" t="n">
+      <c r="G28" s="12" t="n">
         <v>114</v>
       </c>
-      <c r="G28" s="12" t="n">
+      <c r="H28" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="H28" s="13" t="n">
+      <c r="I28" s="13" t="n">
         <v>0.59375</v>
       </c>
-      <c r="I28" s="13" t="n">
+      <c r="J28" s="13" t="n">
         <v>0.03645833333333334</v>
       </c>
-      <c r="J28" s="4" t="inlineStr">
+      <c r="K28" s="4" t="inlineStr">
         <is>
           <t>Súper Crítica</t>
         </is>
@@ -1845,25 +1966,30 @@
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E29" s="5" t="inlineStr">
+        <is>
           <t>Nashville (and vicinity), TN, US</t>
         </is>
       </c>
-      <c r="E29" s="12" t="n">
+      <c r="F29" s="12" t="n">
         <v>98</v>
       </c>
-      <c r="F29" s="12" t="n">
+      <c r="G29" s="12" t="n">
         <v>59</v>
       </c>
-      <c r="G29" s="12" t="n">
+      <c r="H29" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="H29" s="13" t="n">
+      <c r="I29" s="13" t="n">
         <v>0.6020408163265306</v>
       </c>
-      <c r="I29" s="13" t="n">
+      <c r="J29" s="13" t="n">
         <v>0.01020408163265306</v>
       </c>
-      <c r="J29" s="7" t="inlineStr">
+      <c r="K29" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -1885,25 +2011,30 @@
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E30" s="5" t="inlineStr">
+        <is>
           <t>Ohio</t>
         </is>
       </c>
-      <c r="E30" s="12" t="n">
+      <c r="F30" s="12" t="n">
         <v>73</v>
       </c>
-      <c r="F30" s="12" t="n">
+      <c r="G30" s="12" t="n">
         <v>44</v>
       </c>
-      <c r="G30" s="12" t="n">
+      <c r="H30" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="H30" s="13" t="n">
+      <c r="I30" s="13" t="n">
         <v>0.6027397260273972</v>
       </c>
-      <c r="I30" s="13" t="n">
+      <c r="J30" s="13" t="n">
         <v>0.0547945205479452</v>
       </c>
-      <c r="J30" s="7" t="inlineStr">
+      <c r="K30" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -1925,25 +2056,30 @@
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E31" s="5" t="inlineStr">
+        <is>
           <t>Manchester Area</t>
         </is>
       </c>
-      <c r="E31" s="12" t="n">
+      <c r="F31" s="12" t="n">
         <v>150</v>
       </c>
-      <c r="F31" s="12" t="n">
+      <c r="G31" s="12" t="n">
         <v>91</v>
       </c>
-      <c r="G31" s="12" t="n">
+      <c r="H31" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="H31" s="13" t="n">
+      <c r="I31" s="13" t="n">
         <v>0.6066666666666667</v>
       </c>
-      <c r="I31" s="13" t="n">
+      <c r="J31" s="13" t="n">
         <v>0.006666666666666667</v>
       </c>
-      <c r="J31" s="7" t="inlineStr">
+      <c r="K31" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -1965,25 +2101,30 @@
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E32" s="5" t="inlineStr">
+        <is>
           <t>Los Angeles (and vicinity), CA, US</t>
         </is>
       </c>
-      <c r="E32" s="12" t="n">
+      <c r="F32" s="12" t="n">
         <v>74</v>
       </c>
-      <c r="F32" s="12" t="n">
+      <c r="G32" s="12" t="n">
         <v>45</v>
       </c>
-      <c r="G32" s="12" t="n">
+      <c r="H32" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="H32" s="13" t="n">
+      <c r="I32" s="13" t="n">
         <v>0.6081081081081081</v>
       </c>
-      <c r="I32" s="13" t="n">
+      <c r="J32" s="13" t="n">
         <v>0.01351351351351351</v>
       </c>
-      <c r="J32" s="7" t="inlineStr">
+      <c r="K32" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -2005,25 +2146,30 @@
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
+          <t>HBSI</t>
+        </is>
+      </c>
+      <c r="E33" s="5" t="inlineStr">
+        <is>
           <t>Reno Area</t>
         </is>
       </c>
-      <c r="E33" s="12" t="n">
+      <c r="F33" s="12" t="n">
         <v>221</v>
       </c>
-      <c r="F33" s="12" t="n">
+      <c r="G33" s="12" t="n">
         <v>136</v>
       </c>
-      <c r="G33" s="12" t="n">
+      <c r="H33" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="H33" s="13" t="n">
+      <c r="I33" s="13" t="n">
         <v>0.6153846153846154</v>
       </c>
-      <c r="I33" s="13" t="n">
+      <c r="J33" s="13" t="n">
         <v>0.01809954751131222</v>
       </c>
-      <c r="J33" s="7" t="inlineStr">
+      <c r="K33" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -2045,25 +2191,30 @@
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E34" s="5" t="inlineStr">
+        <is>
           <t>Gunnison - Crested Butte Area</t>
         </is>
       </c>
-      <c r="E34" s="12" t="n">
+      <c r="F34" s="12" t="n">
         <v>147</v>
       </c>
-      <c r="F34" s="12" t="n">
+      <c r="G34" s="12" t="n">
         <v>91</v>
       </c>
-      <c r="G34" s="12" t="n">
+      <c r="H34" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="H34" s="13" t="n">
+      <c r="I34" s="13" t="n">
         <v>0.6190476190476191</v>
       </c>
-      <c r="I34" s="13" t="n">
+      <c r="J34" s="13" t="n">
         <v>0.006802721088435374</v>
       </c>
-      <c r="J34" s="7" t="inlineStr">
+      <c r="K34" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -2085,25 +2236,30 @@
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E35" s="5" t="inlineStr">
+        <is>
           <t>Adelaida Area</t>
         </is>
       </c>
-      <c r="E35" s="12" t="n">
+      <c r="F35" s="12" t="n">
         <v>200</v>
       </c>
-      <c r="F35" s="12" t="n">
+      <c r="G35" s="12" t="n">
         <v>124</v>
       </c>
-      <c r="G35" s="12" t="n">
+      <c r="H35" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="H35" s="13" t="n">
+      <c r="I35" s="13" t="n">
         <v>0.62</v>
       </c>
-      <c r="I35" s="13" t="n">
+      <c r="J35" s="13" t="n">
         <v>0.025</v>
       </c>
-      <c r="J35" s="7" t="inlineStr">
+      <c r="K35" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -2125,25 +2281,30 @@
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E36" s="5" t="inlineStr">
+        <is>
           <t>Munich Area</t>
         </is>
       </c>
-      <c r="E36" s="12" t="n">
+      <c r="F36" s="12" t="n">
         <v>88</v>
       </c>
-      <c r="F36" s="12" t="n">
+      <c r="G36" s="12" t="n">
         <v>55</v>
       </c>
-      <c r="G36" s="12" t="n">
+      <c r="H36" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="H36" s="13" t="n">
+      <c r="I36" s="13" t="n">
         <v>0.625</v>
       </c>
-      <c r="I36" s="13" t="n">
+      <c r="J36" s="13" t="n">
         <v>0.04545454545454546</v>
       </c>
-      <c r="J36" s="7" t="inlineStr">
+      <c r="K36" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -2165,25 +2326,30 @@
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="E37" s="5" t="inlineStr">
+        <is>
           <t>Puerto Vallarta Area</t>
         </is>
       </c>
-      <c r="E37" s="12" t="n">
+      <c r="F37" s="12" t="n">
         <v>208</v>
       </c>
-      <c r="F37" s="12" t="n">
+      <c r="G37" s="12" t="n">
         <v>130</v>
       </c>
-      <c r="G37" s="12" t="n">
+      <c r="H37" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="H37" s="13" t="n">
+      <c r="I37" s="13" t="n">
         <v>0.625</v>
       </c>
-      <c r="I37" s="13" t="n">
+      <c r="J37" s="13" t="n">
         <v>0.004807692307692308</v>
       </c>
-      <c r="J37" s="7" t="inlineStr">
+      <c r="K37" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -2205,25 +2371,30 @@
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E38" s="5" t="inlineStr">
+        <is>
           <t>Dallas</t>
         </is>
       </c>
-      <c r="E38" s="12" t="n">
+      <c r="F38" s="12" t="n">
         <v>139</v>
       </c>
-      <c r="F38" s="12" t="n">
+      <c r="G38" s="12" t="n">
         <v>87</v>
       </c>
-      <c r="G38" s="12" t="n">
+      <c r="H38" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="H38" s="13" t="n">
+      <c r="I38" s="13" t="n">
         <v>0.6258992805755396</v>
       </c>
-      <c r="I38" s="13" t="n">
+      <c r="J38" s="13" t="n">
         <v>0.03597122302158273</v>
       </c>
-      <c r="J38" s="7" t="inlineStr">
+      <c r="K38" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -2245,25 +2416,30 @@
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E39" s="5" t="inlineStr">
+        <is>
           <t>Dallas</t>
         </is>
       </c>
-      <c r="E39" s="12" t="n">
+      <c r="F39" s="12" t="n">
         <v>75</v>
       </c>
-      <c r="F39" s="12" t="n">
+      <c r="G39" s="12" t="n">
         <v>47</v>
       </c>
-      <c r="G39" s="12" t="n">
+      <c r="H39" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="H39" s="13" t="n">
+      <c r="I39" s="13" t="n">
         <v>0.6266666666666667</v>
       </c>
-      <c r="I39" s="13" t="n">
+      <c r="J39" s="13" t="n">
         <v>0.01333333333333333</v>
       </c>
-      <c r="J39" s="7" t="inlineStr">
+      <c r="K39" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -2285,25 +2461,30 @@
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E40" s="5" t="inlineStr">
+        <is>
           <t>Okanagan Valley Area</t>
         </is>
       </c>
-      <c r="E40" s="12" t="n">
+      <c r="F40" s="12" t="n">
         <v>215</v>
       </c>
-      <c r="F40" s="12" t="n">
+      <c r="G40" s="12" t="n">
         <v>136</v>
       </c>
-      <c r="G40" s="12" t="n">
+      <c r="H40" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="H40" s="13" t="n">
+      <c r="I40" s="13" t="n">
         <v>0.6325581395348837</v>
       </c>
-      <c r="I40" s="13" t="n">
+      <c r="J40" s="13" t="n">
         <v>0.004651162790697674</v>
       </c>
-      <c r="J40" s="7" t="inlineStr">
+      <c r="K40" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -2325,25 +2506,30 @@
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E41" s="5" t="inlineStr">
+        <is>
           <t>Lincoln Area</t>
         </is>
       </c>
-      <c r="E41" s="12" t="n">
+      <c r="F41" s="12" t="n">
         <v>113</v>
       </c>
-      <c r="F41" s="12" t="n">
+      <c r="G41" s="12" t="n">
         <v>72</v>
       </c>
-      <c r="G41" s="12" t="n">
+      <c r="H41" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="H41" s="13" t="n">
+      <c r="I41" s="13" t="n">
         <v>0.6371681415929203</v>
       </c>
-      <c r="I41" s="13" t="n">
+      <c r="J41" s="13" t="n">
         <v>0.02654867256637168</v>
       </c>
-      <c r="J41" s="7" t="inlineStr">
+      <c r="K41" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -2365,25 +2551,30 @@
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E42" s="5" t="inlineStr">
+        <is>
           <t>Portland (and vicinity), OR, US</t>
         </is>
       </c>
-      <c r="E42" s="12" t="n">
+      <c r="F42" s="12" t="n">
         <v>69</v>
       </c>
-      <c r="F42" s="12" t="n">
+      <c r="G42" s="12" t="n">
         <v>44</v>
       </c>
-      <c r="G42" s="12" t="n">
+      <c r="H42" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="H42" s="13" t="n">
+      <c r="I42" s="13" t="n">
         <v>0.6376811594202898</v>
       </c>
-      <c r="I42" s="13" t="n">
+      <c r="J42" s="13" t="n">
         <v>0.07246376811594203</v>
       </c>
-      <c r="J42" s="7" t="inlineStr">
+      <c r="K42" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -2405,25 +2596,30 @@
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E43" s="5" t="inlineStr">
+        <is>
           <t>Los Angeles (and vicinity), CA, US</t>
         </is>
       </c>
-      <c r="E43" s="12" t="n">
+      <c r="F43" s="12" t="n">
         <v>75</v>
       </c>
-      <c r="F43" s="12" t="n">
+      <c r="G43" s="12" t="n">
         <v>48</v>
       </c>
-      <c r="G43" s="12" t="n">
+      <c r="H43" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="H43" s="13" t="n">
+      <c r="I43" s="13" t="n">
         <v>0.64</v>
       </c>
-      <c r="I43" s="13" t="n">
+      <c r="J43" s="13" t="n">
         <v>0.01333333333333333</v>
       </c>
-      <c r="J43" s="7" t="inlineStr">
+      <c r="K43" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -2445,25 +2641,30 @@
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E44" s="5" t="inlineStr">
+        <is>
           <t>Hanói Area</t>
         </is>
       </c>
-      <c r="E44" s="12" t="n">
+      <c r="F44" s="12" t="n">
         <v>116</v>
       </c>
-      <c r="F44" s="12" t="n">
+      <c r="G44" s="12" t="n">
         <v>75</v>
       </c>
-      <c r="G44" s="12" t="n">
+      <c r="H44" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="H44" s="13" t="n">
+      <c r="I44" s="13" t="n">
         <v>0.646551724137931</v>
       </c>
-      <c r="I44" s="13" t="n">
+      <c r="J44" s="13" t="n">
         <v>0.01724137931034483</v>
       </c>
-      <c r="J44" s="7" t="inlineStr">
+      <c r="K44" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -2485,25 +2686,30 @@
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E45" s="5" t="inlineStr">
+        <is>
           <t>Northern Chesapeake Bay Area</t>
         </is>
       </c>
-      <c r="E45" s="12" t="n">
+      <c r="F45" s="12" t="n">
         <v>71</v>
       </c>
-      <c r="F45" s="12" t="n">
+      <c r="G45" s="12" t="n">
         <v>46</v>
       </c>
-      <c r="G45" s="12" t="n">
+      <c r="H45" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="H45" s="13" t="n">
+      <c r="I45" s="13" t="n">
         <v>0.647887323943662</v>
       </c>
-      <c r="I45" s="13" t="n">
+      <c r="J45" s="13" t="n">
         <v>0.01408450704225352</v>
       </c>
-      <c r="J45" s="7" t="inlineStr">
+      <c r="K45" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -2525,25 +2731,30 @@
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E46" s="5" t="inlineStr">
+        <is>
           <t>Deadwood Area</t>
         </is>
       </c>
-      <c r="E46" s="12" t="n">
+      <c r="F46" s="12" t="n">
         <v>80</v>
       </c>
-      <c r="F46" s="12" t="n">
+      <c r="G46" s="12" t="n">
         <v>52</v>
       </c>
-      <c r="G46" s="12" t="n">
+      <c r="H46" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="H46" s="13" t="n">
+      <c r="I46" s="13" t="n">
         <v>0.65</v>
       </c>
-      <c r="I46" s="13" t="n">
+      <c r="J46" s="13" t="n">
         <v>0.0125</v>
       </c>
-      <c r="J46" s="7" t="inlineStr">
+      <c r="K46" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -2565,25 +2776,30 @@
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E47" s="5" t="inlineStr">
+        <is>
           <t>Houston (and vicinity), TX, US</t>
         </is>
       </c>
-      <c r="E47" s="12" t="n">
+      <c r="F47" s="12" t="n">
         <v>179</v>
       </c>
-      <c r="F47" s="12" t="n">
+      <c r="G47" s="12" t="n">
         <v>117</v>
       </c>
-      <c r="G47" s="12" t="n">
+      <c r="H47" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="H47" s="13" t="n">
+      <c r="I47" s="13" t="n">
         <v>0.6536312849162011</v>
       </c>
-      <c r="I47" s="13" t="n">
+      <c r="J47" s="13" t="n">
         <v>0.01675977653631285</v>
       </c>
-      <c r="J47" s="7" t="inlineStr">
+      <c r="K47" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -2605,25 +2821,30 @@
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="E48" s="5" t="inlineStr">
+        <is>
           <t>Cancún</t>
         </is>
       </c>
-      <c r="E48" s="12" t="n">
+      <c r="F48" s="12" t="n">
         <v>703</v>
       </c>
-      <c r="F48" s="12" t="n">
+      <c r="G48" s="12" t="n">
         <v>460</v>
       </c>
-      <c r="G48" s="12" t="n">
+      <c r="H48" s="12" t="n">
         <v>25</v>
       </c>
-      <c r="H48" s="13" t="n">
+      <c r="I48" s="13" t="n">
         <v>0.6543385490753911</v>
       </c>
-      <c r="I48" s="13" t="n">
+      <c r="J48" s="13" t="n">
         <v>0.03556187766714083</v>
       </c>
-      <c r="J48" s="7" t="inlineStr">
+      <c r="K48" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -2645,25 +2866,30 @@
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="E49" s="5" t="inlineStr">
+        <is>
           <t>Mexico City - Central Mexico</t>
         </is>
       </c>
-      <c r="E49" s="12" t="n">
+      <c r="F49" s="12" t="n">
         <v>102</v>
       </c>
-      <c r="F49" s="12" t="n">
+      <c r="G49" s="12" t="n">
         <v>67</v>
       </c>
-      <c r="G49" s="12" t="n">
+      <c r="H49" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="H49" s="13" t="n">
+      <c r="I49" s="13" t="n">
         <v>0.6568627450980392</v>
       </c>
-      <c r="I49" s="13" t="n">
+      <c r="J49" s="13" t="n">
         <v>0.0196078431372549</v>
       </c>
-      <c r="J49" s="7" t="inlineStr">
+      <c r="K49" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -2685,25 +2911,30 @@
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E50" s="5" t="inlineStr">
+        <is>
           <t>London Area</t>
         </is>
       </c>
-      <c r="E50" s="12" t="n">
+      <c r="F50" s="12" t="n">
         <v>199</v>
       </c>
-      <c r="F50" s="12" t="n">
+      <c r="G50" s="12" t="n">
         <v>131</v>
       </c>
-      <c r="G50" s="12" t="n">
+      <c r="H50" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="H50" s="13" t="n">
+      <c r="I50" s="13" t="n">
         <v>0.6582914572864321</v>
       </c>
-      <c r="I50" s="13" t="n">
+      <c r="J50" s="13" t="n">
         <v>0.005025125628140704</v>
       </c>
-      <c r="J50" s="7" t="inlineStr">
+      <c r="K50" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -2725,25 +2956,30 @@
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E51" s="5" t="inlineStr">
+        <is>
           <t>Sydney Area</t>
         </is>
       </c>
-      <c r="E51" s="12" t="n">
+      <c r="F51" s="12" t="n">
         <v>314</v>
       </c>
-      <c r="F51" s="12" t="n">
+      <c r="G51" s="12" t="n">
         <v>208</v>
       </c>
-      <c r="G51" s="12" t="n">
+      <c r="H51" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="H51" s="13" t="n">
+      <c r="I51" s="13" t="n">
         <v>0.6624203821656051</v>
       </c>
-      <c r="I51" s="13" t="n">
+      <c r="J51" s="13" t="n">
         <v>0.006369426751592357</v>
       </c>
-      <c r="J51" s="7" t="inlineStr">
+      <c r="K51" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -2765,25 +3001,30 @@
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E52" s="5" t="inlineStr">
+        <is>
           <t>Chicago</t>
         </is>
       </c>
-      <c r="E52" s="12" t="n">
+      <c r="F52" s="12" t="n">
         <v>905</v>
       </c>
-      <c r="F52" s="12" t="n">
+      <c r="G52" s="12" t="n">
         <v>600</v>
       </c>
-      <c r="G52" s="12" t="n">
+      <c r="H52" s="12" t="n">
         <v>14</v>
       </c>
-      <c r="H52" s="13" t="n">
+      <c r="I52" s="13" t="n">
         <v>0.6629834254143646</v>
       </c>
-      <c r="I52" s="13" t="n">
+      <c r="J52" s="13" t="n">
         <v>0.01546961325966851</v>
       </c>
-      <c r="J52" s="7" t="inlineStr">
+      <c r="K52" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -2805,25 +3046,30 @@
       </c>
       <c r="D53" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E53" s="5" t="inlineStr">
+        <is>
           <t>Crystal River Area</t>
         </is>
       </c>
-      <c r="E53" s="12" t="n">
+      <c r="F53" s="12" t="n">
         <v>98</v>
       </c>
-      <c r="F53" s="12" t="n">
+      <c r="G53" s="12" t="n">
         <v>65</v>
       </c>
-      <c r="G53" s="12" t="n">
+      <c r="H53" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="H53" s="13" t="n">
+      <c r="I53" s="13" t="n">
         <v>0.6632653061224489</v>
       </c>
-      <c r="I53" s="13" t="n">
+      <c r="J53" s="13" t="n">
         <v>0.05102040816326531</v>
       </c>
-      <c r="J53" s="7" t="inlineStr">
+      <c r="K53" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -2845,25 +3091,30 @@
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E54" s="5" t="inlineStr">
+        <is>
           <t>Helsinki Area</t>
         </is>
       </c>
-      <c r="E54" s="12" t="n">
+      <c r="F54" s="12" t="n">
         <v>156</v>
       </c>
-      <c r="F54" s="12" t="n">
+      <c r="G54" s="12" t="n">
         <v>104</v>
       </c>
-      <c r="G54" s="12" t="n">
+      <c r="H54" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="H54" s="13" t="n">
+      <c r="I54" s="13" t="n">
         <v>0.6666666666666666</v>
       </c>
-      <c r="I54" s="13" t="n">
+      <c r="J54" s="13" t="n">
         <v>0.00641025641025641</v>
       </c>
-      <c r="J54" s="7" t="inlineStr">
+      <c r="K54" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -2885,25 +3136,30 @@
       </c>
       <c r="D55" s="5" t="inlineStr">
         <is>
+          <t>HBSI</t>
+        </is>
+      </c>
+      <c r="E55" s="5" t="inlineStr">
+        <is>
           <t>Reno Area</t>
         </is>
       </c>
-      <c r="E55" s="12" t="n">
+      <c r="F55" s="12" t="n">
         <v>130</v>
       </c>
-      <c r="F55" s="12" t="n">
+      <c r="G55" s="12" t="n">
         <v>87</v>
       </c>
-      <c r="G55" s="12" t="n">
+      <c r="H55" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="H55" s="13" t="n">
+      <c r="I55" s="13" t="n">
         <v>0.6692307692307692</v>
       </c>
-      <c r="I55" s="13" t="n">
+      <c r="J55" s="13" t="n">
         <v>0.007692307692307693</v>
       </c>
-      <c r="J55" s="7" t="inlineStr">
+      <c r="K55" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -2920,18 +3176,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I55"/>
+  <dimension ref="A1:J55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
     <col width="50" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="35" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="11" customWidth="1" min="6" max="6"/>
-    <col width="21" customWidth="1" min="7" max="7"/>
-    <col width="25" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="35" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="21" customWidth="1" min="8" max="8"/>
+    <col width="25" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2951,7 +3208,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 09/05/2026 05:12 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 14:32 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -2973,30 +3230,35 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
+          <t>Channel</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
           <t>Destino</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="F5" s="3" t="inlineStr">
         <is>
           <t>CR_Unicos</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="G5" s="3" t="inlineStr">
         <is>
           <t>Bookings</t>
         </is>
       </c>
-      <c r="G5" s="3" t="inlineStr">
+      <c r="H5" s="3" t="inlineStr">
         <is>
           <t>Eficacia</t>
         </is>
       </c>
-      <c r="H5" s="3" t="inlineStr">
+      <c r="I5" s="3" t="inlineStr">
         <is>
           <t>ConvRate</t>
         </is>
       </c>
-      <c r="I5" s="3" t="inlineStr">
+      <c r="J5" s="3" t="inlineStr">
         <is>
           <t>BandaConvRate</t>
         </is>
@@ -3018,22 +3280,27 @@
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
           <t>New York</t>
         </is>
       </c>
-      <c r="E6" s="12" t="n">
+      <c r="F6" s="12" t="n">
         <v>8879</v>
       </c>
-      <c r="F6" s="12" t="n">
+      <c r="G6" s="12" t="n">
         <v>42</v>
       </c>
-      <c r="G6" s="13" t="n">
+      <c r="H6" s="13" t="n">
         <v>0.9713931749070841</v>
       </c>
-      <c r="H6" s="13" t="n">
+      <c r="I6" s="13" t="n">
         <v>0.004730262416938844</v>
       </c>
-      <c r="I6" s="7" t="inlineStr">
+      <c r="J6" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -3055,22 +3322,27 @@
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
           <t>Istanbul Area</t>
         </is>
       </c>
-      <c r="E7" s="12" t="n">
+      <c r="F7" s="12" t="n">
         <v>6781</v>
       </c>
-      <c r="F7" s="12" t="n">
+      <c r="G7" s="12" t="n">
         <v>14</v>
       </c>
-      <c r="G7" s="13" t="n">
+      <c r="H7" s="13" t="n">
         <v>0.9983778203804748</v>
       </c>
-      <c r="H7" s="13" t="n">
+      <c r="I7" s="13" t="n">
         <v>0.002064592243032001</v>
       </c>
-      <c r="I7" s="7" t="inlineStr">
+      <c r="J7" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -3092,22 +3364,27 @@
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
           <t>New York</t>
         </is>
       </c>
-      <c r="E8" s="12" t="n">
+      <c r="F8" s="12" t="n">
         <v>6333</v>
       </c>
-      <c r="F8" s="12" t="n">
+      <c r="G8" s="12" t="n">
         <v>25</v>
       </c>
-      <c r="G8" s="13" t="n">
+      <c r="H8" s="13" t="n">
         <v>0.9883151744828675</v>
       </c>
-      <c r="H8" s="13" t="n">
+      <c r="I8" s="13" t="n">
         <v>0.003947576188220433</v>
       </c>
-      <c r="I8" s="7" t="inlineStr">
+      <c r="J8" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -3129,22 +3406,27 @@
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
+          <t>HBSI</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
           <t>Las Vegas (and vicinity), NV, US</t>
         </is>
       </c>
-      <c r="E9" s="12" t="n">
+      <c r="F9" s="12" t="n">
         <v>5744</v>
       </c>
-      <c r="F9" s="12" t="n">
+      <c r="G9" s="12" t="n">
         <v>60</v>
       </c>
-      <c r="G9" s="13" t="n">
+      <c r="H9" s="13" t="n">
         <v>0.9895543175487466</v>
       </c>
-      <c r="H9" s="13" t="n">
+      <c r="I9" s="13" t="n">
         <v>0.01044568245125348</v>
       </c>
-      <c r="I9" s="8" t="inlineStr">
+      <c r="J9" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -3166,22 +3448,27 @@
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
+          <t>HBSI</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
           <t>Las Vegas (and vicinity), NV, US</t>
         </is>
       </c>
-      <c r="E10" s="12" t="n">
+      <c r="F10" s="12" t="n">
         <v>4117</v>
       </c>
-      <c r="F10" s="12" t="n">
+      <c r="G10" s="12" t="n">
         <v>29</v>
       </c>
-      <c r="G10" s="13" t="n">
+      <c r="H10" s="13" t="n">
         <v>0.7391304347826086</v>
       </c>
-      <c r="H10" s="13" t="n">
+      <c r="I10" s="13" t="n">
         <v>0.007043964051493806</v>
       </c>
-      <c r="I10" s="7" t="inlineStr">
+      <c r="J10" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -3203,22 +3490,27 @@
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
+          <t>HBSI</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
           <t>Las Vegas (and vicinity), NV, US</t>
         </is>
       </c>
-      <c r="E11" s="12" t="n">
+      <c r="F11" s="12" t="n">
         <v>4029</v>
       </c>
-      <c r="F11" s="12" t="n">
+      <c r="G11" s="12" t="n">
         <v>19</v>
       </c>
-      <c r="G11" s="13" t="n">
+      <c r="H11" s="13" t="n">
         <v>0.9893273765202284</v>
       </c>
-      <c r="H11" s="13" t="n">
+      <c r="I11" s="13" t="n">
         <v>0.004715810374782825</v>
       </c>
-      <c r="I11" s="7" t="inlineStr">
+      <c r="J11" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -3240,22 +3532,27 @@
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
           <t>New Orleans</t>
         </is>
       </c>
-      <c r="E12" s="12" t="n">
+      <c r="F12" s="12" t="n">
         <v>3776</v>
       </c>
-      <c r="F12" s="12" t="n">
+      <c r="G12" s="12" t="n">
         <v>12</v>
       </c>
-      <c r="G12" s="13" t="n">
+      <c r="H12" s="13" t="n">
         <v>0.9909957627118644</v>
       </c>
-      <c r="H12" s="13" t="n">
+      <c r="I12" s="13" t="n">
         <v>0.003177966101694915</v>
       </c>
-      <c r="I12" s="7" t="inlineStr">
+      <c r="J12" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -3277,22 +3574,27 @@
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
           <t>New York</t>
         </is>
       </c>
-      <c r="E13" s="12" t="n">
+      <c r="F13" s="12" t="n">
         <v>3733</v>
       </c>
-      <c r="F13" s="12" t="n">
+      <c r="G13" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="G13" s="13" t="n">
+      <c r="H13" s="13" t="n">
         <v>0.998928475756764</v>
       </c>
-      <c r="H13" s="13" t="n">
+      <c r="I13" s="13" t="n">
         <v>0.002143048486472007</v>
       </c>
-      <c r="I13" s="7" t="inlineStr">
+      <c r="J13" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -3314,22 +3616,27 @@
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
           <t>Vancouver</t>
         </is>
       </c>
-      <c r="E14" s="12" t="n">
+      <c r="F14" s="12" t="n">
         <v>3639</v>
       </c>
-      <c r="F14" s="12" t="n">
+      <c r="G14" s="12" t="n">
         <v>35</v>
       </c>
-      <c r="G14" s="13" t="n">
+      <c r="H14" s="13" t="n">
         <v>0.9884583676834295</v>
       </c>
-      <c r="H14" s="13" t="n">
+      <c r="I14" s="13" t="n">
         <v>0.009618026930475405</v>
       </c>
-      <c r="I14" s="8" t="inlineStr">
+      <c r="J14" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -3351,22 +3658,27 @@
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
           <t>Honolulu Area</t>
         </is>
       </c>
-      <c r="E15" s="12" t="n">
+      <c r="F15" s="12" t="n">
         <v>3420</v>
       </c>
-      <c r="F15" s="12" t="n">
+      <c r="G15" s="12" t="n">
         <v>19</v>
       </c>
-      <c r="G15" s="13" t="n">
+      <c r="H15" s="13" t="n">
         <v>0.9944444444444445</v>
       </c>
-      <c r="H15" s="13" t="n">
+      <c r="I15" s="13" t="n">
         <v>0.005555555555555556</v>
       </c>
-      <c r="I15" s="7" t="inlineStr">
+      <c r="J15" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -3388,22 +3700,27 @@
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
+          <t>HBSI</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
           <t>Las Vegas (and vicinity), NV, US</t>
         </is>
       </c>
-      <c r="E16" s="12" t="n">
+      <c r="F16" s="12" t="n">
         <v>3295</v>
       </c>
-      <c r="F16" s="12" t="n">
+      <c r="G16" s="12" t="n">
         <v>33</v>
       </c>
-      <c r="G16" s="13" t="n">
+      <c r="H16" s="13" t="n">
         <v>0.980576631259484</v>
       </c>
-      <c r="H16" s="13" t="n">
+      <c r="I16" s="13" t="n">
         <v>0.01001517450682853</v>
       </c>
-      <c r="I16" s="8" t="inlineStr">
+      <c r="J16" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -3425,22 +3742,27 @@
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
           <t>Toronto Area</t>
         </is>
       </c>
-      <c r="E17" s="12" t="n">
+      <c r="F17" s="12" t="n">
         <v>3116</v>
       </c>
-      <c r="F17" s="12" t="n">
+      <c r="G17" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="G17" s="13" t="n">
+      <c r="H17" s="13" t="n">
         <v>0.9801026957637997</v>
       </c>
-      <c r="H17" s="13" t="n">
+      <c r="I17" s="13" t="n">
         <v>0.0009627727856225931</v>
       </c>
-      <c r="I17" s="7" t="inlineStr">
+      <c r="J17" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -3462,22 +3784,27 @@
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
           <t>Abu Dhabi</t>
         </is>
       </c>
-      <c r="E18" s="12" t="n">
+      <c r="F18" s="12" t="n">
         <v>3099</v>
       </c>
-      <c r="F18" s="12" t="n">
+      <c r="G18" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G18" s="13" t="n">
+      <c r="H18" s="13" t="n">
         <v>0.9970958373668926</v>
       </c>
-      <c r="H18" s="13" t="n">
+      <c r="I18" s="13" t="n">
         <v>0.0003226847370119393</v>
       </c>
-      <c r="I18" s="7" t="inlineStr">
+      <c r="J18" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -3499,22 +3826,27 @@
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
           <t>Chicago</t>
         </is>
       </c>
-      <c r="E19" s="12" t="n">
+      <c r="F19" s="12" t="n">
         <v>3062</v>
       </c>
-      <c r="F19" s="12" t="n">
+      <c r="G19" s="12" t="n">
         <v>19</v>
       </c>
-      <c r="G19" s="13" t="n">
+      <c r="H19" s="13" t="n">
         <v>0.9647289353363815</v>
       </c>
-      <c r="H19" s="13" t="n">
+      <c r="I19" s="13" t="n">
         <v>0.0062050947093403</v>
       </c>
-      <c r="I19" s="7" t="inlineStr">
+      <c r="J19" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -3536,22 +3868,27 @@
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
           <t>Seattle Area</t>
         </is>
       </c>
-      <c r="E20" s="12" t="n">
+      <c r="F20" s="12" t="n">
         <v>2889</v>
       </c>
-      <c r="F20" s="12" t="n">
+      <c r="G20" s="12" t="n">
         <v>31</v>
       </c>
-      <c r="G20" s="13" t="n">
+      <c r="H20" s="13" t="n">
         <v>0.9930771893388716</v>
       </c>
-      <c r="H20" s="13" t="n">
+      <c r="I20" s="13" t="n">
         <v>0.01073035652474905</v>
       </c>
-      <c r="I20" s="8" t="inlineStr">
+      <c r="J20" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -3573,22 +3910,27 @@
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
           <t>Riviera Maya</t>
         </is>
       </c>
-      <c r="E21" s="12" t="n">
+      <c r="F21" s="12" t="n">
         <v>2849</v>
       </c>
-      <c r="F21" s="12" t="n">
+      <c r="G21" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="G21" s="13" t="n">
+      <c r="H21" s="13" t="n">
         <v>0.9982449982449982</v>
       </c>
-      <c r="H21" s="13" t="n">
+      <c r="I21" s="13" t="n">
         <v>0.002457002457002457</v>
       </c>
-      <c r="I21" s="7" t="inlineStr">
+      <c r="J21" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -3610,22 +3952,27 @@
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="inlineStr">
+        <is>
           <t>Niagara Falls, Canada</t>
         </is>
       </c>
-      <c r="E22" s="12" t="n">
+      <c r="F22" s="12" t="n">
         <v>2778</v>
       </c>
-      <c r="F22" s="12" t="n">
+      <c r="G22" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="G22" s="13" t="n">
+      <c r="H22" s="13" t="n">
         <v>0.9946004319654428</v>
       </c>
-      <c r="H22" s="13" t="n">
+      <c r="I22" s="13" t="n">
         <v>0.001799856011519079</v>
       </c>
-      <c r="I22" s="7" t="inlineStr">
+      <c r="J22" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -3647,22 +3994,27 @@
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
           <t>Anaheim Area</t>
         </is>
       </c>
-      <c r="E23" s="12" t="n">
+      <c r="F23" s="12" t="n">
         <v>2728</v>
       </c>
-      <c r="F23" s="12" t="n">
+      <c r="G23" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="G23" s="13" t="n">
+      <c r="H23" s="13" t="n">
         <v>0.9948680351906158</v>
       </c>
-      <c r="H23" s="13" t="n">
+      <c r="I23" s="13" t="n">
         <v>0.003665689149560118</v>
       </c>
-      <c r="I23" s="7" t="inlineStr">
+      <c r="J23" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -3684,22 +4036,27 @@
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E24" s="5" t="inlineStr">
+        <is>
           <t>Chicago</t>
         </is>
       </c>
-      <c r="E24" s="12" t="n">
+      <c r="F24" s="12" t="n">
         <v>2702</v>
       </c>
-      <c r="F24" s="12" t="n">
+      <c r="G24" s="12" t="n">
         <v>16</v>
       </c>
-      <c r="G24" s="13" t="n">
+      <c r="H24" s="13" t="n">
         <v>0.9803849000740192</v>
       </c>
-      <c r="H24" s="13" t="n">
+      <c r="I24" s="13" t="n">
         <v>0.005921539600296077</v>
       </c>
-      <c r="I24" s="7" t="inlineStr">
+      <c r="J24" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -3721,22 +4078,27 @@
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
           <t>Puerto Rico</t>
         </is>
       </c>
-      <c r="E25" s="12" t="n">
+      <c r="F25" s="12" t="n">
         <v>2701</v>
       </c>
-      <c r="F25" s="12" t="n">
+      <c r="G25" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="G25" s="13" t="n">
+      <c r="H25" s="13" t="n">
         <v>0.9914846353202518</v>
       </c>
-      <c r="H25" s="13" t="n">
+      <c r="I25" s="13" t="n">
         <v>0.003702332469455757</v>
       </c>
-      <c r="I25" s="7" t="inlineStr">
+      <c r="J25" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -3758,22 +4120,27 @@
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E26" s="5" t="inlineStr">
+        <is>
           <t>Paris</t>
         </is>
       </c>
-      <c r="E26" s="12" t="n">
+      <c r="F26" s="12" t="n">
         <v>2625</v>
       </c>
-      <c r="F26" s="12" t="n">
+      <c r="G26" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="G26" s="13" t="n">
+      <c r="H26" s="13" t="n">
         <v>0.9885714285714285</v>
       </c>
-      <c r="H26" s="13" t="n">
+      <c r="I26" s="13" t="n">
         <v>0.0007619047619047619</v>
       </c>
-      <c r="I26" s="7" t="inlineStr">
+      <c r="J26" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -3795,22 +4162,27 @@
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
+          <t>HBSI</t>
+        </is>
+      </c>
+      <c r="E27" s="5" t="inlineStr">
+        <is>
           <t>Las Vegas (and vicinity), NV, US</t>
         </is>
       </c>
-      <c r="E27" s="12" t="n">
+      <c r="F27" s="12" t="n">
         <v>2565</v>
       </c>
-      <c r="F27" s="12" t="n">
+      <c r="G27" s="12" t="n">
         <v>25</v>
       </c>
-      <c r="G27" s="13" t="n">
+      <c r="H27" s="13" t="n">
         <v>0.989083820662768</v>
       </c>
-      <c r="H27" s="13" t="n">
+      <c r="I27" s="13" t="n">
         <v>0.009746588693957114</v>
       </c>
-      <c r="I27" s="8" t="inlineStr">
+      <c r="J27" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -3832,22 +4204,27 @@
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E28" s="5" t="inlineStr">
+        <is>
           <t>Londres</t>
         </is>
       </c>
-      <c r="E28" s="12" t="n">
+      <c r="F28" s="12" t="n">
         <v>2531</v>
       </c>
-      <c r="F28" s="12" t="n">
+      <c r="G28" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="G28" s="13" t="n">
+      <c r="H28" s="13" t="n">
         <v>0.8249703674436981</v>
       </c>
-      <c r="H28" s="13" t="n">
+      <c r="I28" s="13" t="n">
         <v>0.0007902015013828526</v>
       </c>
-      <c r="I28" s="7" t="inlineStr">
+      <c r="J28" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -3869,22 +4246,27 @@
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E29" s="5" t="inlineStr">
+        <is>
           <t>Vancouver</t>
         </is>
       </c>
-      <c r="E29" s="12" t="n">
+      <c r="F29" s="12" t="n">
         <v>2510</v>
       </c>
-      <c r="F29" s="12" t="n">
+      <c r="G29" s="12" t="n">
         <v>24</v>
       </c>
-      <c r="G29" s="13" t="n">
+      <c r="H29" s="13" t="n">
         <v>0.9948207171314741</v>
       </c>
-      <c r="H29" s="13" t="n">
+      <c r="I29" s="13" t="n">
         <v>0.009561752988047808</v>
       </c>
-      <c r="I29" s="8" t="inlineStr">
+      <c r="J29" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -3906,22 +4288,27 @@
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E30" s="5" t="inlineStr">
+        <is>
           <t>New York</t>
         </is>
       </c>
-      <c r="E30" s="12" t="n">
+      <c r="F30" s="12" t="n">
         <v>2394</v>
       </c>
-      <c r="F30" s="12" t="n">
+      <c r="G30" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="G30" s="13" t="n">
+      <c r="H30" s="13" t="n">
         <v>0.9690893901420217</v>
       </c>
-      <c r="H30" s="13" t="n">
+      <c r="I30" s="13" t="n">
         <v>0.002923976608187134</v>
       </c>
-      <c r="I30" s="7" t="inlineStr">
+      <c r="J30" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -3943,22 +4330,27 @@
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E31" s="5" t="inlineStr">
+        <is>
           <t>Halifax Area</t>
         </is>
       </c>
-      <c r="E31" s="12" t="n">
+      <c r="F31" s="12" t="n">
         <v>2264</v>
       </c>
-      <c r="F31" s="12" t="n">
+      <c r="G31" s="12" t="n">
         <v>19</v>
       </c>
-      <c r="G31" s="13" t="n">
+      <c r="H31" s="13" t="n">
         <v>0.9469964664310954</v>
       </c>
-      <c r="H31" s="13" t="n">
+      <c r="I31" s="13" t="n">
         <v>0.008392226148409895</v>
       </c>
-      <c r="I31" s="8" t="inlineStr">
+      <c r="J31" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -3980,22 +4372,27 @@
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E32" s="5" t="inlineStr">
+        <is>
           <t>New York</t>
         </is>
       </c>
-      <c r="E32" s="12" t="n">
+      <c r="F32" s="12" t="n">
         <v>2211</v>
       </c>
-      <c r="F32" s="12" t="n">
+      <c r="G32" s="12" t="n">
         <v>21</v>
       </c>
-      <c r="G32" s="13" t="n">
+      <c r="H32" s="13" t="n">
         <v>0.9877883310719131</v>
       </c>
-      <c r="H32" s="13" t="n">
+      <c r="I32" s="13" t="n">
         <v>0.009497964721845319</v>
       </c>
-      <c r="I32" s="8" t="inlineStr">
+      <c r="J32" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -4017,22 +4414,27 @@
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
+          <t>HBSI</t>
+        </is>
+      </c>
+      <c r="E33" s="5" t="inlineStr">
+        <is>
           <t>Las Vegas (and vicinity), NV, US</t>
         </is>
       </c>
-      <c r="E33" s="12" t="n">
+      <c r="F33" s="12" t="n">
         <v>2209</v>
       </c>
-      <c r="F33" s="12" t="n">
+      <c r="G33" s="12" t="n">
         <v>24</v>
       </c>
-      <c r="G33" s="13" t="n">
+      <c r="H33" s="13" t="n">
         <v>0.9859665006790402</v>
       </c>
-      <c r="H33" s="13" t="n">
+      <c r="I33" s="13" t="n">
         <v>0.01086464463558171</v>
       </c>
-      <c r="I33" s="8" t="inlineStr">
+      <c r="J33" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -4054,22 +4456,27 @@
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E34" s="5" t="inlineStr">
+        <is>
           <t>New York</t>
         </is>
       </c>
-      <c r="E34" s="12" t="n">
+      <c r="F34" s="12" t="n">
         <v>2098</v>
       </c>
-      <c r="F34" s="12" t="n">
+      <c r="G34" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="G34" s="13" t="n">
+      <c r="H34" s="13" t="n">
         <v>0.8975214489990467</v>
       </c>
-      <c r="H34" s="13" t="n">
+      <c r="I34" s="13" t="n">
         <v>0.001906577693040991</v>
       </c>
-      <c r="I34" s="7" t="inlineStr">
+      <c r="J34" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -4091,22 +4498,27 @@
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E35" s="5" t="inlineStr">
+        <is>
           <t>New York</t>
         </is>
       </c>
-      <c r="E35" s="12" t="n">
+      <c r="F35" s="12" t="n">
         <v>2048</v>
       </c>
-      <c r="F35" s="12" t="n">
+      <c r="G35" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="G35" s="13" t="n">
+      <c r="H35" s="13" t="n">
         <v>0.99365234375</v>
       </c>
-      <c r="H35" s="13" t="n">
+      <c r="I35" s="13" t="n">
         <v>0.001953125</v>
       </c>
-      <c r="I35" s="7" t="inlineStr">
+      <c r="J35" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -4128,22 +4540,27 @@
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
+          <t>SynXis</t>
+        </is>
+      </c>
+      <c r="E36" s="5" t="inlineStr">
+        <is>
           <t>Puerto Vallarta Area</t>
         </is>
       </c>
-      <c r="E36" s="12" t="n">
+      <c r="F36" s="12" t="n">
         <v>2041</v>
       </c>
-      <c r="F36" s="12" t="n">
+      <c r="G36" s="12" t="n">
         <v>16</v>
       </c>
-      <c r="G36" s="13" t="n">
+      <c r="H36" s="13" t="n">
         <v>0.9980401763841255</v>
       </c>
-      <c r="H36" s="13" t="n">
+      <c r="I36" s="13" t="n">
         <v>0.007839294463498285</v>
       </c>
-      <c r="I36" s="7" t="inlineStr">
+      <c r="J36" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -4165,22 +4582,27 @@
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E37" s="5" t="inlineStr">
+        <is>
           <t>New Orleans</t>
         </is>
       </c>
-      <c r="E37" s="12" t="n">
+      <c r="F37" s="12" t="n">
         <v>2002</v>
       </c>
-      <c r="F37" s="12" t="n">
+      <c r="G37" s="12" t="n">
         <v>17</v>
       </c>
-      <c r="G37" s="13" t="n">
+      <c r="H37" s="13" t="n">
         <v>0.9745254745254746</v>
       </c>
-      <c r="H37" s="13" t="n">
+      <c r="I37" s="13" t="n">
         <v>0.008491508491508492</v>
       </c>
-      <c r="I37" s="8" t="inlineStr">
+      <c r="J37" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -4202,22 +4624,27 @@
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E38" s="5" t="inlineStr">
+        <is>
           <t>New York</t>
         </is>
       </c>
-      <c r="E38" s="12" t="n">
+      <c r="F38" s="12" t="n">
         <v>1995</v>
       </c>
-      <c r="F38" s="12" t="n">
+      <c r="G38" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="G38" s="13" t="n">
+      <c r="H38" s="13" t="n">
         <v>0.9739348370927319</v>
       </c>
-      <c r="H38" s="13" t="n">
+      <c r="I38" s="13" t="n">
         <v>0.003508771929824561</v>
       </c>
-      <c r="I38" s="7" t="inlineStr">
+      <c r="J38" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -4239,22 +4666,27 @@
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
+          <t>HBSI</t>
+        </is>
+      </c>
+      <c r="E39" s="5" t="inlineStr">
+        <is>
           <t>Las Vegas (and vicinity), NV, US</t>
         </is>
       </c>
-      <c r="E39" s="12" t="n">
+      <c r="F39" s="12" t="n">
         <v>1967</v>
       </c>
-      <c r="F39" s="12" t="n">
+      <c r="G39" s="12" t="n">
         <v>17</v>
       </c>
-      <c r="G39" s="13" t="n">
+      <c r="H39" s="13" t="n">
         <v>0.9898322318251144</v>
       </c>
-      <c r="H39" s="13" t="n">
+      <c r="I39" s="13" t="n">
         <v>0.00864260294865277</v>
       </c>
-      <c r="I39" s="8" t="inlineStr">
+      <c r="J39" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -4276,22 +4708,27 @@
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E40" s="5" t="inlineStr">
+        <is>
           <t>New York</t>
         </is>
       </c>
-      <c r="E40" s="12" t="n">
+      <c r="F40" s="12" t="n">
         <v>1966</v>
       </c>
-      <c r="F40" s="12" t="n">
+      <c r="G40" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="G40" s="13" t="n">
+      <c r="H40" s="13" t="n">
         <v>0.9771108850457783</v>
       </c>
-      <c r="H40" s="13" t="n">
+      <c r="I40" s="13" t="n">
         <v>0.001017293997965412</v>
       </c>
-      <c r="I40" s="7" t="inlineStr">
+      <c r="J40" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -4313,22 +4750,27 @@
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E41" s="5" t="inlineStr">
+        <is>
           <t>Toronto Area</t>
         </is>
       </c>
-      <c r="E41" s="12" t="n">
+      <c r="F41" s="12" t="n">
         <v>1875</v>
       </c>
-      <c r="F41" s="12" t="n">
+      <c r="G41" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="G41" s="13" t="n">
+      <c r="H41" s="13" t="n">
         <v>0.9861333333333333</v>
       </c>
-      <c r="H41" s="13" t="n">
+      <c r="I41" s="13" t="n">
         <v>0.002133333333333333</v>
       </c>
-      <c r="I41" s="7" t="inlineStr">
+      <c r="J41" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -4350,22 +4792,27 @@
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E42" s="5" t="inlineStr">
+        <is>
           <t>Londres</t>
         </is>
       </c>
-      <c r="E42" s="12" t="n">
+      <c r="F42" s="12" t="n">
         <v>1873</v>
       </c>
-      <c r="F42" s="12" t="n">
+      <c r="G42" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="G42" s="13" t="n">
+      <c r="H42" s="13" t="n">
         <v>0.9679658302189001</v>
       </c>
-      <c r="H42" s="13" t="n">
+      <c r="I42" s="13" t="n">
         <v>0.002669514148424987</v>
       </c>
-      <c r="I42" s="7" t="inlineStr">
+      <c r="J42" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -4387,22 +4834,27 @@
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E43" s="5" t="inlineStr">
+        <is>
           <t>Toronto Area</t>
         </is>
       </c>
-      <c r="E43" s="12" t="n">
+      <c r="F43" s="12" t="n">
         <v>1853</v>
       </c>
-      <c r="F43" s="12" t="n">
+      <c r="G43" s="12" t="n">
         <v>24</v>
       </c>
-      <c r="G43" s="13" t="n">
+      <c r="H43" s="13" t="n">
         <v>0.9767943874797625</v>
       </c>
-      <c r="H43" s="13" t="n">
+      <c r="I43" s="13" t="n">
         <v>0.01295196977873718</v>
       </c>
-      <c r="I43" s="8" t="inlineStr">
+      <c r="J43" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -4424,22 +4876,27 @@
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E44" s="5" t="inlineStr">
+        <is>
           <t>French Riviera Area</t>
         </is>
       </c>
-      <c r="E44" s="12" t="n">
+      <c r="F44" s="12" t="n">
         <v>1743</v>
       </c>
-      <c r="F44" s="12" t="n">
+      <c r="G44" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="G44" s="13" t="n">
+      <c r="H44" s="13" t="n">
         <v>0.9845094664371773</v>
       </c>
-      <c r="H44" s="13" t="n">
+      <c r="I44" s="13" t="n">
         <v>0.001147446930579461</v>
       </c>
-      <c r="I44" s="7" t="inlineStr">
+      <c r="J44" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -4461,22 +4918,27 @@
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E45" s="5" t="inlineStr">
+        <is>
           <t>Madrid</t>
         </is>
       </c>
-      <c r="E45" s="12" t="n">
+      <c r="F45" s="12" t="n">
         <v>1700</v>
       </c>
-      <c r="F45" s="12" t="n">
+      <c r="G45" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="G45" s="13" t="n">
+      <c r="H45" s="13" t="n">
         <v>0.971764705882353</v>
       </c>
-      <c r="H45" s="13" t="n">
+      <c r="I45" s="13" t="n">
         <v>0.005882352941176471</v>
       </c>
-      <c r="I45" s="7" t="inlineStr">
+      <c r="J45" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -4498,22 +4960,27 @@
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E46" s="5" t="inlineStr">
+        <is>
           <t>Miami Area</t>
         </is>
       </c>
-      <c r="E46" s="12" t="n">
+      <c r="F46" s="12" t="n">
         <v>1688</v>
       </c>
-      <c r="F46" s="12" t="n">
+      <c r="G46" s="12" t="n">
         <v>19</v>
       </c>
-      <c r="G46" s="13" t="n">
+      <c r="H46" s="13" t="n">
         <v>0.9792654028436019</v>
       </c>
-      <c r="H46" s="13" t="n">
+      <c r="I46" s="13" t="n">
         <v>0.01125592417061611</v>
       </c>
-      <c r="I46" s="8" t="inlineStr">
+      <c r="J46" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -4535,22 +5002,27 @@
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E47" s="5" t="inlineStr">
+        <is>
           <t>Greenville Area</t>
         </is>
       </c>
-      <c r="E47" s="12" t="n">
+      <c r="F47" s="12" t="n">
         <v>1687</v>
       </c>
-      <c r="F47" s="12" t="n">
+      <c r="G47" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="G47" s="13" t="n">
+      <c r="H47" s="13" t="n">
         <v>0.99407231772377</v>
       </c>
-      <c r="H47" s="13" t="n">
+      <c r="I47" s="13" t="n">
         <v>0.001778304682868998</v>
       </c>
-      <c r="I47" s="7" t="inlineStr">
+      <c r="J47" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -4572,22 +5044,27 @@
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E48" s="5" t="inlineStr">
+        <is>
           <t>Miami Area</t>
         </is>
       </c>
-      <c r="E48" s="12" t="n">
+      <c r="F48" s="12" t="n">
         <v>1663</v>
       </c>
-      <c r="F48" s="12" t="n">
+      <c r="G48" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="G48" s="13" t="n">
+      <c r="H48" s="13" t="n">
         <v>0.9446782922429344</v>
       </c>
-      <c r="H48" s="13" t="n">
+      <c r="I48" s="13" t="n">
         <v>0.003006614552014432</v>
       </c>
-      <c r="I48" s="7" t="inlineStr">
+      <c r="J48" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -4609,22 +5086,27 @@
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E49" s="5" t="inlineStr">
+        <is>
           <t>Seattle Area</t>
         </is>
       </c>
-      <c r="E49" s="12" t="n">
+      <c r="F49" s="12" t="n">
         <v>1645</v>
       </c>
-      <c r="F49" s="12" t="n">
+      <c r="G49" s="12" t="n">
         <v>22</v>
       </c>
-      <c r="G49" s="13" t="n">
+      <c r="H49" s="13" t="n">
         <v>0.9951367781155015</v>
       </c>
-      <c r="H49" s="13" t="n">
+      <c r="I49" s="13" t="n">
         <v>0.01337386018237082</v>
       </c>
-      <c r="I49" s="8" t="inlineStr">
+      <c r="J49" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -4646,22 +5128,27 @@
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="E50" s="5" t="inlineStr">
+        <is>
           <t>Punta Cana</t>
         </is>
       </c>
-      <c r="E50" s="12" t="n">
+      <c r="F50" s="12" t="n">
         <v>1629</v>
       </c>
-      <c r="F50" s="12" t="n">
+      <c r="G50" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="G50" s="13" t="n">
+      <c r="H50" s="13" t="n">
         <v>0.9987722529158993</v>
       </c>
-      <c r="H50" s="13" t="n">
+      <c r="I50" s="13" t="n">
         <v>0.005524861878453038</v>
       </c>
-      <c r="I50" s="7" t="inlineStr">
+      <c r="J50" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -4683,22 +5170,27 @@
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
+          <t>Siteminder</t>
+        </is>
+      </c>
+      <c r="E51" s="5" t="inlineStr">
+        <is>
           <t>Riviera Nayarit</t>
         </is>
       </c>
-      <c r="E51" s="12" t="n">
+      <c r="F51" s="12" t="n">
         <v>1601</v>
       </c>
-      <c r="F51" s="12" t="n">
+      <c r="G51" s="12" t="n">
         <v>18</v>
       </c>
-      <c r="G51" s="13" t="n">
+      <c r="H51" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="H51" s="13" t="n">
+      <c r="I51" s="13" t="n">
         <v>0.01124297314178638</v>
       </c>
-      <c r="I51" s="8" t="inlineStr">
+      <c r="J51" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -4720,22 +5212,27 @@
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E52" s="5" t="inlineStr">
+        <is>
           <t>El Cairo Area</t>
         </is>
       </c>
-      <c r="E52" s="12" t="n">
+      <c r="F52" s="12" t="n">
         <v>1556</v>
       </c>
-      <c r="F52" s="12" t="n">
+      <c r="G52" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="G52" s="13" t="n">
+      <c r="H52" s="13" t="n">
         <v>0.9839331619537275</v>
       </c>
-      <c r="H52" s="13" t="n">
+      <c r="I52" s="13" t="n">
         <v>0.001285347043701799</v>
       </c>
-      <c r="I52" s="7" t="inlineStr">
+      <c r="J52" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -4757,22 +5254,27 @@
       </c>
       <c r="D53" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E53" s="5" t="inlineStr">
+        <is>
           <t>Amsterdam</t>
         </is>
       </c>
-      <c r="E53" s="12" t="n">
+      <c r="F53" s="12" t="n">
         <v>1552</v>
       </c>
-      <c r="F53" s="12" t="n">
+      <c r="G53" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G53" s="13" t="n">
+      <c r="H53" s="13" t="n">
         <v>0.9877577319587629</v>
       </c>
-      <c r="H53" s="13" t="n">
+      <c r="I53" s="13" t="n">
         <v>0.0006443298969072165</v>
       </c>
-      <c r="I53" s="7" t="inlineStr">
+      <c r="J53" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -4794,22 +5296,27 @@
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E54" s="5" t="inlineStr">
+        <is>
           <t>Londres</t>
         </is>
       </c>
-      <c r="E54" s="12" t="n">
+      <c r="F54" s="12" t="n">
         <v>1533</v>
       </c>
-      <c r="F54" s="12" t="n">
+      <c r="G54" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="G54" s="13" t="n">
+      <c r="H54" s="13" t="n">
         <v>0.9980430528375733</v>
       </c>
-      <c r="H54" s="13" t="n">
+      <c r="I54" s="13" t="n">
         <v>0.001304631441617743</v>
       </c>
-      <c r="I54" s="7" t="inlineStr">
+      <c r="J54" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -4831,22 +5338,27 @@
       </c>
       <c r="D55" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E55" s="5" t="inlineStr">
+        <is>
           <t>New York</t>
         </is>
       </c>
-      <c r="E55" s="12" t="n">
+      <c r="F55" s="12" t="n">
         <v>1532</v>
       </c>
-      <c r="F55" s="12" t="n">
+      <c r="G55" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="G55" s="13" t="n">
+      <c r="H55" s="13" t="n">
         <v>0.9895561357702349</v>
       </c>
-      <c r="H55" s="13" t="n">
+      <c r="I55" s="13" t="n">
         <v>0.00391644908616188</v>
       </c>
-      <c r="I55" s="7" t="inlineStr">
+      <c r="J55" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -4863,18 +5375,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I55"/>
+  <dimension ref="A1:J55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
     <col width="50" customWidth="1" min="2" max="2"/>
     <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="37" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
-    <col width="11" customWidth="1" min="7" max="7"/>
-    <col width="22" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="37" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4894,7 +5407,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 09/05/2026 05:12 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 14:32 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -4916,30 +5429,35 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
+          <t>Channel</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
           <t>Destino</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="F5" s="3" t="inlineStr">
         <is>
           <t>CR_Unicos</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="G5" s="3" t="inlineStr">
         <is>
           <t>Successful</t>
         </is>
       </c>
-      <c r="G5" s="3" t="inlineStr">
+      <c r="H5" s="3" t="inlineStr">
         <is>
           <t>Bookings</t>
         </is>
       </c>
-      <c r="H5" s="3" t="inlineStr">
+      <c r="I5" s="3" t="inlineStr">
         <is>
           <t>Eficacia</t>
         </is>
       </c>
-      <c r="I5" s="3" t="inlineStr">
+      <c r="J5" s="3" t="inlineStr">
         <is>
           <t>BandaEficacia</t>
         </is>
@@ -4961,22 +5479,27 @@
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
           <t>Abu Dhabi</t>
         </is>
       </c>
-      <c r="E6" s="12" t="n">
+      <c r="F6" s="12" t="n">
         <v>4411</v>
       </c>
-      <c r="F6" s="12" t="n">
+      <c r="G6" s="12" t="n">
         <v>4408</v>
       </c>
-      <c r="G6" s="12" t="n">
+      <c r="H6" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H6" s="13" t="n">
+      <c r="I6" s="13" t="n">
         <v>0.9993198821128996</v>
       </c>
-      <c r="I6" s="10" t="inlineStr">
+      <c r="J6" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -4998,22 +5521,27 @@
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
           <t>El Cairo Area</t>
         </is>
       </c>
-      <c r="E7" s="12" t="n">
+      <c r="F7" s="12" t="n">
         <v>3304</v>
       </c>
-      <c r="F7" s="12" t="n">
+      <c r="G7" s="12" t="n">
         <v>3189</v>
       </c>
-      <c r="G7" s="12" t="n">
+      <c r="H7" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H7" s="13" t="n">
+      <c r="I7" s="13" t="n">
         <v>0.9651937046004843</v>
       </c>
-      <c r="I7" s="9" t="inlineStr">
+      <c r="J7" s="9" t="inlineStr">
         <is>
           <t>Aceptable</t>
         </is>
@@ -5035,22 +5563,27 @@
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
           <t>El Cairo Area</t>
         </is>
       </c>
-      <c r="E8" s="12" t="n">
+      <c r="F8" s="12" t="n">
         <v>2923</v>
       </c>
-      <c r="F8" s="12" t="n">
+      <c r="G8" s="12" t="n">
         <v>2891</v>
       </c>
-      <c r="G8" s="12" t="n">
+      <c r="H8" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H8" s="13" t="n">
+      <c r="I8" s="13" t="n">
         <v>0.9890523434827232</v>
       </c>
-      <c r="I8" s="10" t="inlineStr">
+      <c r="J8" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -5072,22 +5605,27 @@
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
+          <t>HBSI</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
           <t>Las Vegas (and vicinity), NV, US</t>
         </is>
       </c>
-      <c r="E9" s="12" t="n">
+      <c r="F9" s="12" t="n">
         <v>2861</v>
       </c>
-      <c r="F9" s="12" t="n">
+      <c r="G9" s="12" t="n">
         <v>284</v>
       </c>
-      <c r="G9" s="12" t="n">
+      <c r="H9" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H9" s="13" t="n">
+      <c r="I9" s="13" t="n">
         <v>0.09926599091226844</v>
       </c>
-      <c r="I9" s="4" t="inlineStr">
+      <c r="J9" s="4" t="inlineStr">
         <is>
           <t>Súper Crítica</t>
         </is>
@@ -5109,22 +5647,27 @@
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
+          <t>HBSI</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
           <t>Las Vegas (and vicinity), NV, US</t>
         </is>
       </c>
-      <c r="E10" s="12" t="n">
+      <c r="F10" s="12" t="n">
         <v>2637</v>
       </c>
-      <c r="F10" s="12" t="n">
+      <c r="G10" s="12" t="n">
         <v>480</v>
       </c>
-      <c r="G10" s="12" t="n">
+      <c r="H10" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H10" s="13" t="n">
+      <c r="I10" s="13" t="n">
         <v>0.1820250284414107</v>
       </c>
-      <c r="I10" s="4" t="inlineStr">
+      <c r="J10" s="4" t="inlineStr">
         <is>
           <t>Súper Crítica</t>
         </is>
@@ -5146,22 +5689,27 @@
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
           <t>Dubai Area</t>
         </is>
       </c>
-      <c r="E11" s="12" t="n">
+      <c r="F11" s="12" t="n">
         <v>2424</v>
       </c>
-      <c r="F11" s="12" t="n">
+      <c r="G11" s="12" t="n">
         <v>2100</v>
       </c>
-      <c r="G11" s="12" t="n">
+      <c r="H11" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H11" s="13" t="n">
+      <c r="I11" s="13" t="n">
         <v>0.8663366336633663</v>
       </c>
-      <c r="I11" s="8" t="inlineStr">
+      <c r="J11" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -5183,22 +5731,27 @@
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
           <t>Istanbul Area</t>
         </is>
       </c>
-      <c r="E12" s="12" t="n">
+      <c r="F12" s="12" t="n">
         <v>2022</v>
       </c>
-      <c r="F12" s="12" t="n">
+      <c r="G12" s="12" t="n">
         <v>2003</v>
       </c>
-      <c r="G12" s="12" t="n">
+      <c r="H12" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H12" s="13" t="n">
+      <c r="I12" s="13" t="n">
         <v>0.9906033630069239</v>
       </c>
-      <c r="I12" s="10" t="inlineStr">
+      <c r="J12" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -5220,22 +5773,27 @@
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
           <t>El Cairo Area</t>
         </is>
       </c>
-      <c r="E13" s="12" t="n">
+      <c r="F13" s="12" t="n">
         <v>1937</v>
       </c>
-      <c r="F13" s="12" t="n">
+      <c r="G13" s="12" t="n">
         <v>1930</v>
       </c>
-      <c r="G13" s="12" t="n">
+      <c r="H13" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H13" s="13" t="n">
+      <c r="I13" s="13" t="n">
         <v>0.996386164171399</v>
       </c>
-      <c r="I13" s="10" t="inlineStr">
+      <c r="J13" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -5257,22 +5815,27 @@
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
           <t>Amsterdam</t>
         </is>
       </c>
-      <c r="E14" s="12" t="n">
+      <c r="F14" s="12" t="n">
         <v>1709</v>
       </c>
-      <c r="F14" s="12" t="n">
+      <c r="G14" s="12" t="n">
         <v>1661</v>
       </c>
-      <c r="G14" s="12" t="n">
+      <c r="H14" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H14" s="13" t="n">
+      <c r="I14" s="13" t="n">
         <v>0.9719133996489175</v>
       </c>
-      <c r="I14" s="10" t="inlineStr">
+      <c r="J14" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -5294,22 +5857,27 @@
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
           <t>Paris</t>
         </is>
       </c>
-      <c r="E15" s="12" t="n">
+      <c r="F15" s="12" t="n">
         <v>1566</v>
       </c>
-      <c r="F15" s="12" t="n">
+      <c r="G15" s="12" t="n">
         <v>1546</v>
       </c>
-      <c r="G15" s="12" t="n">
+      <c r="H15" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H15" s="13" t="n">
+      <c r="I15" s="13" t="n">
         <v>0.9872286079182631</v>
       </c>
-      <c r="I15" s="10" t="inlineStr">
+      <c r="J15" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -5331,22 +5899,27 @@
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
           <t>New York</t>
         </is>
       </c>
-      <c r="E16" s="12" t="n">
+      <c r="F16" s="12" t="n">
         <v>1414</v>
       </c>
-      <c r="F16" s="12" t="n">
+      <c r="G16" s="12" t="n">
         <v>1355</v>
       </c>
-      <c r="G16" s="12" t="n">
+      <c r="H16" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H16" s="13" t="n">
+      <c r="I16" s="13" t="n">
         <v>0.9582743988684582</v>
       </c>
-      <c r="I16" s="9" t="inlineStr">
+      <c r="J16" s="9" t="inlineStr">
         <is>
           <t>Aceptable</t>
         </is>
@@ -5368,22 +5941,27 @@
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
           <t>Sharm el Sheikh Area</t>
         </is>
-      </c>
-      <c r="E17" s="12" t="n">
-        <v>1359</v>
       </c>
       <c r="F17" s="12" t="n">
         <v>1359</v>
       </c>
       <c r="G17" s="12" t="n">
+        <v>1359</v>
+      </c>
+      <c r="H17" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H17" s="13" t="n">
+      <c r="I17" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="I17" s="10" t="inlineStr">
+      <c r="J17" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -5405,22 +5983,27 @@
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
           <t>SinClasificar</t>
         </is>
       </c>
-      <c r="E18" s="12" t="n">
+      <c r="F18" s="12" t="n">
         <v>1356</v>
       </c>
-      <c r="F18" s="12" t="n">
+      <c r="G18" s="12" t="n">
         <v>1052</v>
       </c>
-      <c r="G18" s="12" t="n">
+      <c r="H18" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H18" s="13" t="n">
+      <c r="I18" s="13" t="n">
         <v>0.775811209439528</v>
       </c>
-      <c r="I18" s="7" t="inlineStr">
+      <c r="J18" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -5442,22 +6025,27 @@
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
           <t>Adjara Area</t>
         </is>
       </c>
-      <c r="E19" s="12" t="n">
+      <c r="F19" s="12" t="n">
         <v>1350</v>
       </c>
-      <c r="F19" s="12" t="n">
+      <c r="G19" s="12" t="n">
         <v>1301</v>
       </c>
-      <c r="G19" s="12" t="n">
+      <c r="H19" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H19" s="13" t="n">
+      <c r="I19" s="13" t="n">
         <v>0.9637037037037037</v>
       </c>
-      <c r="I19" s="9" t="inlineStr">
+      <c r="J19" s="9" t="inlineStr">
         <is>
           <t>Aceptable</t>
         </is>
@@ -5479,22 +6067,27 @@
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
           <t>New York</t>
         </is>
       </c>
-      <c r="E20" s="12" t="n">
+      <c r="F20" s="12" t="n">
         <v>1337</v>
       </c>
-      <c r="F20" s="12" t="n">
+      <c r="G20" s="12" t="n">
         <v>1315</v>
       </c>
-      <c r="G20" s="12" t="n">
+      <c r="H20" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H20" s="13" t="n">
+      <c r="I20" s="13" t="n">
         <v>0.9835452505609573</v>
       </c>
-      <c r="I20" s="10" t="inlineStr">
+      <c r="J20" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -5516,22 +6109,27 @@
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
           <t>Paris</t>
         </is>
       </c>
-      <c r="E21" s="12" t="n">
+      <c r="F21" s="12" t="n">
         <v>1264</v>
       </c>
-      <c r="F21" s="12" t="n">
+      <c r="G21" s="12" t="n">
         <v>1254</v>
       </c>
-      <c r="G21" s="12" t="n">
+      <c r="H21" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H21" s="13" t="n">
+      <c r="I21" s="13" t="n">
         <v>0.9920886075949367</v>
       </c>
-      <c r="I21" s="10" t="inlineStr">
+      <c r="J21" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -5553,22 +6151,27 @@
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="inlineStr">
+        <is>
           <t>New York</t>
         </is>
-      </c>
-      <c r="E22" s="12" t="n">
-        <v>1218</v>
       </c>
       <c r="F22" s="12" t="n">
         <v>1218</v>
       </c>
       <c r="G22" s="12" t="n">
+        <v>1218</v>
+      </c>
+      <c r="H22" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H22" s="13" t="n">
+      <c r="I22" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="I22" s="10" t="inlineStr">
+      <c r="J22" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -5590,22 +6193,27 @@
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
           <t>Istanbul Area</t>
         </is>
-      </c>
-      <c r="E23" s="12" t="n">
-        <v>1193</v>
       </c>
       <c r="F23" s="12" t="n">
         <v>1193</v>
       </c>
       <c r="G23" s="12" t="n">
+        <v>1193</v>
+      </c>
+      <c r="H23" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H23" s="13" t="n">
+      <c r="I23" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="I23" s="10" t="inlineStr">
+      <c r="J23" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -5627,22 +6235,27 @@
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E24" s="5" t="inlineStr">
+        <is>
           <t>Istanbul Area</t>
         </is>
       </c>
-      <c r="E24" s="12" t="n">
+      <c r="F24" s="12" t="n">
         <v>1182</v>
       </c>
-      <c r="F24" s="12" t="n">
+      <c r="G24" s="12" t="n">
         <v>1176</v>
       </c>
-      <c r="G24" s="12" t="n">
+      <c r="H24" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H24" s="13" t="n">
+      <c r="I24" s="13" t="n">
         <v>0.9949238578680203</v>
       </c>
-      <c r="I24" s="10" t="inlineStr">
+      <c r="J24" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -5664,22 +6277,27 @@
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
           <t>Ras Al Khaimah Area</t>
         </is>
       </c>
-      <c r="E25" s="12" t="n">
+      <c r="F25" s="12" t="n">
         <v>1178</v>
       </c>
-      <c r="F25" s="12" t="n">
+      <c r="G25" s="12" t="n">
         <v>1085</v>
       </c>
-      <c r="G25" s="12" t="n">
+      <c r="H25" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H25" s="13" t="n">
+      <c r="I25" s="13" t="n">
         <v>0.9210526315789473</v>
       </c>
-      <c r="I25" s="8" t="inlineStr">
+      <c r="J25" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -5701,22 +6319,27 @@
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
+          <t>Expedia</t>
+        </is>
+      </c>
+      <c r="E26" s="5" t="inlineStr">
+        <is>
           <t>Miami Area</t>
         </is>
       </c>
-      <c r="E26" s="12" t="n">
+      <c r="F26" s="12" t="n">
         <v>1141</v>
       </c>
-      <c r="F26" s="12" t="n">
+      <c r="G26" s="12" t="n">
         <v>1099</v>
       </c>
-      <c r="G26" s="12" t="n">
+      <c r="H26" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H26" s="13" t="n">
+      <c r="I26" s="13" t="n">
         <v>0.9631901840490797</v>
       </c>
-      <c r="I26" s="9" t="inlineStr">
+      <c r="J26" s="9" t="inlineStr">
         <is>
           <t>Aceptable</t>
         </is>
@@ -5738,22 +6361,27 @@
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="E27" s="5" t="inlineStr">
+        <is>
           <t>Cancún</t>
         </is>
       </c>
-      <c r="E27" s="12" t="n">
+      <c r="F27" s="12" t="n">
         <v>1111</v>
-      </c>
-      <c r="F27" s="12" t="n">
-        <v>0</v>
       </c>
       <c r="G27" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H27" s="13" t="n">
+      <c r="H27" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="I27" s="4" t="inlineStr">
+      <c r="I27" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" s="4" t="inlineStr">
         <is>
           <t>Súper Crítica</t>
         </is>
@@ -5775,22 +6403,27 @@
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E28" s="5" t="inlineStr">
+        <is>
           <t>Jeddah Area</t>
         </is>
       </c>
-      <c r="E28" s="12" t="n">
+      <c r="F28" s="12" t="n">
         <v>1086</v>
       </c>
-      <c r="F28" s="12" t="n">
+      <c r="G28" s="12" t="n">
         <v>1063</v>
       </c>
-      <c r="G28" s="12" t="n">
+      <c r="H28" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H28" s="13" t="n">
+      <c r="I28" s="13" t="n">
         <v>0.9788213627992634</v>
       </c>
-      <c r="I28" s="10" t="inlineStr">
+      <c r="J28" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -5812,22 +6445,27 @@
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E29" s="5" t="inlineStr">
+        <is>
           <t>El Cairo Area</t>
         </is>
       </c>
-      <c r="E29" s="12" t="n">
+      <c r="F29" s="12" t="n">
         <v>1064</v>
       </c>
-      <c r="F29" s="12" t="n">
+      <c r="G29" s="12" t="n">
         <v>1062</v>
       </c>
-      <c r="G29" s="12" t="n">
+      <c r="H29" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H29" s="13" t="n">
+      <c r="I29" s="13" t="n">
         <v>0.9981203007518797</v>
       </c>
-      <c r="I29" s="10" t="inlineStr">
+      <c r="J29" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -5849,22 +6487,27 @@
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E30" s="5" t="inlineStr">
+        <is>
           <t>New York</t>
         </is>
       </c>
-      <c r="E30" s="12" t="n">
+      <c r="F30" s="12" t="n">
         <v>1058</v>
       </c>
-      <c r="F30" s="12" t="n">
+      <c r="G30" s="12" t="n">
         <v>1043</v>
       </c>
-      <c r="G30" s="12" t="n">
+      <c r="H30" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H30" s="13" t="n">
+      <c r="I30" s="13" t="n">
         <v>0.9858223062381852</v>
       </c>
-      <c r="I30" s="10" t="inlineStr">
+      <c r="J30" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -5886,22 +6529,27 @@
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E31" s="5" t="inlineStr">
+        <is>
           <t>Berlin Area</t>
         </is>
       </c>
-      <c r="E31" s="12" t="n">
+      <c r="F31" s="12" t="n">
         <v>1007</v>
       </c>
-      <c r="F31" s="12" t="n">
+      <c r="G31" s="12" t="n">
         <v>918</v>
       </c>
-      <c r="G31" s="12" t="n">
+      <c r="H31" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H31" s="13" t="n">
+      <c r="I31" s="13" t="n">
         <v>0.9116186693147964</v>
       </c>
-      <c r="I31" s="8" t="inlineStr">
+      <c r="J31" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -5923,22 +6571,27 @@
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E32" s="5" t="inlineStr">
+        <is>
           <t>Tbilisi Area</t>
         </is>
-      </c>
-      <c r="E32" s="12" t="n">
-        <v>995</v>
       </c>
       <c r="F32" s="12" t="n">
         <v>995</v>
       </c>
       <c r="G32" s="12" t="n">
+        <v>995</v>
+      </c>
+      <c r="H32" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H32" s="13" t="n">
+      <c r="I32" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="I32" s="10" t="inlineStr">
+      <c r="J32" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -5960,22 +6613,27 @@
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E33" s="5" t="inlineStr">
+        <is>
           <t>Ras Al Khaimah Area</t>
         </is>
       </c>
-      <c r="E33" s="12" t="n">
+      <c r="F33" s="12" t="n">
         <v>992</v>
       </c>
-      <c r="F33" s="12" t="n">
+      <c r="G33" s="12" t="n">
         <v>978</v>
       </c>
-      <c r="G33" s="12" t="n">
+      <c r="H33" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H33" s="13" t="n">
+      <c r="I33" s="13" t="n">
         <v>0.9858870967741935</v>
       </c>
-      <c r="I33" s="10" t="inlineStr">
+      <c r="J33" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -5997,22 +6655,27 @@
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E34" s="5" t="inlineStr">
+        <is>
           <t>Dubai Area</t>
         </is>
       </c>
-      <c r="E34" s="12" t="n">
+      <c r="F34" s="12" t="n">
         <v>985</v>
       </c>
-      <c r="F34" s="12" t="n">
+      <c r="G34" s="12" t="n">
         <v>846</v>
       </c>
-      <c r="G34" s="12" t="n">
+      <c r="H34" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H34" s="13" t="n">
+      <c r="I34" s="13" t="n">
         <v>0.8588832487309644</v>
       </c>
-      <c r="I34" s="8" t="inlineStr">
+      <c r="J34" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -6034,22 +6697,27 @@
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E35" s="5" t="inlineStr">
+        <is>
           <t>Londres</t>
         </is>
       </c>
-      <c r="E35" s="12" t="n">
+      <c r="F35" s="12" t="n">
         <v>959</v>
       </c>
-      <c r="F35" s="12" t="n">
+      <c r="G35" s="12" t="n">
         <v>956</v>
       </c>
-      <c r="G35" s="12" t="n">
+      <c r="H35" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H35" s="13" t="n">
+      <c r="I35" s="13" t="n">
         <v>0.9968717413972888</v>
       </c>
-      <c r="I35" s="10" t="inlineStr">
+      <c r="J35" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -6071,22 +6739,27 @@
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E36" s="5" t="inlineStr">
+        <is>
           <t>Atlanta Area</t>
         </is>
       </c>
-      <c r="E36" s="12" t="n">
+      <c r="F36" s="12" t="n">
         <v>952</v>
       </c>
-      <c r="F36" s="12" t="n">
+      <c r="G36" s="12" t="n">
         <v>921</v>
       </c>
-      <c r="G36" s="12" t="n">
+      <c r="H36" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H36" s="13" t="n">
+      <c r="I36" s="13" t="n">
         <v>0.967436974789916</v>
       </c>
-      <c r="I36" s="9" t="inlineStr">
+      <c r="J36" s="9" t="inlineStr">
         <is>
           <t>Aceptable</t>
         </is>
@@ -6108,22 +6781,27 @@
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E37" s="5" t="inlineStr">
+        <is>
           <t>Dubai Area</t>
         </is>
       </c>
-      <c r="E37" s="12" t="n">
+      <c r="F37" s="12" t="n">
         <v>929</v>
       </c>
-      <c r="F37" s="12" t="n">
+      <c r="G37" s="12" t="n">
         <v>842</v>
       </c>
-      <c r="G37" s="12" t="n">
+      <c r="H37" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H37" s="13" t="n">
+      <c r="I37" s="13" t="n">
         <v>0.9063509149623251</v>
       </c>
-      <c r="I37" s="8" t="inlineStr">
+      <c r="J37" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -6145,22 +6823,27 @@
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E38" s="5" t="inlineStr">
+        <is>
           <t>Los Angeles (and vicinity), CA, US</t>
         </is>
       </c>
-      <c r="E38" s="12" t="n">
+      <c r="F38" s="12" t="n">
         <v>921</v>
       </c>
-      <c r="F38" s="12" t="n">
+      <c r="G38" s="12" t="n">
         <v>905</v>
       </c>
-      <c r="G38" s="12" t="n">
+      <c r="H38" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H38" s="13" t="n">
+      <c r="I38" s="13" t="n">
         <v>0.9826275787187839</v>
       </c>
-      <c r="I38" s="10" t="inlineStr">
+      <c r="J38" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -6182,22 +6865,27 @@
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E39" s="5" t="inlineStr">
+        <is>
           <t>Orlando</t>
         </is>
       </c>
-      <c r="E39" s="12" t="n">
+      <c r="F39" s="12" t="n">
         <v>899</v>
       </c>
-      <c r="F39" s="12" t="n">
+      <c r="G39" s="12" t="n">
         <v>897</v>
       </c>
-      <c r="G39" s="12" t="n">
+      <c r="H39" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H39" s="13" t="n">
+      <c r="I39" s="13" t="n">
         <v>0.9977753058954394</v>
       </c>
-      <c r="I39" s="10" t="inlineStr">
+      <c r="J39" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -6219,22 +6907,27 @@
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E40" s="5" t="inlineStr">
+        <is>
           <t>New York</t>
         </is>
-      </c>
-      <c r="E40" s="12" t="n">
-        <v>869</v>
       </c>
       <c r="F40" s="12" t="n">
         <v>869</v>
       </c>
       <c r="G40" s="12" t="n">
+        <v>869</v>
+      </c>
+      <c r="H40" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H40" s="13" t="n">
+      <c r="I40" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="I40" s="10" t="inlineStr">
+      <c r="J40" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -6256,22 +6949,27 @@
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E41" s="5" t="inlineStr">
+        <is>
           <t>Amsterdam</t>
         </is>
       </c>
-      <c r="E41" s="12" t="n">
+      <c r="F41" s="12" t="n">
         <v>845</v>
       </c>
-      <c r="F41" s="12" t="n">
+      <c r="G41" s="12" t="n">
         <v>830</v>
       </c>
-      <c r="G41" s="12" t="n">
+      <c r="H41" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H41" s="13" t="n">
+      <c r="I41" s="13" t="n">
         <v>0.9822485207100592</v>
       </c>
-      <c r="I41" s="10" t="inlineStr">
+      <c r="J41" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -6293,22 +6991,27 @@
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E42" s="5" t="inlineStr">
+        <is>
           <t>New York</t>
         </is>
       </c>
-      <c r="E42" s="12" t="n">
+      <c r="F42" s="12" t="n">
         <v>841</v>
       </c>
-      <c r="F42" s="12" t="n">
+      <c r="G42" s="12" t="n">
         <v>711</v>
       </c>
-      <c r="G42" s="12" t="n">
+      <c r="H42" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H42" s="13" t="n">
+      <c r="I42" s="13" t="n">
         <v>0.845422116527943</v>
       </c>
-      <c r="I42" s="7" t="inlineStr">
+      <c r="J42" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -6330,22 +7033,27 @@
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E43" s="5" t="inlineStr">
+        <is>
           <t>Vienna Area</t>
         </is>
       </c>
-      <c r="E43" s="12" t="n">
+      <c r="F43" s="12" t="n">
         <v>829</v>
       </c>
-      <c r="F43" s="12" t="n">
+      <c r="G43" s="12" t="n">
         <v>827</v>
       </c>
-      <c r="G43" s="12" t="n">
+      <c r="H43" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H43" s="13" t="n">
+      <c r="I43" s="13" t="n">
         <v>0.9975874547647768</v>
       </c>
-      <c r="I43" s="10" t="inlineStr">
+      <c r="J43" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -6367,22 +7075,27 @@
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E44" s="5" t="inlineStr">
+        <is>
           <t>Los Angeles (and vicinity), CA, US</t>
         </is>
       </c>
-      <c r="E44" s="12" t="n">
+      <c r="F44" s="12" t="n">
         <v>809</v>
       </c>
-      <c r="F44" s="12" t="n">
+      <c r="G44" s="12" t="n">
         <v>448</v>
       </c>
-      <c r="G44" s="12" t="n">
+      <c r="H44" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H44" s="13" t="n">
+      <c r="I44" s="13" t="n">
         <v>0.553770086526576</v>
       </c>
-      <c r="I44" s="4" t="inlineStr">
+      <c r="J44" s="4" t="inlineStr">
         <is>
           <t>Súper Crítica</t>
         </is>
@@ -6404,22 +7117,27 @@
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E45" s="5" t="inlineStr">
+        <is>
           <t>Veneto Area</t>
         </is>
       </c>
-      <c r="E45" s="12" t="n">
+      <c r="F45" s="12" t="n">
         <v>803</v>
       </c>
-      <c r="F45" s="12" t="n">
+      <c r="G45" s="12" t="n">
         <v>499</v>
       </c>
-      <c r="G45" s="12" t="n">
+      <c r="H45" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H45" s="13" t="n">
+      <c r="I45" s="13" t="n">
         <v>0.6214196762141968</v>
       </c>
-      <c r="I45" s="7" t="inlineStr">
+      <c r="J45" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -6441,22 +7159,27 @@
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="E46" s="5" t="inlineStr">
+        <is>
           <t>Cancún</t>
         </is>
-      </c>
-      <c r="E46" s="12" t="n">
-        <v>725</v>
       </c>
       <c r="F46" s="12" t="n">
         <v>725</v>
       </c>
       <c r="G46" s="12" t="n">
+        <v>725</v>
+      </c>
+      <c r="H46" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H46" s="13" t="n">
+      <c r="I46" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="I46" s="10" t="inlineStr">
+      <c r="J46" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -6478,22 +7201,27 @@
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E47" s="5" t="inlineStr">
+        <is>
           <t>New York</t>
         </is>
-      </c>
-      <c r="E47" s="12" t="n">
-        <v>713</v>
       </c>
       <c r="F47" s="12" t="n">
         <v>713</v>
       </c>
       <c r="G47" s="12" t="n">
+        <v>713</v>
+      </c>
+      <c r="H47" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H47" s="13" t="n">
+      <c r="I47" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="I47" s="10" t="inlineStr">
+      <c r="J47" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -6515,22 +7243,27 @@
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E48" s="5" t="inlineStr">
+        <is>
           <t>El Cairo Area</t>
         </is>
       </c>
-      <c r="E48" s="12" t="n">
+      <c r="F48" s="12" t="n">
         <v>706</v>
       </c>
-      <c r="F48" s="12" t="n">
+      <c r="G48" s="12" t="n">
         <v>685</v>
       </c>
-      <c r="G48" s="12" t="n">
+      <c r="H48" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H48" s="13" t="n">
+      <c r="I48" s="13" t="n">
         <v>0.9702549575070821</v>
       </c>
-      <c r="I48" s="10" t="inlineStr">
+      <c r="J48" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -6552,22 +7285,27 @@
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
+          <t>Expedia</t>
+        </is>
+      </c>
+      <c r="E49" s="5" t="inlineStr">
+        <is>
           <t>Dubai Area</t>
         </is>
-      </c>
-      <c r="E49" s="12" t="n">
-        <v>691</v>
       </c>
       <c r="F49" s="12" t="n">
         <v>691</v>
       </c>
       <c r="G49" s="12" t="n">
+        <v>691</v>
+      </c>
+      <c r="H49" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H49" s="13" t="n">
+      <c r="I49" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="I49" s="10" t="inlineStr">
+      <c r="J49" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -6589,22 +7327,27 @@
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E50" s="5" t="inlineStr">
+        <is>
           <t>Bali Area</t>
         </is>
       </c>
-      <c r="E50" s="12" t="n">
+      <c r="F50" s="12" t="n">
         <v>679</v>
       </c>
-      <c r="F50" s="12" t="n">
+      <c r="G50" s="12" t="n">
         <v>678</v>
       </c>
-      <c r="G50" s="12" t="n">
+      <c r="H50" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H50" s="13" t="n">
+      <c r="I50" s="13" t="n">
         <v>0.9985272459499264</v>
       </c>
-      <c r="I50" s="10" t="inlineStr">
+      <c r="J50" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -6626,22 +7369,27 @@
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E51" s="5" t="inlineStr">
+        <is>
           <t>Key Largo Area</t>
         </is>
       </c>
-      <c r="E51" s="12" t="n">
+      <c r="F51" s="12" t="n">
         <v>677</v>
       </c>
-      <c r="F51" s="12" t="n">
+      <c r="G51" s="12" t="n">
         <v>522</v>
       </c>
-      <c r="G51" s="12" t="n">
+      <c r="H51" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H51" s="13" t="n">
+      <c r="I51" s="13" t="n">
         <v>0.7710487444608567</v>
       </c>
-      <c r="I51" s="7" t="inlineStr">
+      <c r="J51" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -6663,22 +7411,27 @@
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E52" s="5" t="inlineStr">
+        <is>
           <t>New York</t>
         </is>
       </c>
-      <c r="E52" s="12" t="n">
+      <c r="F52" s="12" t="n">
         <v>674</v>
       </c>
-      <c r="F52" s="12" t="n">
+      <c r="G52" s="12" t="n">
         <v>552</v>
       </c>
-      <c r="G52" s="12" t="n">
+      <c r="H52" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H52" s="13" t="n">
+      <c r="I52" s="13" t="n">
         <v>0.8189910979228486</v>
       </c>
-      <c r="I52" s="7" t="inlineStr">
+      <c r="J52" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -6700,22 +7453,27 @@
       </c>
       <c r="D53" s="5" t="inlineStr">
         <is>
+          <t>Expedia</t>
+        </is>
+      </c>
+      <c r="E53" s="5" t="inlineStr">
+        <is>
           <t>Paphos Area</t>
         </is>
       </c>
-      <c r="E53" s="12" t="n">
+      <c r="F53" s="12" t="n">
         <v>673</v>
       </c>
-      <c r="F53" s="12" t="n">
+      <c r="G53" s="12" t="n">
         <v>667</v>
       </c>
-      <c r="G53" s="12" t="n">
+      <c r="H53" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H53" s="13" t="n">
+      <c r="I53" s="13" t="n">
         <v>0.9910846953937593</v>
       </c>
-      <c r="I53" s="10" t="inlineStr">
+      <c r="J53" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -6737,22 +7495,27 @@
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E54" s="5" t="inlineStr">
+        <is>
           <t>Cancún</t>
         </is>
       </c>
-      <c r="E54" s="12" t="n">
+      <c r="F54" s="12" t="n">
         <v>648</v>
       </c>
-      <c r="F54" s="12" t="n">
+      <c r="G54" s="12" t="n">
         <v>600</v>
       </c>
-      <c r="G54" s="12" t="n">
+      <c r="H54" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H54" s="13" t="n">
+      <c r="I54" s="13" t="n">
         <v>0.9259259259259259</v>
       </c>
-      <c r="I54" s="8" t="inlineStr">
+      <c r="J54" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -6774,22 +7537,27 @@
       </c>
       <c r="D55" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E55" s="5" t="inlineStr">
+        <is>
           <t>Daytona Beach Area</t>
         </is>
       </c>
-      <c r="E55" s="12" t="n">
+      <c r="F55" s="12" t="n">
         <v>644</v>
       </c>
-      <c r="F55" s="12" t="n">
+      <c r="G55" s="12" t="n">
         <v>641</v>
       </c>
-      <c r="G55" s="12" t="n">
+      <c r="H55" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H55" s="13" t="n">
+      <c r="I55" s="13" t="n">
         <v>0.9953416149068323</v>
       </c>
-      <c r="I55" s="10" t="inlineStr">
+      <c r="J55" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -6837,7 +7605,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 09/05/2026 05:12 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 14:32 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -8680,7 +9448,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 09/05/2026 05:12 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 14:32 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -10492,18 +11260,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I15"/>
+  <dimension ref="A1:J15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="23" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="11" customWidth="1" min="5" max="5"/>
-    <col width="21" customWidth="1" min="6" max="6"/>
-    <col width="24" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="21" customWidth="1" min="7" max="7"/>
+    <col width="24" customWidth="1" min="8" max="8"/>
     <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -10523,7 +11292,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 09/05/2026 05:12 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 14:32 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -10535,40 +11304,45 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>ExternalProviderName</t>
+          <t>Channel</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
+          <t>Grupo</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
           <t>CR_Unicos</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="E5" s="3" t="inlineStr">
         <is>
           <t>Successful</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="F5" s="3" t="inlineStr">
         <is>
           <t>Bookings</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="G5" s="3" t="inlineStr">
         <is>
           <t>Eficacia</t>
         </is>
       </c>
-      <c r="G5" s="3" t="inlineStr">
+      <c r="H5" s="3" t="inlineStr">
         <is>
           <t>ConvRate</t>
         </is>
       </c>
-      <c r="H5" s="3" t="inlineStr">
+      <c r="I5" s="3" t="inlineStr">
         <is>
           <t>BandaEficacia</t>
         </is>
       </c>
-      <c r="I5" s="3" t="inlineStr">
+      <c r="J5" s="3" t="inlineStr">
         <is>
           <t>BandaConvRate</t>
         </is>
@@ -10583,27 +11357,32 @@
           <t>DerbySoft</t>
         </is>
       </c>
-      <c r="C6" s="12" t="n">
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>Producto Propio</t>
+        </is>
+      </c>
+      <c r="D6" s="12" t="n">
         <v>1070257</v>
       </c>
-      <c r="D6" s="12" t="n">
+      <c r="E6" s="12" t="n">
         <v>1018135</v>
       </c>
-      <c r="E6" s="12" t="n">
+      <c r="F6" s="12" t="n">
         <v>12351</v>
       </c>
-      <c r="F6" s="13" t="n">
+      <c r="G6" s="13" t="n">
         <v>0.9512995476787351</v>
       </c>
-      <c r="G6" s="13" t="n">
+      <c r="H6" s="13" t="n">
         <v>0.01154021884463264</v>
       </c>
-      <c r="H6" s="9" t="inlineStr">
+      <c r="I6" s="9" t="inlineStr">
         <is>
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I6" s="5" t="inlineStr">
+      <c r="J6" s="5" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -10618,27 +11397,32 @@
           <t>Internal</t>
         </is>
       </c>
-      <c r="C7" s="12" t="n">
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>Producto Propio</t>
+        </is>
+      </c>
+      <c r="D7" s="12" t="n">
         <v>90490</v>
       </c>
-      <c r="D7" s="12" t="n">
+      <c r="E7" s="12" t="n">
         <v>84007</v>
       </c>
-      <c r="E7" s="12" t="n">
+      <c r="F7" s="12" t="n">
         <v>1754</v>
       </c>
-      <c r="F7" s="13" t="n">
+      <c r="G7" s="13" t="n">
         <v>0.9283567244999448</v>
       </c>
-      <c r="G7" s="13" t="n">
+      <c r="H7" s="13" t="n">
         <v>0.01938335727704719</v>
       </c>
-      <c r="H7" s="8" t="inlineStr">
+      <c r="I7" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I7" s="5" t="inlineStr">
+      <c r="J7" s="5" t="inlineStr">
         <is>
           <t>Aceptable</t>
         </is>
@@ -10653,27 +11437,32 @@
           <t>Expedia</t>
         </is>
       </c>
-      <c r="C8" s="12" t="n">
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>Third Party</t>
+        </is>
+      </c>
+      <c r="D8" s="12" t="n">
         <v>55316</v>
       </c>
-      <c r="D8" s="12" t="n">
+      <c r="E8" s="12" t="n">
         <v>53044</v>
       </c>
-      <c r="E8" s="12" t="n">
+      <c r="F8" s="12" t="n">
         <v>57</v>
       </c>
-      <c r="F8" s="13" t="n">
+      <c r="G8" s="13" t="n">
         <v>0.9589268927615879</v>
       </c>
-      <c r="G8" s="13" t="n">
+      <c r="H8" s="13" t="n">
         <v>0.001030443271386217</v>
       </c>
-      <c r="H8" s="9" t="inlineStr">
+      <c r="I8" s="9" t="inlineStr">
         <is>
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I8" s="5" t="inlineStr">
+      <c r="J8" s="5" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -10688,27 +11477,32 @@
           <t>HBSI</t>
         </is>
       </c>
-      <c r="C9" s="12" t="n">
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>Producto Propio</t>
+        </is>
+      </c>
+      <c r="D9" s="12" t="n">
         <v>54935</v>
       </c>
-      <c r="D9" s="12" t="n">
+      <c r="E9" s="12" t="n">
         <v>46651</v>
       </c>
-      <c r="E9" s="12" t="n">
+      <c r="F9" s="12" t="n">
         <v>714</v>
       </c>
-      <c r="F9" s="13" t="n">
+      <c r="G9" s="13" t="n">
         <v>0.8492036042595795</v>
       </c>
-      <c r="G9" s="13" t="n">
+      <c r="H9" s="13" t="n">
         <v>0.01299717848366251</v>
       </c>
-      <c r="H9" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
-        </is>
-      </c>
-      <c r="I9" s="5" t="inlineStr">
+      <c r="I9" s="7" t="inlineStr">
+        <is>
+          <t>Crítica</t>
+        </is>
+      </c>
+      <c r="J9" s="5" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -10723,27 +11517,32 @@
           <t>SynXis</t>
         </is>
       </c>
-      <c r="C10" s="12" t="n">
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>Producto Propio</t>
+        </is>
+      </c>
+      <c r="D10" s="12" t="n">
         <v>15318</v>
       </c>
-      <c r="D10" s="12" t="n">
+      <c r="E10" s="12" t="n">
         <v>15168</v>
       </c>
-      <c r="E10" s="12" t="n">
+      <c r="F10" s="12" t="n">
         <v>159</v>
       </c>
-      <c r="F10" s="13" t="n">
+      <c r="G10" s="13" t="n">
         <v>0.9902075989032511</v>
       </c>
-      <c r="G10" s="13" t="n">
+      <c r="H10" s="13" t="n">
         <v>0.01037994516255386</v>
       </c>
-      <c r="H10" s="10" t="inlineStr">
+      <c r="I10" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I10" s="5" t="inlineStr">
+      <c r="J10" s="5" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -10758,27 +11557,32 @@
           <t>Siteminder</t>
         </is>
       </c>
-      <c r="C11" s="12" t="n">
-        <v>9624</v>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>Producto Propio</t>
+        </is>
       </c>
       <c r="D11" s="12" t="n">
         <v>9624</v>
       </c>
       <c r="E11" s="12" t="n">
+        <v>9624</v>
+      </c>
+      <c r="F11" s="12" t="n">
         <v>201</v>
       </c>
-      <c r="F11" s="13" t="n">
+      <c r="G11" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="G11" s="13" t="n">
+      <c r="H11" s="13" t="n">
         <v>0.02088528678304239</v>
       </c>
-      <c r="H11" s="10" t="inlineStr">
+      <c r="I11" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I11" s="5" t="inlineStr">
+      <c r="J11" s="5" t="inlineStr">
         <is>
           <t>Aceptable</t>
         </is>
@@ -10793,27 +11597,32 @@
           <t>HotelBeds Apitude</t>
         </is>
       </c>
-      <c r="C12" s="12" t="n">
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>Third Party</t>
+        </is>
+      </c>
+      <c r="D12" s="12" t="n">
         <v>5129</v>
       </c>
-      <c r="D12" s="12" t="n">
+      <c r="E12" s="12" t="n">
         <v>4731</v>
       </c>
-      <c r="E12" s="12" t="n">
+      <c r="F12" s="12" t="n">
         <v>63</v>
       </c>
-      <c r="F12" s="13" t="n">
+      <c r="G12" s="13" t="n">
         <v>0.9224020276857087</v>
       </c>
-      <c r="G12" s="13" t="n">
+      <c r="H12" s="13" t="n">
         <v>0.01228309612010138</v>
       </c>
-      <c r="H12" s="8" t="inlineStr">
+      <c r="I12" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I12" s="5" t="inlineStr">
+      <c r="J12" s="5" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -10828,27 +11637,32 @@
           <t>Travelclick</t>
         </is>
       </c>
-      <c r="C13" s="12" t="n">
-        <v>1464</v>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>Producto Propio</t>
+        </is>
       </c>
       <c r="D13" s="12" t="n">
         <v>1464</v>
       </c>
       <c r="E13" s="12" t="n">
+        <v>1464</v>
+      </c>
+      <c r="F13" s="12" t="n">
         <v>41</v>
       </c>
-      <c r="F13" s="13" t="n">
+      <c r="G13" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="G13" s="13" t="n">
+      <c r="H13" s="13" t="n">
         <v>0.02800546448087432</v>
       </c>
-      <c r="H13" s="10" t="inlineStr">
+      <c r="I13" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I13" s="5" t="inlineStr">
+      <c r="J13" s="5" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -10863,27 +11677,32 @@
           <t>Omnibees</t>
         </is>
       </c>
-      <c r="C14" s="12" t="n">
-        <v>382</v>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>Producto Propio</t>
+        </is>
       </c>
       <c r="D14" s="12" t="n">
         <v>382</v>
       </c>
       <c r="E14" s="12" t="n">
+        <v>382</v>
+      </c>
+      <c r="F14" s="12" t="n">
         <v>25</v>
       </c>
-      <c r="F14" s="13" t="n">
+      <c r="G14" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="G14" s="13" t="n">
+      <c r="H14" s="13" t="n">
         <v>0.06544502617801047</v>
       </c>
-      <c r="H14" s="10" t="inlineStr">
+      <c r="I14" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I14" s="5" t="inlineStr">
+      <c r="J14" s="5" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -10898,27 +11717,32 @@
           <t>Hotel Unico V2</t>
         </is>
       </c>
-      <c r="C15" s="12" t="n">
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>Third Party</t>
+        </is>
+      </c>
+      <c r="D15" s="12" t="n">
         <v>15</v>
       </c>
-      <c r="D15" s="12" t="n">
+      <c r="E15" s="12" t="n">
         <v>13</v>
       </c>
-      <c r="E15" s="12" t="n">
+      <c r="F15" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="F15" s="13" t="n">
+      <c r="G15" s="13" t="n">
         <v>0.8666666666666667</v>
       </c>
-      <c r="G15" s="13" t="n">
+      <c r="H15" s="13" t="n">
         <v>0.1333333333333333</v>
       </c>
-      <c r="H15" s="8" t="inlineStr">
+      <c r="I15" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I15" s="5" t="inlineStr">
+      <c r="J15" s="5" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -10935,18 +11759,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I55"/>
+  <dimension ref="A1:J55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
     <col width="50" customWidth="1" min="2" max="2"/>
     <col width="17" customWidth="1" min="3" max="3"/>
-    <col width="41" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="11" customWidth="1" min="6" max="6"/>
-    <col width="21" customWidth="1" min="7" max="7"/>
-    <col width="25" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="41" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="21" customWidth="1" min="8" max="8"/>
+    <col width="25" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -10966,7 +11791,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 09/05/2026 05:12 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 14:32 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -10988,30 +11813,35 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
+          <t>Channel</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
           <t>Destino</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="F5" s="3" t="inlineStr">
         <is>
           <t>CR_Unicos</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="G5" s="3" t="inlineStr">
         <is>
           <t>Bookings</t>
         </is>
       </c>
-      <c r="G5" s="3" t="inlineStr">
+      <c r="H5" s="3" t="inlineStr">
         <is>
           <t>Eficacia</t>
         </is>
       </c>
-      <c r="H5" s="3" t="inlineStr">
+      <c r="I5" s="3" t="inlineStr">
         <is>
           <t>ConvRate</t>
         </is>
       </c>
-      <c r="I5" s="3" t="inlineStr">
+      <c r="J5" s="3" t="inlineStr">
         <is>
           <t>BandaConvRate</t>
         </is>
@@ -11033,22 +11863,27 @@
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
           <t>Abu Dhabi</t>
         </is>
       </c>
-      <c r="E6" s="12" t="n">
+      <c r="F6" s="12" t="n">
         <v>3099</v>
       </c>
-      <c r="F6" s="12" t="n">
+      <c r="G6" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G6" s="13" t="n">
+      <c r="H6" s="13" t="n">
         <v>0.9970958373668926</v>
       </c>
-      <c r="H6" s="13" t="n">
+      <c r="I6" s="13" t="n">
         <v>0.0003226847370119393</v>
       </c>
-      <c r="I6" s="7" t="inlineStr">
+      <c r="J6" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -11070,22 +11905,27 @@
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
           <t>Amsterdam</t>
         </is>
       </c>
-      <c r="E7" s="12" t="n">
+      <c r="F7" s="12" t="n">
         <v>1552</v>
       </c>
-      <c r="F7" s="12" t="n">
+      <c r="G7" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G7" s="13" t="n">
+      <c r="H7" s="13" t="n">
         <v>0.9877577319587629</v>
       </c>
-      <c r="H7" s="13" t="n">
+      <c r="I7" s="13" t="n">
         <v>0.0006443298969072165</v>
       </c>
-      <c r="I7" s="7" t="inlineStr">
+      <c r="J7" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -11107,22 +11947,27 @@
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
           <t>Ras Al Khaimah Area</t>
         </is>
       </c>
-      <c r="E8" s="12" t="n">
+      <c r="F8" s="12" t="n">
         <v>1503</v>
       </c>
-      <c r="F8" s="12" t="n">
+      <c r="G8" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G8" s="13" t="n">
+      <c r="H8" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="H8" s="13" t="n">
+      <c r="I8" s="13" t="n">
         <v>0.0006653359946773121</v>
       </c>
-      <c r="I8" s="7" t="inlineStr">
+      <c r="J8" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -11144,22 +11989,27 @@
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
           <t>Vancouver</t>
         </is>
       </c>
-      <c r="E9" s="12" t="n">
+      <c r="F9" s="12" t="n">
         <v>1464</v>
       </c>
-      <c r="F9" s="12" t="n">
+      <c r="G9" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G9" s="13" t="n">
+      <c r="H9" s="13" t="n">
         <v>0.9330601092896175</v>
       </c>
-      <c r="H9" s="13" t="n">
+      <c r="I9" s="13" t="n">
         <v>0.0006830601092896175</v>
       </c>
-      <c r="I9" s="7" t="inlineStr">
+      <c r="J9" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -11181,22 +12031,27 @@
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
           <t>Orlando</t>
         </is>
       </c>
-      <c r="E10" s="12" t="n">
+      <c r="F10" s="12" t="n">
         <v>1447</v>
       </c>
-      <c r="F10" s="12" t="n">
+      <c r="G10" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G10" s="13" t="n">
+      <c r="H10" s="13" t="n">
         <v>0.9689011748445059</v>
       </c>
-      <c r="H10" s="13" t="n">
+      <c r="I10" s="13" t="n">
         <v>0.000691085003455425</v>
       </c>
-      <c r="I10" s="7" t="inlineStr">
+      <c r="J10" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -11218,22 +12073,27 @@
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
           <t>Paris</t>
         </is>
       </c>
-      <c r="E11" s="12" t="n">
+      <c r="F11" s="12" t="n">
         <v>2625</v>
       </c>
-      <c r="F11" s="12" t="n">
+      <c r="G11" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="G11" s="13" t="n">
+      <c r="H11" s="13" t="n">
         <v>0.9885714285714285</v>
       </c>
-      <c r="H11" s="13" t="n">
+      <c r="I11" s="13" t="n">
         <v>0.0007619047619047619</v>
       </c>
-      <c r="I11" s="7" t="inlineStr">
+      <c r="J11" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -11255,22 +12115,27 @@
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
           <t>Londres</t>
         </is>
       </c>
-      <c r="E12" s="12" t="n">
+      <c r="F12" s="12" t="n">
         <v>2531</v>
       </c>
-      <c r="F12" s="12" t="n">
+      <c r="G12" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="G12" s="13" t="n">
+      <c r="H12" s="13" t="n">
         <v>0.8249703674436981</v>
       </c>
-      <c r="H12" s="13" t="n">
+      <c r="I12" s="13" t="n">
         <v>0.0007902015013828526</v>
       </c>
-      <c r="I12" s="7" t="inlineStr">
+      <c r="J12" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -11292,22 +12157,27 @@
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
           <t>Dubai Area</t>
         </is>
       </c>
-      <c r="E13" s="12" t="n">
+      <c r="F13" s="12" t="n">
         <v>1173</v>
       </c>
-      <c r="F13" s="12" t="n">
+      <c r="G13" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G13" s="13" t="n">
+      <c r="H13" s="13" t="n">
         <v>0.7919863597612958</v>
       </c>
-      <c r="H13" s="13" t="n">
+      <c r="I13" s="13" t="n">
         <v>0.0008525149190110827</v>
       </c>
-      <c r="I13" s="7" t="inlineStr">
+      <c r="J13" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -11329,22 +12199,27 @@
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
           <t>Dubai Area</t>
         </is>
       </c>
-      <c r="E14" s="12" t="n">
+      <c r="F14" s="12" t="n">
         <v>1133</v>
       </c>
-      <c r="F14" s="12" t="n">
+      <c r="G14" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G14" s="13" t="n">
+      <c r="H14" s="13" t="n">
         <v>0.9982347749338041</v>
       </c>
-      <c r="H14" s="13" t="n">
+      <c r="I14" s="13" t="n">
         <v>0.00088261253309797</v>
       </c>
-      <c r="I14" s="7" t="inlineStr">
+      <c r="J14" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -11366,22 +12241,27 @@
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
           <t>Toronto Area</t>
         </is>
       </c>
-      <c r="E15" s="12" t="n">
+      <c r="F15" s="12" t="n">
         <v>3116</v>
       </c>
-      <c r="F15" s="12" t="n">
+      <c r="G15" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="G15" s="13" t="n">
+      <c r="H15" s="13" t="n">
         <v>0.9801026957637997</v>
       </c>
-      <c r="H15" s="13" t="n">
+      <c r="I15" s="13" t="n">
         <v>0.0009627727856225931</v>
       </c>
-      <c r="I15" s="7" t="inlineStr">
+      <c r="J15" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -11403,22 +12283,27 @@
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
           <t>Dubai Area</t>
         </is>
       </c>
-      <c r="E16" s="12" t="n">
+      <c r="F16" s="12" t="n">
         <v>1009</v>
       </c>
-      <c r="F16" s="12" t="n">
+      <c r="G16" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G16" s="13" t="n">
+      <c r="H16" s="13" t="n">
         <v>0.9940535183349851</v>
       </c>
-      <c r="H16" s="13" t="n">
+      <c r="I16" s="13" t="n">
         <v>0.0009910802775024777</v>
       </c>
-      <c r="I16" s="7" t="inlineStr">
+      <c r="J16" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -11440,22 +12325,27 @@
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
           <t>Fort Lauderdale (and vicinity), FL, US</t>
         </is>
       </c>
-      <c r="E17" s="12" t="n">
+      <c r="F17" s="12" t="n">
         <v>999</v>
       </c>
-      <c r="F17" s="12" t="n">
+      <c r="G17" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G17" s="13" t="n">
+      <c r="H17" s="13" t="n">
         <v>0.991991991991992</v>
       </c>
-      <c r="H17" s="13" t="n">
+      <c r="I17" s="13" t="n">
         <v>0.001001001001001001</v>
       </c>
-      <c r="I17" s="7" t="inlineStr">
+      <c r="J17" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -11477,22 +12367,27 @@
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
           <t>Sharjah Area</t>
         </is>
       </c>
-      <c r="E18" s="12" t="n">
+      <c r="F18" s="12" t="n">
         <v>992</v>
       </c>
-      <c r="F18" s="12" t="n">
+      <c r="G18" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G18" s="13" t="n">
+      <c r="H18" s="13" t="n">
         <v>0.9879032258064516</v>
       </c>
-      <c r="H18" s="13" t="n">
+      <c r="I18" s="13" t="n">
         <v>0.001008064516129032</v>
       </c>
-      <c r="I18" s="7" t="inlineStr">
+      <c r="J18" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -11514,22 +12409,27 @@
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
           <t>New York</t>
         </is>
       </c>
-      <c r="E19" s="12" t="n">
+      <c r="F19" s="12" t="n">
         <v>1966</v>
       </c>
-      <c r="F19" s="12" t="n">
+      <c r="G19" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="G19" s="13" t="n">
+      <c r="H19" s="13" t="n">
         <v>0.9771108850457783</v>
       </c>
-      <c r="H19" s="13" t="n">
+      <c r="I19" s="13" t="n">
         <v>0.001017293997965412</v>
       </c>
-      <c r="I19" s="7" t="inlineStr">
+      <c r="J19" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -11551,22 +12451,27 @@
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
           <t>Múnich Area</t>
         </is>
       </c>
-      <c r="E20" s="12" t="n">
+      <c r="F20" s="12" t="n">
         <v>953</v>
       </c>
-      <c r="F20" s="12" t="n">
+      <c r="G20" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G20" s="13" t="n">
+      <c r="H20" s="13" t="n">
         <v>0.8426023084994754</v>
       </c>
-      <c r="H20" s="13" t="n">
+      <c r="I20" s="13" t="n">
         <v>0.001049317943336831</v>
       </c>
-      <c r="I20" s="7" t="inlineStr">
+      <c r="J20" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -11588,22 +12493,27 @@
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
           <t>El Cairo Area</t>
         </is>
       </c>
-      <c r="E21" s="12" t="n">
+      <c r="F21" s="12" t="n">
         <v>953</v>
       </c>
-      <c r="F21" s="12" t="n">
+      <c r="G21" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G21" s="13" t="n">
+      <c r="H21" s="13" t="n">
         <v>0.7292759706190975</v>
       </c>
-      <c r="H21" s="13" t="n">
+      <c r="I21" s="13" t="n">
         <v>0.001049317943336831</v>
       </c>
-      <c r="I21" s="7" t="inlineStr">
+      <c r="J21" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -11625,22 +12535,27 @@
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="inlineStr">
+        <is>
           <t>Paris</t>
         </is>
       </c>
-      <c r="E22" s="12" t="n">
+      <c r="F22" s="12" t="n">
         <v>943</v>
       </c>
-      <c r="F22" s="12" t="n">
+      <c r="G22" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G22" s="13" t="n">
+      <c r="H22" s="13" t="n">
         <v>0.8176033934252386</v>
       </c>
-      <c r="H22" s="13" t="n">
+      <c r="I22" s="13" t="n">
         <v>0.001060445387062566</v>
       </c>
-      <c r="I22" s="7" t="inlineStr">
+      <c r="J22" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -11662,22 +12577,27 @@
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
           <t>Washington, DC Area</t>
         </is>
       </c>
-      <c r="E23" s="12" t="n">
+      <c r="F23" s="12" t="n">
         <v>880</v>
       </c>
-      <c r="F23" s="12" t="n">
+      <c r="G23" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G23" s="13" t="n">
+      <c r="H23" s="13" t="n">
         <v>0.9761363636363637</v>
       </c>
-      <c r="H23" s="13" t="n">
+      <c r="I23" s="13" t="n">
         <v>0.001136363636363636</v>
       </c>
-      <c r="I23" s="7" t="inlineStr">
+      <c r="J23" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -11699,22 +12619,27 @@
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E24" s="5" t="inlineStr">
+        <is>
           <t>French Riviera Area</t>
         </is>
       </c>
-      <c r="E24" s="12" t="n">
+      <c r="F24" s="12" t="n">
         <v>1743</v>
       </c>
-      <c r="F24" s="12" t="n">
+      <c r="G24" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="G24" s="13" t="n">
+      <c r="H24" s="13" t="n">
         <v>0.9845094664371773</v>
       </c>
-      <c r="H24" s="13" t="n">
+      <c r="I24" s="13" t="n">
         <v>0.001147446930579461</v>
       </c>
-      <c r="I24" s="7" t="inlineStr">
+      <c r="J24" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -11736,22 +12661,27 @@
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
           <t>Pittsburgh Area</t>
         </is>
       </c>
-      <c r="E25" s="12" t="n">
+      <c r="F25" s="12" t="n">
         <v>852</v>
       </c>
-      <c r="F25" s="12" t="n">
+      <c r="G25" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G25" s="13" t="n">
+      <c r="H25" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="H25" s="13" t="n">
+      <c r="I25" s="13" t="n">
         <v>0.001173708920187793</v>
       </c>
-      <c r="I25" s="7" t="inlineStr">
+      <c r="J25" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -11773,22 +12703,27 @@
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E26" s="5" t="inlineStr">
+        <is>
           <t>Atenas</t>
         </is>
       </c>
-      <c r="E26" s="12" t="n">
+      <c r="F26" s="12" t="n">
         <v>818</v>
       </c>
-      <c r="F26" s="12" t="n">
+      <c r="G26" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G26" s="13" t="n">
+      <c r="H26" s="13" t="n">
         <v>0.9559902200488998</v>
       </c>
-      <c r="H26" s="13" t="n">
+      <c r="I26" s="13" t="n">
         <v>0.001222493887530562</v>
       </c>
-      <c r="I26" s="7" t="inlineStr">
+      <c r="J26" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -11810,22 +12745,27 @@
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E27" s="5" t="inlineStr">
+        <is>
           <t>Chicago</t>
         </is>
       </c>
-      <c r="E27" s="12" t="n">
+      <c r="F27" s="12" t="n">
         <v>789</v>
       </c>
-      <c r="F27" s="12" t="n">
+      <c r="G27" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G27" s="13" t="n">
+      <c r="H27" s="13" t="n">
         <v>0.7503168567807351</v>
       </c>
-      <c r="H27" s="13" t="n">
+      <c r="I27" s="13" t="n">
         <v>0.001267427122940431</v>
       </c>
-      <c r="I27" s="7" t="inlineStr">
+      <c r="J27" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -11847,22 +12787,27 @@
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E28" s="5" t="inlineStr">
+        <is>
           <t>El Cairo Area</t>
         </is>
       </c>
-      <c r="E28" s="12" t="n">
+      <c r="F28" s="12" t="n">
         <v>1556</v>
       </c>
-      <c r="F28" s="12" t="n">
+      <c r="G28" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="G28" s="13" t="n">
+      <c r="H28" s="13" t="n">
         <v>0.9839331619537275</v>
       </c>
-      <c r="H28" s="13" t="n">
+      <c r="I28" s="13" t="n">
         <v>0.001285347043701799</v>
       </c>
-      <c r="I28" s="7" t="inlineStr">
+      <c r="J28" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -11884,22 +12829,27 @@
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E29" s="5" t="inlineStr">
+        <is>
           <t>Londres</t>
         </is>
       </c>
-      <c r="E29" s="12" t="n">
+      <c r="F29" s="12" t="n">
         <v>1533</v>
       </c>
-      <c r="F29" s="12" t="n">
+      <c r="G29" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="G29" s="13" t="n">
+      <c r="H29" s="13" t="n">
         <v>0.9980430528375733</v>
       </c>
-      <c r="H29" s="13" t="n">
+      <c r="I29" s="13" t="n">
         <v>0.001304631441617743</v>
       </c>
-      <c r="I29" s="7" t="inlineStr">
+      <c r="J29" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -11921,22 +12871,27 @@
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E30" s="5" t="inlineStr">
+        <is>
           <t>Istanbul Area</t>
         </is>
       </c>
-      <c r="E30" s="12" t="n">
+      <c r="F30" s="12" t="n">
         <v>735</v>
       </c>
-      <c r="F30" s="12" t="n">
+      <c r="G30" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G30" s="13" t="n">
+      <c r="H30" s="13" t="n">
         <v>0.9918367346938776</v>
       </c>
-      <c r="H30" s="13" t="n">
+      <c r="I30" s="13" t="n">
         <v>0.001360544217687075</v>
       </c>
-      <c r="I30" s="7" t="inlineStr">
+      <c r="J30" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -11958,22 +12913,27 @@
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E31" s="5" t="inlineStr">
+        <is>
           <t>Fort Lauderdale (and vicinity), FL, US</t>
         </is>
       </c>
-      <c r="E31" s="12" t="n">
+      <c r="F31" s="12" t="n">
         <v>713</v>
       </c>
-      <c r="F31" s="12" t="n">
+      <c r="G31" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G31" s="13" t="n">
+      <c r="H31" s="13" t="n">
         <v>0.9537166900420757</v>
       </c>
-      <c r="H31" s="13" t="n">
+      <c r="I31" s="13" t="n">
         <v>0.001402524544179523</v>
       </c>
-      <c r="I31" s="7" t="inlineStr">
+      <c r="J31" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -11995,22 +12955,27 @@
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E32" s="5" t="inlineStr">
+        <is>
           <t>Tbilisi Area</t>
         </is>
       </c>
-      <c r="E32" s="12" t="n">
+      <c r="F32" s="12" t="n">
         <v>712</v>
       </c>
-      <c r="F32" s="12" t="n">
+      <c r="G32" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G32" s="13" t="n">
+      <c r="H32" s="13" t="n">
         <v>0.8202247191011236</v>
       </c>
-      <c r="H32" s="13" t="n">
+      <c r="I32" s="13" t="n">
         <v>0.001404494382022472</v>
       </c>
-      <c r="I32" s="7" t="inlineStr">
+      <c r="J32" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -12032,22 +12997,27 @@
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E33" s="5" t="inlineStr">
+        <is>
           <t>Chicago</t>
         </is>
       </c>
-      <c r="E33" s="12" t="n">
+      <c r="F33" s="12" t="n">
         <v>712</v>
       </c>
-      <c r="F33" s="12" t="n">
+      <c r="G33" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G33" s="13" t="n">
+      <c r="H33" s="13" t="n">
         <v>0.9705056179775281</v>
       </c>
-      <c r="H33" s="13" t="n">
+      <c r="I33" s="13" t="n">
         <v>0.001404494382022472</v>
       </c>
-      <c r="I33" s="7" t="inlineStr">
+      <c r="J33" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -12069,22 +13039,27 @@
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="E34" s="5" t="inlineStr">
+        <is>
           <t>Cancún</t>
         </is>
       </c>
-      <c r="E34" s="12" t="n">
+      <c r="F34" s="12" t="n">
         <v>682</v>
       </c>
-      <c r="F34" s="12" t="n">
+      <c r="G34" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G34" s="13" t="n">
+      <c r="H34" s="13" t="n">
         <v>0.9970674486803519</v>
       </c>
-      <c r="H34" s="13" t="n">
+      <c r="I34" s="13" t="n">
         <v>0.001466275659824047</v>
       </c>
-      <c r="I34" s="7" t="inlineStr">
+      <c r="J34" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -12106,22 +13081,27 @@
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E35" s="5" t="inlineStr">
+        <is>
           <t>Vienna Area</t>
         </is>
       </c>
-      <c r="E35" s="12" t="n">
+      <c r="F35" s="12" t="n">
         <v>675</v>
       </c>
-      <c r="F35" s="12" t="n">
+      <c r="G35" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G35" s="13" t="n">
+      <c r="H35" s="13" t="n">
         <v>0.9792592592592593</v>
       </c>
-      <c r="H35" s="13" t="n">
+      <c r="I35" s="13" t="n">
         <v>0.001481481481481481</v>
       </c>
-      <c r="I35" s="7" t="inlineStr">
+      <c r="J35" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -12143,22 +13123,27 @@
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E36" s="5" t="inlineStr">
+        <is>
           <t>Phu Quoc Island Area</t>
         </is>
       </c>
-      <c r="E36" s="12" t="n">
+      <c r="F36" s="12" t="n">
         <v>673</v>
       </c>
-      <c r="F36" s="12" t="n">
+      <c r="G36" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G36" s="13" t="n">
+      <c r="H36" s="13" t="n">
         <v>0.7622585438335809</v>
       </c>
-      <c r="H36" s="13" t="n">
+      <c r="I36" s="13" t="n">
         <v>0.001485884101040119</v>
       </c>
-      <c r="I36" s="7" t="inlineStr">
+      <c r="J36" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -12180,22 +13165,27 @@
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E37" s="5" t="inlineStr">
+        <is>
           <t>Boston</t>
         </is>
       </c>
-      <c r="E37" s="12" t="n">
+      <c r="F37" s="12" t="n">
         <v>669</v>
       </c>
-      <c r="F37" s="12" t="n">
+      <c r="G37" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G37" s="13" t="n">
+      <c r="H37" s="13" t="n">
         <v>0.9955156950672646</v>
       </c>
-      <c r="H37" s="13" t="n">
+      <c r="I37" s="13" t="n">
         <v>0.001494768310911809</v>
       </c>
-      <c r="I37" s="7" t="inlineStr">
+      <c r="J37" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -12217,22 +13207,27 @@
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E38" s="5" t="inlineStr">
+        <is>
           <t>Paris</t>
         </is>
       </c>
-      <c r="E38" s="12" t="n">
+      <c r="F38" s="12" t="n">
         <v>1313</v>
       </c>
-      <c r="F38" s="12" t="n">
+      <c r="G38" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="G38" s="13" t="n">
+      <c r="H38" s="13" t="n">
         <v>0.9878141660319878</v>
       </c>
-      <c r="H38" s="13" t="n">
+      <c r="I38" s="13" t="n">
         <v>0.001523229246001523</v>
       </c>
-      <c r="I38" s="7" t="inlineStr">
+      <c r="J38" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -12254,22 +13249,27 @@
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E39" s="5" t="inlineStr">
+        <is>
           <t>Miami Area</t>
         </is>
       </c>
-      <c r="E39" s="12" t="n">
+      <c r="F39" s="12" t="n">
         <v>649</v>
       </c>
-      <c r="F39" s="12" t="n">
+      <c r="G39" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G39" s="13" t="n">
+      <c r="H39" s="13" t="n">
         <v>0.9938366718027735</v>
       </c>
-      <c r="H39" s="13" t="n">
+      <c r="I39" s="13" t="n">
         <v>0.001540832049306626</v>
       </c>
-      <c r="I39" s="7" t="inlineStr">
+      <c r="J39" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -12291,22 +13291,27 @@
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E40" s="5" t="inlineStr">
+        <is>
           <t>Fort Lauderdale (and vicinity), FL, US</t>
         </is>
       </c>
-      <c r="E40" s="12" t="n">
+      <c r="F40" s="12" t="n">
         <v>636</v>
       </c>
-      <c r="F40" s="12" t="n">
+      <c r="G40" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G40" s="13" t="n">
+      <c r="H40" s="13" t="n">
         <v>0.9921383647798742</v>
       </c>
-      <c r="H40" s="13" t="n">
+      <c r="I40" s="13" t="n">
         <v>0.001572327044025157</v>
       </c>
-      <c r="I40" s="7" t="inlineStr">
+      <c r="J40" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -12328,22 +13333,27 @@
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E41" s="5" t="inlineStr">
+        <is>
           <t>Bahamas</t>
         </is>
       </c>
-      <c r="E41" s="12" t="n">
+      <c r="F41" s="12" t="n">
         <v>636</v>
       </c>
-      <c r="F41" s="12" t="n">
+      <c r="G41" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G41" s="13" t="n">
+      <c r="H41" s="13" t="n">
         <v>0.9292452830188679</v>
       </c>
-      <c r="H41" s="13" t="n">
+      <c r="I41" s="13" t="n">
         <v>0.001572327044025157</v>
       </c>
-      <c r="I41" s="7" t="inlineStr">
+      <c r="J41" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -12365,22 +13375,27 @@
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E42" s="5" t="inlineStr">
+        <is>
           <t>New Orleans</t>
         </is>
       </c>
-      <c r="E42" s="12" t="n">
+      <c r="F42" s="12" t="n">
         <v>630</v>
       </c>
-      <c r="F42" s="12" t="n">
+      <c r="G42" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G42" s="13" t="n">
+      <c r="H42" s="13" t="n">
         <v>0.9666666666666667</v>
       </c>
-      <c r="H42" s="13" t="n">
+      <c r="I42" s="13" t="n">
         <v>0.001587301587301587</v>
       </c>
-      <c r="I42" s="7" t="inlineStr">
+      <c r="J42" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -12402,22 +13417,27 @@
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E43" s="5" t="inlineStr">
+        <is>
           <t>Londres</t>
         </is>
       </c>
-      <c r="E43" s="12" t="n">
+      <c r="F43" s="12" t="n">
         <v>616</v>
       </c>
-      <c r="F43" s="12" t="n">
+      <c r="G43" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G43" s="13" t="n">
+      <c r="H43" s="13" t="n">
         <v>0.9967532467532467</v>
       </c>
-      <c r="H43" s="13" t="n">
+      <c r="I43" s="13" t="n">
         <v>0.001623376623376623</v>
       </c>
-      <c r="I43" s="7" t="inlineStr">
+      <c r="J43" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -12439,22 +13459,27 @@
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E44" s="5" t="inlineStr">
+        <is>
           <t>Düsseldorf Area</t>
         </is>
       </c>
-      <c r="E44" s="12" t="n">
+      <c r="F44" s="12" t="n">
         <v>615</v>
       </c>
-      <c r="F44" s="12" t="n">
+      <c r="G44" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G44" s="13" t="n">
+      <c r="H44" s="13" t="n">
         <v>0.8634146341463415</v>
       </c>
-      <c r="H44" s="13" t="n">
+      <c r="I44" s="13" t="n">
         <v>0.001626016260162602</v>
       </c>
-      <c r="I44" s="7" t="inlineStr">
+      <c r="J44" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -12476,22 +13501,27 @@
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E45" s="5" t="inlineStr">
+        <is>
           <t>Hurghada Area</t>
         </is>
       </c>
-      <c r="E45" s="12" t="n">
+      <c r="F45" s="12" t="n">
         <v>610</v>
       </c>
-      <c r="F45" s="12" t="n">
+      <c r="G45" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G45" s="13" t="n">
+      <c r="H45" s="13" t="n">
         <v>0.9967213114754099</v>
       </c>
-      <c r="H45" s="13" t="n">
+      <c r="I45" s="13" t="n">
         <v>0.001639344262295082</v>
       </c>
-      <c r="I45" s="7" t="inlineStr">
+      <c r="J45" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -12513,22 +13543,27 @@
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E46" s="5" t="inlineStr">
+        <is>
           <t>Bucarest Area</t>
         </is>
       </c>
-      <c r="E46" s="12" t="n">
+      <c r="F46" s="12" t="n">
         <v>586</v>
       </c>
-      <c r="F46" s="12" t="n">
+      <c r="G46" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G46" s="13" t="n">
+      <c r="H46" s="13" t="n">
         <v>0.8020477815699659</v>
       </c>
-      <c r="H46" s="13" t="n">
+      <c r="I46" s="13" t="n">
         <v>0.001706484641638225</v>
       </c>
-      <c r="I46" s="7" t="inlineStr">
+      <c r="J46" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -12550,22 +13585,27 @@
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E47" s="5" t="inlineStr">
+        <is>
           <t>Miami Area</t>
         </is>
       </c>
-      <c r="E47" s="12" t="n">
+      <c r="F47" s="12" t="n">
         <v>580</v>
       </c>
-      <c r="F47" s="12" t="n">
+      <c r="G47" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G47" s="13" t="n">
+      <c r="H47" s="13" t="n">
         <v>0.9517241379310345</v>
       </c>
-      <c r="H47" s="13" t="n">
+      <c r="I47" s="13" t="n">
         <v>0.001724137931034483</v>
       </c>
-      <c r="I47" s="7" t="inlineStr">
+      <c r="J47" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -12587,22 +13627,27 @@
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E48" s="5" t="inlineStr">
+        <is>
           <t>Orlando</t>
         </is>
       </c>
-      <c r="E48" s="12" t="n">
+      <c r="F48" s="12" t="n">
         <v>568</v>
       </c>
-      <c r="F48" s="12" t="n">
+      <c r="G48" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G48" s="13" t="n">
+      <c r="H48" s="13" t="n">
         <v>0.9911971830985915</v>
       </c>
-      <c r="H48" s="13" t="n">
+      <c r="I48" s="13" t="n">
         <v>0.00176056338028169</v>
       </c>
-      <c r="I48" s="7" t="inlineStr">
+      <c r="J48" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -12624,22 +13669,27 @@
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E49" s="5" t="inlineStr">
+        <is>
           <t>Puerto Rico</t>
         </is>
       </c>
-      <c r="E49" s="12" t="n">
+      <c r="F49" s="12" t="n">
         <v>565</v>
       </c>
-      <c r="F49" s="12" t="n">
+      <c r="G49" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G49" s="13" t="n">
+      <c r="H49" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="H49" s="13" t="n">
+      <c r="I49" s="13" t="n">
         <v>0.001769911504424779</v>
       </c>
-      <c r="I49" s="7" t="inlineStr">
+      <c r="J49" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -12661,22 +13711,27 @@
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E50" s="5" t="inlineStr">
+        <is>
           <t>Greenville Area</t>
         </is>
       </c>
-      <c r="E50" s="12" t="n">
+      <c r="F50" s="12" t="n">
         <v>1687</v>
       </c>
-      <c r="F50" s="12" t="n">
+      <c r="G50" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="G50" s="13" t="n">
+      <c r="H50" s="13" t="n">
         <v>0.99407231772377</v>
       </c>
-      <c r="H50" s="13" t="n">
+      <c r="I50" s="13" t="n">
         <v>0.001778304682868998</v>
       </c>
-      <c r="I50" s="7" t="inlineStr">
+      <c r="J50" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -12698,22 +13753,27 @@
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E51" s="5" t="inlineStr">
+        <is>
           <t>Niagara Falls, Canada</t>
         </is>
       </c>
-      <c r="E51" s="12" t="n">
+      <c r="F51" s="12" t="n">
         <v>2778</v>
       </c>
-      <c r="F51" s="12" t="n">
+      <c r="G51" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="G51" s="13" t="n">
+      <c r="H51" s="13" t="n">
         <v>0.9946004319654428</v>
       </c>
-      <c r="H51" s="13" t="n">
+      <c r="I51" s="13" t="n">
         <v>0.001799856011519079</v>
       </c>
-      <c r="I51" s="7" t="inlineStr">
+      <c r="J51" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -12735,22 +13795,27 @@
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E52" s="5" t="inlineStr">
+        <is>
           <t>Cleveland Area</t>
         </is>
       </c>
-      <c r="E52" s="12" t="n">
+      <c r="F52" s="12" t="n">
         <v>538</v>
       </c>
-      <c r="F52" s="12" t="n">
+      <c r="G52" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G52" s="13" t="n">
+      <c r="H52" s="13" t="n">
         <v>0.9312267657992565</v>
       </c>
-      <c r="H52" s="13" t="n">
+      <c r="I52" s="13" t="n">
         <v>0.001858736059479554</v>
       </c>
-      <c r="I52" s="7" t="inlineStr">
+      <c r="J52" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -12772,22 +13837,27 @@
       </c>
       <c r="D53" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E53" s="5" t="inlineStr">
+        <is>
           <t>New York</t>
         </is>
       </c>
-      <c r="E53" s="12" t="n">
+      <c r="F53" s="12" t="n">
         <v>2098</v>
       </c>
-      <c r="F53" s="12" t="n">
+      <c r="G53" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="G53" s="13" t="n">
+      <c r="H53" s="13" t="n">
         <v>0.8975214489990467</v>
       </c>
-      <c r="H53" s="13" t="n">
+      <c r="I53" s="13" t="n">
         <v>0.001906577693040991</v>
       </c>
-      <c r="I53" s="7" t="inlineStr">
+      <c r="J53" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -12809,22 +13879,27 @@
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E54" s="5" t="inlineStr">
+        <is>
           <t>Buffalo Area</t>
         </is>
       </c>
-      <c r="E54" s="12" t="n">
+      <c r="F54" s="12" t="n">
         <v>516</v>
       </c>
-      <c r="F54" s="12" t="n">
+      <c r="G54" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G54" s="13" t="n">
+      <c r="H54" s="13" t="n">
         <v>0.9709302325581395</v>
       </c>
-      <c r="H54" s="13" t="n">
+      <c r="I54" s="13" t="n">
         <v>0.001937984496124031</v>
       </c>
-      <c r="I54" s="7" t="inlineStr">
+      <c r="J54" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -12846,22 +13921,27 @@
       </c>
       <c r="D55" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E55" s="5" t="inlineStr">
+        <is>
           <t>New York</t>
         </is>
       </c>
-      <c r="E55" s="12" t="n">
+      <c r="F55" s="12" t="n">
         <v>2048</v>
       </c>
-      <c r="F55" s="12" t="n">
+      <c r="G55" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="G55" s="13" t="n">
+      <c r="H55" s="13" t="n">
         <v>0.99365234375</v>
       </c>
-      <c r="H55" s="13" t="n">
+      <c r="I55" s="13" t="n">
         <v>0.001953125</v>
       </c>
-      <c r="I55" s="7" t="inlineStr">
+      <c r="J55" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>

--- a/checkrates/week-18/Analisis_Checkrates_OP_7d.xlsx
+++ b/checkrates/week-18/Analisis_Checkrates_OP_7d.xlsx
@@ -541,7 +541,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 09/05/2026 14:32 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 14:42 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -694,7 +694,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 09/05/2026 14:32 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 14:42 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -854,7 +854,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 09/05/2026 14:32 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 14:42 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3208,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 09/05/2026 14:32 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 14:42 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -5407,7 +5407,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 09/05/2026 14:32 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 14:42 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -7605,7 +7605,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 09/05/2026 14:32 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 14:42 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -9448,7 +9448,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 09/05/2026 14:32 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 14:42 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -11292,7 +11292,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 09/05/2026 14:32 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 14:42 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -11791,7 +11791,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 09/05/2026 14:32 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 14:42 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
